--- a/database/event/6334/event_6334_evp_summary.xlsx
+++ b/database/event/6334/event_6334_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.7526</v>
+        <v>5.6264</v>
       </c>
       <c r="C2" t="n">
-        <v>1.1246</v>
+        <v>1.1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9026</v>
+        <v>1.7976</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7526</v>
+        <v>5.6264</v>
       </c>
       <c r="F2" t="n">
-        <v>5.7526</v>
+        <v>5.6264</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>6.7169</v>
+        <v>6.519</v>
       </c>
       <c r="I2" t="n">
         <v>6.9711</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.2967</v>
+        <v>4.2443</v>
       </c>
       <c r="C3" t="n">
-        <v>0.84</v>
+        <v>0.8298</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3144</v>
+        <v>1.247</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2967</v>
+        <v>4.2443</v>
       </c>
       <c r="F3" t="n">
-        <v>4.2967</v>
+        <v>4.2443</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4341</v>
+        <v>4.352</v>
       </c>
       <c r="I3" t="n">
         <v>4.5383</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.2331</v>
+        <v>4.1517</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8276</v>
+        <v>0.8117</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2887</v>
+        <v>1.2101</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2331</v>
+        <v>4.1517</v>
       </c>
       <c r="F4" t="n">
-        <v>4.2331</v>
+        <v>4.1517</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3345</v>
+        <v>4.2068</v>
       </c>
       <c r="I4" t="n">
         <v>4.4986</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.2193</v>
+        <v>4.1382</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8249</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2831</v>
+        <v>1.2047</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2193</v>
+        <v>4.1382</v>
       </c>
       <c r="F5" t="n">
-        <v>4.2193</v>
+        <v>4.1382</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4.3128</v>
+        <v>4.1857</v>
       </c>
       <c r="I5" t="n">
         <v>4.476</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.7803</v>
+        <v>3.7242</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7391</v>
+        <v>0.7281</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1058</v>
+        <v>1.0398</v>
       </c>
       <c r="E6" t="n">
-        <v>3.7803</v>
+        <v>3.7242</v>
       </c>
       <c r="F6" t="n">
-        <v>3.7803</v>
+        <v>3.7242</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7803</v>
+        <v>3.7242</v>
       </c>
       <c r="I6" t="n">
         <v>3.8512</v>
@@ -722,93 +722,93 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lack1</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.7425</v>
+        <v>3.6331</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7317</v>
+        <v>0.7103</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0905</v>
+        <v>1.0035</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7425</v>
+        <v>3.6331</v>
       </c>
       <c r="F7" t="n">
-        <v>3.7425</v>
+        <v>3.6331</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3.7425</v>
+        <v>3.6331</v>
       </c>
       <c r="I7" t="n">
-        <v>3.9022</v>
+        <v>3.7886</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>440</v>
+        <v>292</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.9022</v>
+        <v>3.7886</v>
       </c>
       <c r="N7" t="n">
-        <v>440</v>
+        <v>292</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>Lack1</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7017</v>
+        <v>3.6187</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7237</v>
+        <v>0.7075</v>
       </c>
       <c r="D8" t="n">
-        <v>1.074</v>
+        <v>0.9978</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7017</v>
+        <v>3.6187</v>
       </c>
       <c r="F8" t="n">
-        <v>3.7017</v>
+        <v>3.6187</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3.7017</v>
+        <v>3.6187</v>
       </c>
       <c r="I8" t="n">
-        <v>3.7886</v>
+        <v>3.9022</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>292</v>
+        <v>440</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7886</v>
+        <v>3.9022</v>
       </c>
       <c r="N8" t="n">
-        <v>292</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9">
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.6382</v>
+        <v>3.5178</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7113</v>
+        <v>0.6877</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0484</v>
+        <v>0.9576</v>
       </c>
       <c r="E9" t="n">
-        <v>3.6382</v>
+        <v>3.5178</v>
       </c>
       <c r="F9" t="n">
-        <v>3.6382</v>
+        <v>3.5178</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3.6382</v>
+        <v>3.5178</v>
       </c>
       <c r="I9" t="n">
         <v>3.7934</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.8682</v>
+        <v>2.8151</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5607</v>
+        <v>0.5504</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7373</v>
+        <v>0.6776</v>
       </c>
       <c r="E10" t="n">
-        <v>2.8682</v>
+        <v>2.8151</v>
       </c>
       <c r="F10" t="n">
-        <v>2.8682</v>
+        <v>2.8151</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8682</v>
+        <v>2.8151</v>
       </c>
       <c r="I10" t="n">
         <v>2.9356</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.1328</v>
+        <v>2.1012</v>
       </c>
       <c r="C11" t="n">
-        <v>0.417</v>
+        <v>0.4108</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4402</v>
+        <v>0.3932</v>
       </c>
       <c r="E11" t="n">
-        <v>2.1328</v>
+        <v>2.1012</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1328</v>
+        <v>2.1012</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.1328</v>
+        <v>2.1012</v>
       </c>
       <c r="I11" t="n">
         <v>2.1728</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.9773</v>
+        <v>1.9119</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3866</v>
+        <v>0.3738</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3774</v>
+        <v>0.3178</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9773</v>
+        <v>1.9119</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9773</v>
+        <v>1.9119</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.9773</v>
+        <v>1.9119</v>
       </c>
       <c r="I12" t="n">
         <v>2.0617</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.8459</v>
+        <v>1.839</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3609</v>
+        <v>0.3595</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3243</v>
+        <v>0.2887</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8459</v>
+        <v>1.839</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8459</v>
+        <v>1.839</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.8459</v>
+        <v>1.839</v>
       </c>
       <c r="I13" t="n">
         <v>1.8545</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.5745</v>
+        <v>1.5454</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3078</v>
+        <v>0.3021</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2147</v>
+        <v>0.1718</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5745</v>
+        <v>1.5454</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5745</v>
+        <v>1.5454</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5745</v>
+        <v>1.5454</v>
       </c>
       <c r="I14" t="n">
         <v>1.6115</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.5603</v>
+        <v>1.5315</v>
       </c>
       <c r="C15" t="n">
-        <v>0.305</v>
+        <v>0.2994</v>
       </c>
       <c r="D15" t="n">
-        <v>0.209</v>
+        <v>0.1662</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5603</v>
+        <v>1.5315</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5603</v>
+        <v>1.5315</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5603</v>
+        <v>1.5315</v>
       </c>
       <c r="I15" t="n">
         <v>1.597</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8554</v>
+        <v>0.8302</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1672</v>
+        <v>0.1623</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.07580000000000001</v>
+        <v>-0.1132</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8554</v>
+        <v>0.8302</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8554</v>
+        <v>0.8302</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8554</v>
+        <v>0.8302</v>
       </c>
       <c r="I16" t="n">
         <v>0.8878</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7658</v>
+        <v>0.7516</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1497</v>
+        <v>0.1469</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.112</v>
+        <v>-0.1445</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7658</v>
+        <v>0.7516</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7658</v>
+        <v>0.7516</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7658</v>
+        <v>0.7516</v>
       </c>
       <c r="I17" t="n">
         <v>0.7838000000000001</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7025</v>
+        <v>0.6921</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1373</v>
+        <v>0.1353</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1376</v>
+        <v>-0.1682</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7025</v>
+        <v>0.6921</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7025</v>
+        <v>0.6921</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7025</v>
+        <v>0.6921</v>
       </c>
       <c r="I18" t="n">
         <v>0.7157</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6833</v>
+        <v>0.6632</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1336</v>
+        <v>0.1297</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1453</v>
+        <v>-0.1797</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6833</v>
+        <v>0.6632</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6833</v>
+        <v>0.6632</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6833</v>
+        <v>0.6632</v>
       </c>
       <c r="I19" t="n">
         <v>0.7092000000000001</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6113</v>
+        <v>0.6067</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1195</v>
+        <v>0.1186</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1744</v>
+        <v>-0.2022</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6113</v>
+        <v>0.6067</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6113</v>
+        <v>0.6067</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6113</v>
+        <v>0.6067</v>
       </c>
       <c r="I20" t="n">
         <v>0.617</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5484</v>
+        <v>0.5443</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1072</v>
+        <v>0.1064</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1998</v>
+        <v>-0.2271</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5484</v>
+        <v>0.5443</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5484</v>
+        <v>0.5443</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5484</v>
+        <v>0.5443</v>
       </c>
       <c r="I21" t="n">
         <v>0.5535</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2745</v>
+        <v>0.2704</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0537</v>
+        <v>0.0529</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3105</v>
+        <v>-0.3362</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2745</v>
+        <v>0.2704</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2745</v>
+        <v>0.2704</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2745</v>
+        <v>0.2704</v>
       </c>
       <c r="I22" t="n">
         <v>0.2796</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2725</v>
+        <v>0.2694</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0533</v>
+        <v>0.0527</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3113</v>
+        <v>-0.3366</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2725</v>
+        <v>0.2694</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2725</v>
+        <v>0.2694</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2725</v>
+        <v>0.2694</v>
       </c>
       <c r="I23" t="n">
         <v>0.2763</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2604</v>
+        <v>0.2556</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0509</v>
+        <v>0.05</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3162</v>
+        <v>-0.3421</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2604</v>
+        <v>0.2556</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2604</v>
+        <v>0.2556</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2604</v>
+        <v>0.2556</v>
       </c>
       <c r="I24" t="n">
         <v>0.2665</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1398</v>
+        <v>0.1393</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0273</v>
+        <v>0.0272</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3649</v>
+        <v>-0.3884</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1398</v>
+        <v>0.1393</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1398</v>
+        <v>0.1393</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1398</v>
+        <v>0.1393</v>
       </c>
       <c r="I25" t="n">
         <v>0.1405</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1102</v>
+        <v>-0.1082</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0215</v>
+        <v>-0.0212</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4659</v>
+        <v>-0.487</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1102</v>
+        <v>-0.1082</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1102</v>
+        <v>-0.1082</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1102</v>
+        <v>-0.1082</v>
       </c>
       <c r="I26" t="n">
         <v>-0.1128</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.4595</v>
+        <v>-0.451</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0898</v>
+        <v>-0.0882</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.607</v>
+        <v>-0.6236</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.4595</v>
+        <v>-0.451</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.4595</v>
+        <v>-0.451</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.4595</v>
+        <v>-0.451</v>
       </c>
       <c r="I27" t="n">
         <v>-0.4703</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.4662</v>
+        <v>-0.4628</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0911</v>
+        <v>-0.0905</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6097</v>
+        <v>-0.6283</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.4662</v>
+        <v>-0.4628</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.4662</v>
+        <v>-0.4628</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.4662</v>
+        <v>-0.4628</v>
       </c>
       <c r="I28" t="n">
         <v>-0.4706</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.4684</v>
+        <v>-0.4632</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0916</v>
+        <v>-0.0906</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6106</v>
+        <v>-0.6284</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.4684</v>
+        <v>-0.4632</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.4684</v>
+        <v>-0.4632</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.4684</v>
+        <v>-0.4632</v>
       </c>
       <c r="I29" t="n">
         <v>-0.475</v>
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.5003</v>
+        <v>-0.4984</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0978</v>
+        <v>-0.0974</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.6425</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.5003</v>
+        <v>-0.4984</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.5003</v>
+        <v>-0.4984</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.5003</v>
+        <v>-0.4984</v>
       </c>
       <c r="I30" t="n">
         <v>-0.5026</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.6768999999999999</v>
+        <v>-0.6669</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1323</v>
+        <v>-0.1304</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6948</v>
+        <v>-0.7096</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.6768999999999999</v>
+        <v>-0.6669</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.6768999999999999</v>
+        <v>-0.6669</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.6768999999999999</v>
+        <v>-0.6669</v>
       </c>
       <c r="I31" t="n">
         <v>-0.6896</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.7925</v>
+        <v>-0.7896</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1549</v>
+        <v>-0.1544</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7415</v>
+        <v>-0.7585</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.7925</v>
+        <v>-0.7896</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.7925</v>
+        <v>-0.7896</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.7925</v>
+        <v>-0.7896</v>
       </c>
       <c r="I32" t="n">
         <v>-0.7962</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.926</v>
+        <v>-0.9191</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.181</v>
+        <v>-0.1797</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7954</v>
+        <v>-0.8101</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.926</v>
+        <v>-0.9191</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.926</v>
+        <v>-0.9191</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.926</v>
+        <v>-0.9191</v>
       </c>
       <c r="I33" t="n">
         <v>-0.9346</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.9998</v>
+        <v>-0.9668</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1955</v>
+        <v>-0.189</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8253</v>
+        <v>-0.8290999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.9998</v>
+        <v>-0.9668</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.9998</v>
+        <v>-0.9668</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.9998</v>
+        <v>-0.9668</v>
       </c>
       <c r="I34" t="n">
         <v>-1.0425</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.0911</v>
+        <v>-1.0871</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2133</v>
+        <v>-0.2125</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8621</v>
+        <v>-0.877</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.0911</v>
+        <v>-1.0871</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.0911</v>
+        <v>-1.0871</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.0911</v>
+        <v>-1.0871</v>
       </c>
       <c r="I35" t="n">
         <v>-1.0962</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.443</v>
+        <v>-1.4163</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2821</v>
+        <v>-0.2769</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0043</v>
+        <v>-1.0082</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.443</v>
+        <v>-1.4163</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.443</v>
+        <v>-1.4163</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.443</v>
+        <v>-1.4163</v>
       </c>
       <c r="I36" t="n">
         <v>-1.4769</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.4844</v>
+        <v>-1.4678</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2902</v>
+        <v>-0.287</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.021</v>
+        <v>-1.0287</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.4844</v>
+        <v>-1.4678</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.4844</v>
+        <v>-1.4678</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.4844</v>
+        <v>-1.4678</v>
       </c>
       <c r="I37" t="n">
         <v>-1.5052</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.5435</v>
+        <v>-1.532</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3018</v>
+        <v>-0.2995</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0449</v>
+        <v>-1.0543</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.5435</v>
+        <v>-1.532</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.5435</v>
+        <v>-1.532</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.5435</v>
+        <v>-1.532</v>
       </c>
       <c r="I38" t="n">
         <v>-1.5579</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.9782</v>
+        <v>-1.9561</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3867</v>
+        <v>-0.3824</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2205</v>
+        <v>-1.2232</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.9782</v>
+        <v>-1.9561</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.9782</v>
+        <v>-1.9561</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.9782</v>
+        <v>-1.9561</v>
       </c>
       <c r="I39" t="n">
         <v>-2.0059</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.0264</v>
+        <v>-1.9594</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3962</v>
+        <v>-0.3831</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.24</v>
+        <v>-1.2245</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.0264</v>
+        <v>-1.9594</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.0264</v>
+        <v>-1.9594</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.0264</v>
+        <v>-1.9594</v>
       </c>
       <c r="I40" t="n">
         <v>-2.1129</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.5749</v>
+        <v>-2.5462</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5034</v>
+        <v>-0.4978</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4616</v>
+        <v>-1.4583</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.5749</v>
+        <v>-2.5462</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.5749</v>
+        <v>-2.5462</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.5749</v>
+        <v>-2.5462</v>
       </c>
       <c r="I41" t="n">
         <v>-2.611</v>

--- a/database/event/6334/event_6334_evp_summary.xlsx
+++ b/database/event/6334/event_6334_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.6264</v>
+        <v>4.7451</v>
       </c>
       <c r="C2" t="n">
-        <v>1.1</v>
+        <v>0.9277</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7976</v>
+        <v>1.5042</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6264</v>
+        <v>4.7451</v>
       </c>
       <c r="F2" t="n">
-        <v>5.6264</v>
+        <v>4.7451</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>6.519</v>
+        <v>7.0595</v>
       </c>
       <c r="I2" t="n">
-        <v>6.9711</v>
+        <v>9.7455</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>6.9711</v>
+        <v>9.7455</v>
       </c>
       <c r="N2" t="n">
         <v>257</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.2443</v>
+        <v>3.9159</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8298</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>1.247</v>
+        <v>1.1298</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2443</v>
+        <v>3.9159</v>
       </c>
       <c r="F3" t="n">
-        <v>4.2443</v>
+        <v>3.9159</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>4.352</v>
+        <v>5.2387</v>
       </c>
       <c r="I3" t="n">
-        <v>4.5383</v>
+        <v>6.4083</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>4.5383</v>
+        <v>6.4083</v>
       </c>
       <c r="N3" t="n">
         <v>266</v>
@@ -584,32 +584,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>Ax1Le</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.1517</v>
+        <v>3.4398</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8117</v>
+        <v>0.6725</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2101</v>
+        <v>0.9149</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1517</v>
+        <v>3.4398</v>
       </c>
       <c r="F4" t="n">
-        <v>4.1517</v>
+        <v>3.4398</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2068</v>
+        <v>4.1934</v>
       </c>
       <c r="I4" t="n">
-        <v>4.4986</v>
+        <v>5.7889</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>4.4986</v>
+        <v>5.7889</v>
       </c>
       <c r="N4" t="n">
         <v>257</v>
@@ -630,32 +630,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ax1Le</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.1382</v>
+        <v>3.4338</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.6713</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2047</v>
+        <v>0.9122</v>
       </c>
       <c r="E5" t="n">
-        <v>4.1382</v>
+        <v>3.4338</v>
       </c>
       <c r="F5" t="n">
-        <v>4.1382</v>
+        <v>3.4338</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4.1857</v>
+        <v>4.1802</v>
       </c>
       <c r="I5" t="n">
-        <v>4.476</v>
+        <v>5.7706</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.476</v>
+        <v>5.7706</v>
       </c>
       <c r="N5" t="n">
         <v>257</v>
@@ -676,170 +676,170 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.7242</v>
+        <v>3.3095</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7281</v>
+        <v>0.647</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0398</v>
+        <v>0.8561</v>
       </c>
       <c r="E6" t="n">
-        <v>3.7242</v>
+        <v>3.3095</v>
       </c>
       <c r="F6" t="n">
-        <v>3.7242</v>
+        <v>3.3095</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7242</v>
+        <v>3.9073</v>
       </c>
       <c r="I6" t="n">
-        <v>3.8512</v>
+        <v>4.7796</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>264</v>
+        <v>292</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.8512</v>
+        <v>4.7796</v>
       </c>
       <c r="N6" t="n">
-        <v>264</v>
+        <v>292</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.6331</v>
+        <v>3.2504</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7103</v>
+        <v>0.6355</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0035</v>
+        <v>0.8294</v>
       </c>
       <c r="E7" t="n">
-        <v>3.6331</v>
+        <v>3.2504</v>
       </c>
       <c r="F7" t="n">
-        <v>3.6331</v>
+        <v>3.2504</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3.6331</v>
+        <v>3.7775</v>
       </c>
       <c r="I7" t="n">
-        <v>3.7886</v>
+        <v>4.4383</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>292</v>
+        <v>264</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7886</v>
+        <v>4.4383</v>
       </c>
       <c r="N7" t="n">
-        <v>292</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lack1</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.6187</v>
+        <v>3.1448</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7075</v>
+        <v>0.6148</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9978</v>
+        <v>0.7817</v>
       </c>
       <c r="E8" t="n">
-        <v>3.6187</v>
+        <v>3.1448</v>
       </c>
       <c r="F8" t="n">
-        <v>3.6187</v>
+        <v>3.1448</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6187</v>
+        <v>3.5458</v>
       </c>
       <c r="I8" t="n">
-        <v>3.9022</v>
+        <v>4.3374</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>440</v>
+        <v>292</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.9022</v>
+        <v>4.3374</v>
       </c>
       <c r="N8" t="n">
-        <v>440</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Forester</t>
+          <t>Lack1</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.5178</v>
+        <v>3.132</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6877</v>
+        <v>0.6123</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9576</v>
+        <v>0.7759</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5178</v>
+        <v>3.132</v>
       </c>
       <c r="F9" t="n">
-        <v>3.5178</v>
+        <v>3.132</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5178</v>
+        <v>3.5175</v>
       </c>
       <c r="I9" t="n">
-        <v>3.7934</v>
+        <v>5.0555</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7934</v>
+        <v>5.0555</v>
       </c>
       <c r="N9" t="n">
         <v>440</v>
@@ -860,47 +860,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>Forester</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.8151</v>
+        <v>3.0405</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5504</v>
+        <v>0.5944</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6776</v>
+        <v>0.7346</v>
       </c>
       <c r="E10" t="n">
-        <v>2.8151</v>
+        <v>3.0405</v>
       </c>
       <c r="F10" t="n">
-        <v>2.8151</v>
+        <v>3.0405</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8151</v>
+        <v>3.3168</v>
       </c>
       <c r="I10" t="n">
-        <v>2.9356</v>
+        <v>4.767</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>292</v>
+        <v>440</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9356</v>
+        <v>4.767</v>
       </c>
       <c r="N10" t="n">
-        <v>292</v>
+        <v>440</v>
       </c>
     </row>
     <row r="11">
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.1012</v>
+        <v>2.3976</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4108</v>
+        <v>0.4687</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3932</v>
+        <v>0.4444</v>
       </c>
       <c r="E11" t="n">
-        <v>2.1012</v>
+        <v>2.3976</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1012</v>
+        <v>2.3976</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.1012</v>
+        <v>2.3976</v>
       </c>
       <c r="I11" t="n">
-        <v>2.1728</v>
+        <v>2.817</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.1728</v>
+        <v>2.817</v>
       </c>
       <c r="N11" t="n">
         <v>264</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>El1an</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.9119</v>
+        <v>2.2631</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3738</v>
+        <v>0.4424</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3178</v>
+        <v>0.3837</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9119</v>
+        <v>2.2631</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9119</v>
+        <v>2.2631</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.9119</v>
+        <v>2.2631</v>
       </c>
       <c r="I12" t="n">
-        <v>2.0617</v>
+        <v>2.3562</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>440</v>
+        <v>154</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.0617</v>
+        <v>2.3562</v>
       </c>
       <c r="N12" t="n">
-        <v>440</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>k1to</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.839</v>
+        <v>2.146</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3595</v>
+        <v>0.4195</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2887</v>
+        <v>0.3308</v>
       </c>
       <c r="E13" t="n">
-        <v>1.839</v>
+        <v>2.146</v>
       </c>
       <c r="F13" t="n">
-        <v>1.839</v>
+        <v>2.146</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.839</v>
+        <v>2.146</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8545</v>
+        <v>2.6251</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>154</v>
+        <v>292</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.8545</v>
+        <v>2.6251</v>
       </c>
       <c r="N13" t="n">
-        <v>154</v>
+        <v>292</v>
       </c>
     </row>
     <row r="14">
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.5454</v>
+        <v>1.749</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3021</v>
+        <v>0.3419</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1718</v>
+        <v>0.1516</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5454</v>
+        <v>1.749</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5454</v>
+        <v>1.749</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5454</v>
+        <v>1.749</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6115</v>
+        <v>2.1395</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.6115</v>
+        <v>2.1395</v>
       </c>
       <c r="N14" t="n">
         <v>266</v>
@@ -1090,308 +1090,308 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>k1to</t>
+          <t>El1an</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.5315</v>
+        <v>1.6626</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2994</v>
+        <v>0.325</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1662</v>
+        <v>0.1126</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5315</v>
+        <v>1.6626</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5315</v>
+        <v>1.6626</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5315</v>
+        <v>1.6626</v>
       </c>
       <c r="I15" t="n">
-        <v>1.597</v>
+        <v>2.3895</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>292</v>
+        <v>440</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.597</v>
+        <v>2.3895</v>
       </c>
       <c r="N15" t="n">
-        <v>292</v>
+        <v>440</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>nafany</t>
+          <t>faveN</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8302</v>
+        <v>1.5414</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1623</v>
+        <v>0.3013</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1132</v>
+        <v>0.0579</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8302</v>
+        <v>1.5414</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8302</v>
+        <v>1.5414</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8302</v>
+        <v>1.5414</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8878</v>
+        <v>1.8855</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>257</v>
+        <v>292</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8878</v>
+        <v>1.8855</v>
       </c>
       <c r="N16" t="n">
-        <v>257</v>
+        <v>292</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>faveN</t>
+          <t>nafany</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7516</v>
+        <v>1.0479</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1469</v>
+        <v>0.2049</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1445</v>
+        <v>-0.1649</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7516</v>
+        <v>1.0479</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7516</v>
+        <v>1.0479</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7516</v>
+        <v>1.0479</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7838000000000001</v>
+        <v>1.4466</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>292</v>
+        <v>257</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7838000000000001</v>
+        <v>1.4466</v>
       </c>
       <c r="N17" t="n">
-        <v>292</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>interz</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6921</v>
+        <v>0.9324</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1353</v>
+        <v>0.1823</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1682</v>
+        <v>-0.2171</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6921</v>
+        <v>0.9324</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6921</v>
+        <v>0.9324</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6921</v>
+        <v>0.9324</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7157</v>
+        <v>1.2871</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7157</v>
+        <v>1.2871</v>
       </c>
       <c r="N18" t="n">
-        <v>264</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>interz</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6632</v>
+        <v>0.9256</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1297</v>
+        <v>0.181</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1797</v>
+        <v>-0.2202</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6632</v>
+        <v>0.9256</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6632</v>
+        <v>0.9256</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6632</v>
+        <v>0.9256</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7092000000000001</v>
+        <v>1.0875</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7092000000000001</v>
+        <v>1.0875</v>
       </c>
       <c r="N19" t="n">
-        <v>257</v>
+        <v>264</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>smooya</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6067</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1186</v>
+        <v>0.1475</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2022</v>
+        <v>-0.2974</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6067</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6067</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6067</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.617</v>
+        <v>0.8865</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>169</v>
+        <v>264</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.617</v>
+        <v>0.8865</v>
       </c>
       <c r="N20" t="n">
-        <v>169</v>
+        <v>264</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>smooya</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5443</v>
+        <v>0.5894</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1064</v>
+        <v>0.1152</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2271</v>
+        <v>-0.3719</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5443</v>
+        <v>0.5894</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5443</v>
+        <v>0.5894</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5443</v>
+        <v>0.5894</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5535</v>
+        <v>0.6389</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5535</v>
+        <v>0.6389</v>
       </c>
       <c r="N21" t="n">
         <v>169</v>
@@ -1412,231 +1412,231 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2704</v>
+        <v>0.5534</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0529</v>
+        <v>0.1082</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3362</v>
+        <v>-0.3882</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2704</v>
+        <v>0.5534</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2704</v>
+        <v>0.5534</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2704</v>
+        <v>0.5534</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2796</v>
+        <v>0.5999</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>264</v>
+        <v>169</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2796</v>
+        <v>0.5999</v>
       </c>
       <c r="N22" t="n">
-        <v>264</v>
+        <v>169</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>xsepower</t>
+          <t>birdfromsky</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2694</v>
+        <v>0.5409</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0527</v>
+        <v>0.1057</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3366</v>
+        <v>-0.3938</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2694</v>
+        <v>0.5409</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2694</v>
+        <v>0.5409</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2694</v>
+        <v>0.5409</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2763</v>
+        <v>0.6616</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>222</v>
+        <v>266</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2763</v>
+        <v>0.6616</v>
       </c>
       <c r="N23" t="n">
-        <v>222</v>
+        <v>266</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>birdfromsky</t>
+          <t>xsepower</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2556</v>
+        <v>0.4237</v>
       </c>
       <c r="C24" t="n">
-        <v>0.05</v>
+        <v>0.0828</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3421</v>
+        <v>-0.4467</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2556</v>
+        <v>0.4237</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2556</v>
+        <v>0.4237</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2556</v>
+        <v>0.4237</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2665</v>
+        <v>0.4781</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>266</v>
+        <v>222</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2665</v>
+        <v>0.4781</v>
       </c>
       <c r="N24" t="n">
-        <v>266</v>
+        <v>222</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1393</v>
+        <v>0.3766</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0272</v>
+        <v>0.0736</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3884</v>
+        <v>-0.468</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1393</v>
+        <v>0.3766</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1393</v>
+        <v>0.3766</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1393</v>
+        <v>0.3766</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1405</v>
+        <v>0.4607</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>154</v>
+        <v>292</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1405</v>
+        <v>0.4607</v>
       </c>
       <c r="N25" t="n">
-        <v>154</v>
+        <v>292</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1082</v>
+        <v>0.2619</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0212</v>
+        <v>0.0512</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.487</v>
+        <v>-0.5198</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1082</v>
+        <v>0.2619</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1082</v>
+        <v>0.2619</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1082</v>
+        <v>0.2619</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1128</v>
+        <v>0.2727</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>292</v>
+        <v>154</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1128</v>
+        <v>0.2727</v>
       </c>
       <c r="N26" t="n">
-        <v>292</v>
+        <v>154</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.451</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0882</v>
+        <v>0.0178</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6236</v>
+        <v>-0.597</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.451</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.451</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.451</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.4703</v>
+        <v>0.1112</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.4703</v>
+        <v>0.1112</v>
       </c>
       <c r="N27" t="n">
         <v>266</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.4628</v>
+        <v>-0.0192</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0905</v>
+        <v>-0.0038</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6283</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.4628</v>
+        <v>-0.0192</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.4628</v>
+        <v>-0.0192</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.4628</v>
+        <v>-0.0192</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.4706</v>
+        <v>-0.0208</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.4706</v>
+        <v>-0.0208</v>
       </c>
       <c r="N28" t="n">
         <v>169</v>
@@ -1734,78 +1734,78 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.4632</v>
+        <v>-0.0451</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0906</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6284</v>
+        <v>-0.6584</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.4632</v>
+        <v>-0.0451</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.4632</v>
+        <v>-0.0451</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.4632</v>
+        <v>-0.0451</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.475</v>
+        <v>-0.053</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>222</v>
+        <v>264</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.475</v>
+        <v>-0.053</v>
       </c>
       <c r="N29" t="n">
-        <v>222</v>
+        <v>264</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>junior</t>
+          <t>FaNg</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4984</v>
+        <v>-0.0839</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0974</v>
+        <v>-0.0164</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6425</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4984</v>
+        <v>-0.0839</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.4984</v>
+        <v>-0.0839</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.4984</v>
+        <v>-0.0839</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.5026</v>
+        <v>-0.0873</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.5026</v>
+        <v>-0.0873</v>
       </c>
       <c r="N30" t="n">
         <v>154</v>
@@ -1826,461 +1826,461 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>NickelBack</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.6669</v>
+        <v>-0.1647</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1304</v>
+        <v>-0.0322</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7096</v>
+        <v>-0.7124</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.6669</v>
+        <v>-0.1647</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.6669</v>
+        <v>-0.1647</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.6669</v>
+        <v>-0.1647</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6896</v>
+        <v>-0.2367</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>264</v>
+        <v>440</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.6896</v>
+        <v>-0.2367</v>
       </c>
       <c r="N31" t="n">
-        <v>264</v>
+        <v>440</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FaNg</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.7896</v>
+        <v>-0.2395</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1544</v>
+        <v>-0.0468</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7585</v>
+        <v>-0.7461</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.7896</v>
+        <v>-0.2395</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.7896</v>
+        <v>-0.2395</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.7896</v>
+        <v>-0.2395</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.7962</v>
+        <v>-0.2703</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>154</v>
+        <v>222</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.7962</v>
+        <v>-0.2703</v>
       </c>
       <c r="N32" t="n">
-        <v>154</v>
+        <v>222</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>junior</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.9191</v>
+        <v>-0.2591</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1797</v>
+        <v>-0.0507</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8101</v>
+        <v>-0.755</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.9191</v>
+        <v>-0.2591</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.9191</v>
+        <v>-0.2591</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.9191</v>
+        <v>-0.2591</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.9346</v>
+        <v>-0.2698</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.9346</v>
+        <v>-0.2698</v>
       </c>
       <c r="N33" t="n">
-        <v>169</v>
+        <v>154</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NickelBack</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.9668</v>
+        <v>-0.4551</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.189</v>
+        <v>-0.089</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8290999999999999</v>
+        <v>-0.8435</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.9668</v>
+        <v>-0.4551</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.9668</v>
+        <v>-0.4551</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.9668</v>
+        <v>-0.4551</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.0425</v>
+        <v>-0.4933</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>440</v>
+        <v>169</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.0425</v>
+        <v>-0.4933</v>
       </c>
       <c r="N34" t="n">
-        <v>440</v>
+        <v>169</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>Daffu</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.0871</v>
+        <v>-0.6528</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2125</v>
+        <v>-0.1276</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.877</v>
+        <v>-0.9327</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.0871</v>
+        <v>-0.6528</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.0871</v>
+        <v>-0.6528</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.0871</v>
+        <v>-0.6528</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.0962</v>
+        <v>-0.7986</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>154</v>
+        <v>266</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.0962</v>
+        <v>-0.7986</v>
       </c>
       <c r="N35" t="n">
-        <v>154</v>
+        <v>266</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Daffu</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.4163</v>
+        <v>-0.6651</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2769</v>
+        <v>-0.13</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0082</v>
+        <v>-0.9383</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.4163</v>
+        <v>-0.6651</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.4163</v>
+        <v>-0.6651</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.4163</v>
+        <v>-0.6651</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.4769</v>
+        <v>-0.6925</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>266</v>
+        <v>154</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.4769</v>
+        <v>-0.6925</v>
       </c>
       <c r="N36" t="n">
-        <v>266</v>
+        <v>154</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>Krad</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.4678</v>
+        <v>-0.7992</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.287</v>
+        <v>-0.1562</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0287</v>
+        <v>-0.9988</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.4678</v>
+        <v>-0.7992</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.4678</v>
+        <v>-0.7992</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.4678</v>
+        <v>-0.7992</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.5052</v>
+        <v>-1.1487</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>222</v>
+        <v>440</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.5052</v>
+        <v>-1.1487</v>
       </c>
       <c r="N37" t="n">
-        <v>222</v>
+        <v>440</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.532</v>
+        <v>-0.8964</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2995</v>
+        <v>-0.1752</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0543</v>
+        <v>-1.0427</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.532</v>
+        <v>-0.8964</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.532</v>
+        <v>-0.8964</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.532</v>
+        <v>-0.8964</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.5579</v>
+        <v>-1.0116</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>169</v>
+        <v>222</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.5579</v>
+        <v>-1.0116</v>
       </c>
       <c r="N38" t="n">
-        <v>169</v>
+        <v>222</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>X5G7V</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.9561</v>
+        <v>-1.1997</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3824</v>
+        <v>-0.2345</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2232</v>
+        <v>-1.1796</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.9561</v>
+        <v>-1.1997</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.9561</v>
+        <v>-1.1997</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.9561</v>
+        <v>-1.1997</v>
       </c>
       <c r="I39" t="n">
-        <v>-2.0059</v>
+        <v>-1.3004</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>222</v>
+        <v>169</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-2.0059</v>
+        <v>-1.3004</v>
       </c>
       <c r="N39" t="n">
-        <v>222</v>
+        <v>169</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Krad</t>
+          <t>X5G7V</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.9594</v>
+        <v>-1.2488</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3831</v>
+        <v>-0.2441</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2245</v>
+        <v>-1.2018</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.9594</v>
+        <v>-1.2488</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.9594</v>
+        <v>-1.2488</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.9594</v>
+        <v>-1.2488</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.1129</v>
+        <v>-1.4093</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>440</v>
+        <v>222</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.1129</v>
+        <v>-1.4093</v>
       </c>
       <c r="N40" t="n">
-        <v>440</v>
+        <v>222</v>
       </c>
     </row>
     <row r="41">
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.5462</v>
+        <v>-1.8109</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4978</v>
+        <v>-0.354</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4583</v>
+        <v>-1.4555</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.5462</v>
+        <v>-1.8109</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.5462</v>
+        <v>-1.8109</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.5462</v>
+        <v>-1.8109</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.611</v>
+        <v>-2.0437</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.611</v>
+        <v>-2.0437</v>
       </c>
       <c r="N41" t="n">
         <v>222</v>
@@ -2429,10 +2429,10 @@
         <v>1.61</v>
       </c>
       <c r="I2" t="n">
-        <v>1.448</v>
+        <v>1.2877</v>
       </c>
       <c r="J2" t="n">
-        <v>33.304</v>
+        <v>29.6171</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.33</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8745000000000001</v>
+        <v>0.8698</v>
       </c>
       <c r="J3" t="n">
-        <v>20.1135</v>
+        <v>20.0054</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.03</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0248</v>
+        <v>0.0905</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5704</v>
+        <v>2.0815</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1141</v>
+        <v>-0.0425</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.6243</v>
+        <v>-0.9775</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.91</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4408</v>
+        <v>-0.3682</v>
       </c>
       <c r="J6" t="n">
-        <v>-10.1384</v>
+        <v>-8.4686</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4316</v>
+        <v>0.4919</v>
       </c>
       <c r="J7" t="n">
-        <v>9.9268</v>
+        <v>11.3137</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.96</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0379</v>
+        <v>-0.0494</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8717</v>
+        <v>-1.1362</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.82</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3116</v>
+        <v>-0.203</v>
       </c>
       <c r="J9" t="n">
-        <v>-7.1668</v>
+        <v>-4.669</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5048</v>
+        <v>-0.3295</v>
       </c>
       <c r="J10" t="n">
-        <v>-11.6104</v>
+        <v>-7.5785</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.67</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5319</v>
+        <v>-0.3484</v>
       </c>
       <c r="J11" t="n">
-        <v>-12.2337</v>
+        <v>-8.013199999999999</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.26</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7492</v>
+        <v>0.7274</v>
       </c>
       <c r="J12" t="n">
-        <v>20.9776</v>
+        <v>20.3672</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.13</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4047</v>
+        <v>0.401</v>
       </c>
       <c r="J13" t="n">
-        <v>11.3316</v>
+        <v>11.228</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.08</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2293</v>
+        <v>0.2655</v>
       </c>
       <c r="J14" t="n">
-        <v>6.4204</v>
+        <v>7.434</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.08</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2293</v>
+        <v>0.2655</v>
       </c>
       <c r="J15" t="n">
-        <v>6.4204</v>
+        <v>7.434</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0848</v>
+        <v>-0.0255</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.3744</v>
+        <v>-0.714</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.07</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1921</v>
+        <v>0.1946</v>
       </c>
       <c r="J17" t="n">
-        <v>5.3788</v>
+        <v>5.4488</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.98</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0345</v>
+        <v>-0.0329</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.966</v>
+        <v>-0.9212</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1348</v>
+        <v>-0.0839</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.7744</v>
+        <v>-2.3492</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.91</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.194</v>
+        <v>-0.1183</v>
       </c>
       <c r="J20" t="n">
-        <v>-5.432</v>
+        <v>-3.3124</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.88</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.247</v>
+        <v>-0.1511</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.916</v>
+        <v>-4.2308</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.48</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7482</v>
+        <v>0.7128</v>
       </c>
       <c r="J22" t="n">
-        <v>21.6978</v>
+        <v>20.6712</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.05</v>
       </c>
       <c r="I23" t="n">
-        <v>0.145</v>
+        <v>0.1102</v>
       </c>
       <c r="J23" t="n">
-        <v>4.205</v>
+        <v>3.1958</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.93</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1658</v>
+        <v>-0.0978</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.8082</v>
+        <v>-2.8362</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.77</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4212</v>
+        <v>-0.2662</v>
       </c>
       <c r="J25" t="n">
-        <v>-12.2148</v>
+        <v>-7.7198</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.66</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5678</v>
+        <v>-0.3714</v>
       </c>
       <c r="J26" t="n">
-        <v>-16.4662</v>
+        <v>-10.7706</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.62</v>
       </c>
       <c r="I27" t="n">
-        <v>0.878</v>
+        <v>0.7942</v>
       </c>
       <c r="J27" t="n">
-        <v>25.462</v>
+        <v>23.0318</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.95</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.156</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>-4.524</v>
+        <v>-2.3809</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1749</v>
+        <v>-0.0944</v>
       </c>
       <c r="J29" t="n">
-        <v>-5.0721</v>
+        <v>-2.7376</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.91</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2281</v>
+        <v>-0.1296</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.6149</v>
+        <v>-3.7584</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.88</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2772</v>
+        <v>-0.1628</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.0388</v>
+        <v>-4.7212</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.37</v>
       </c>
       <c r="I32" t="n">
-        <v>1.0092</v>
+        <v>0.9868</v>
       </c>
       <c r="J32" t="n">
-        <v>29.2668</v>
+        <v>28.6172</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.29</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8309</v>
+        <v>0.8072</v>
       </c>
       <c r="J33" t="n">
-        <v>24.0961</v>
+        <v>23.4088</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.08</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2473</v>
+        <v>0.2693</v>
       </c>
       <c r="J34" t="n">
-        <v>7.1717</v>
+        <v>7.8097</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3185</v>
+        <v>-0.2537</v>
       </c>
       <c r="J35" t="n">
-        <v>-9.236499999999999</v>
+        <v>-7.3573</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.77</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7712</v>
+        <v>-0.7241</v>
       </c>
       <c r="J36" t="n">
-        <v>-22.3648</v>
+        <v>-20.9989</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.21</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4084</v>
+        <v>0.4673</v>
       </c>
       <c r="J37" t="n">
-        <v>11.8436</v>
+        <v>13.5517</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.08</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2046</v>
+        <v>0.2124</v>
       </c>
       <c r="J38" t="n">
-        <v>5.9334</v>
+        <v>6.1596</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.06</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1678</v>
+        <v>0.1687</v>
       </c>
       <c r="J39" t="n">
-        <v>4.8662</v>
+        <v>4.8923</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.92</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1814</v>
+        <v>-0.1085</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.2606</v>
+        <v>-3.1465</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.58</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6657</v>
+        <v>-0.4443</v>
       </c>
       <c r="J41" t="n">
-        <v>-19.3053</v>
+        <v>-12.8847</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.3</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9194</v>
+        <v>0.8873</v>
       </c>
       <c r="J42" t="n">
-        <v>27.582</v>
+        <v>26.619</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.13</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4983</v>
+        <v>0.4433</v>
       </c>
       <c r="J43" t="n">
-        <v>14.949</v>
+        <v>13.299</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.02</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1397</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="J44" t="n">
-        <v>4.191</v>
+        <v>2.988</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.84</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5531</v>
+        <v>-0.5081</v>
       </c>
       <c r="J45" t="n">
-        <v>-16.593</v>
+        <v>-15.243</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.59</v>
       </c>
       <c r="I46" t="n">
-        <v>-1.1387</v>
+        <v>-1.1327</v>
       </c>
       <c r="J46" t="n">
-        <v>-34.161</v>
+        <v>-33.981</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.39</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6097</v>
+        <v>0.7419</v>
       </c>
       <c r="J47" t="n">
-        <v>18.291</v>
+        <v>22.257</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.27</v>
       </c>
       <c r="I48" t="n">
-        <v>0.456</v>
+        <v>0.5405</v>
       </c>
       <c r="J48" t="n">
-        <v>13.68</v>
+        <v>16.215</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.14</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2655</v>
+        <v>0.308</v>
       </c>
       <c r="J49" t="n">
-        <v>7.965</v>
+        <v>9.24</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.08</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1571</v>
+        <v>0.1916</v>
       </c>
       <c r="J50" t="n">
-        <v>4.713</v>
+        <v>5.748</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.49</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.7827</v>
+        <v>-0.5345</v>
       </c>
       <c r="J51" t="n">
-        <v>-23.481</v>
+        <v>-16.035</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.65</v>
       </c>
       <c r="I52" t="n">
-        <v>1.4305</v>
+        <v>1.288</v>
       </c>
       <c r="J52" t="n">
-        <v>30.0405</v>
+        <v>27.048</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.58</v>
       </c>
       <c r="I53" t="n">
-        <v>1.2967</v>
+        <v>1.2043</v>
       </c>
       <c r="J53" t="n">
-        <v>27.2307</v>
+        <v>25.2903</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.51</v>
       </c>
       <c r="I54" t="n">
-        <v>1.1569</v>
+        <v>1.1196</v>
       </c>
       <c r="J54" t="n">
-        <v>24.2949</v>
+        <v>23.5116</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.14</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2759</v>
+        <v>0.3716</v>
       </c>
       <c r="J55" t="n">
-        <v>5.7939</v>
+        <v>7.8036</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.176</v>
+        <v>-0.0898</v>
       </c>
       <c r="J56" t="n">
-        <v>-3.696</v>
+        <v>-1.8858</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.26</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5617</v>
+        <v>0.6792</v>
       </c>
       <c r="J57" t="n">
-        <v>11.7957</v>
+        <v>14.2632</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.75</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.3667</v>
+        <v>-0.2578</v>
       </c>
       <c r="J58" t="n">
-        <v>-7.7007</v>
+        <v>-5.4138</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.67</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.4969</v>
+        <v>-0.3325</v>
       </c>
       <c r="J59" t="n">
-        <v>-10.4349</v>
+        <v>-6.9825</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.66</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5115</v>
+        <v>-0.3419</v>
       </c>
       <c r="J60" t="n">
-        <v>-10.7415</v>
+        <v>-7.1799</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.44</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.7995</v>
+        <v>-0.5468</v>
       </c>
       <c r="J61" t="n">
-        <v>-16.7895</v>
+        <v>-11.4828</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.3</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8068</v>
       </c>
       <c r="J62" t="n">
-        <v>21.242</v>
+        <v>20.9768</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.25</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6978</v>
+        <v>0.6887</v>
       </c>
       <c r="J63" t="n">
-        <v>18.1428</v>
+        <v>17.9062</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.24</v>
       </c>
       <c r="I64" t="n">
-        <v>0.673</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="J64" t="n">
-        <v>17.498</v>
+        <v>17.2848</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.18</v>
       </c>
       <c r="I65" t="n">
-        <v>0.5139</v>
+        <v>0.5189</v>
       </c>
       <c r="J65" t="n">
-        <v>13.3614</v>
+        <v>13.4914</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6946</v>
+        <v>-0.6384</v>
       </c>
       <c r="J66" t="n">
-        <v>-18.0596</v>
+        <v>-16.5984</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.17</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3691</v>
+        <v>0.4115</v>
       </c>
       <c r="J67" t="n">
-        <v>9.5966</v>
+        <v>10.699</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1037</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="J68" t="n">
-        <v>-2.6962</v>
+        <v>-2.1112</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.86</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2662</v>
+        <v>-0.168</v>
       </c>
       <c r="J69" t="n">
-        <v>-6.9212</v>
+        <v>-4.368</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.82</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3309</v>
+        <v>-0.209</v>
       </c>
       <c r="J70" t="n">
-        <v>-8.603400000000001</v>
+        <v>-5.434</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.8</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3616</v>
+        <v>-0.2291</v>
       </c>
       <c r="J71" t="n">
-        <v>-9.4016</v>
+        <v>-5.9566</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.22</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4397</v>
+        <v>0.5049</v>
       </c>
       <c r="J72" t="n">
-        <v>11.8719</v>
+        <v>13.6323</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.16</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3527</v>
+        <v>0.3905</v>
       </c>
       <c r="J73" t="n">
-        <v>9.5229</v>
+        <v>10.5435</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.88</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2333</v>
+        <v>-0.1474</v>
       </c>
       <c r="J74" t="n">
-        <v>-6.2991</v>
+        <v>-3.9798</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.77</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4071</v>
+        <v>-0.2593</v>
       </c>
       <c r="J75" t="n">
-        <v>-10.9917</v>
+        <v>-7.0011</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.58</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6582</v>
+        <v>-0.439</v>
       </c>
       <c r="J76" t="n">
-        <v>-17.7714</v>
+        <v>-11.853</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.24</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6817</v>
+        <v>0.6688</v>
       </c>
       <c r="J77" t="n">
-        <v>18.4059</v>
+        <v>18.0576</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.19</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5525</v>
+        <v>0.5466</v>
       </c>
       <c r="J78" t="n">
-        <v>14.9175</v>
+        <v>14.7582</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.16</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4673</v>
+        <v>0.4718</v>
       </c>
       <c r="J79" t="n">
-        <v>12.6171</v>
+        <v>12.7386</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.08</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2076</v>
+        <v>0.2585</v>
       </c>
       <c r="J80" t="n">
-        <v>5.6052</v>
+        <v>6.9795</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1.04</v>
       </c>
       <c r="I81" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.1337</v>
       </c>
       <c r="J81" t="n">
-        <v>2.0601</v>
+        <v>3.6099</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.55</v>
       </c>
       <c r="I82" t="n">
-        <v>0.7135</v>
+        <v>0.6475</v>
       </c>
       <c r="J82" t="n">
-        <v>15.697</v>
+        <v>14.245</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.52</v>
       </c>
       <c r="I83" t="n">
-        <v>0.6788999999999999</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="J83" t="n">
-        <v>14.9358</v>
+        <v>13.5608</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.32</v>
       </c>
       <c r="I84" t="n">
-        <v>0.4097</v>
+        <v>0.4056</v>
       </c>
       <c r="J84" t="n">
-        <v>9.013400000000001</v>
+        <v>8.9232</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.29</v>
       </c>
       <c r="I85" t="n">
-        <v>0.3688</v>
+        <v>0.3719</v>
       </c>
       <c r="J85" t="n">
-        <v>8.1136</v>
+        <v>8.181800000000001</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.16</v>
       </c>
       <c r="I86" t="n">
-        <v>0.1892</v>
+        <v>0.2142</v>
       </c>
       <c r="J86" t="n">
-        <v>4.1624</v>
+        <v>4.7124</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.13</v>
       </c>
       <c r="I87" t="n">
-        <v>0.346</v>
+        <v>0.2877</v>
       </c>
       <c r="J87" t="n">
-        <v>7.612</v>
+        <v>6.3294</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.302</v>
+        <v>-0.2077</v>
       </c>
       <c r="J88" t="n">
-        <v>-6.644</v>
+        <v>-4.5694</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.78</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3548</v>
+        <v>-0.2366</v>
       </c>
       <c r="J89" t="n">
-        <v>-7.8056</v>
+        <v>-5.2052</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.71</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4622</v>
+        <v>-0.3038</v>
       </c>
       <c r="J90" t="n">
-        <v>-10.1684</v>
+        <v>-6.6836</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.67</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5188</v>
+        <v>-0.3418</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.4136</v>
+        <v>-7.5196</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.17</v>
       </c>
       <c r="I92" t="n">
-        <v>0.336</v>
+        <v>0.38</v>
       </c>
       <c r="J92" t="n">
-        <v>12.096</v>
+        <v>13.68</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.07</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1701</v>
+        <v>0.1814</v>
       </c>
       <c r="J93" t="n">
-        <v>6.1236</v>
+        <v>6.5304</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.05</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1308</v>
+        <v>0.1374</v>
       </c>
       <c r="J94" t="n">
-        <v>4.7088</v>
+        <v>4.9464</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.92</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1961</v>
+        <v>-0.1127</v>
       </c>
       <c r="J95" t="n">
-        <v>-7.0596</v>
+        <v>-4.0572</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.84</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3269</v>
+        <v>-0.1995</v>
       </c>
       <c r="J96" t="n">
-        <v>-11.7684</v>
+        <v>-7.182</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.77</v>
       </c>
       <c r="I97" t="n">
-        <v>1.7608</v>
+        <v>1.501</v>
       </c>
       <c r="J97" t="n">
-        <v>63.3888</v>
+        <v>54.036</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.24</v>
       </c>
       <c r="I98" t="n">
-        <v>0.6841</v>
+        <v>0.67</v>
       </c>
       <c r="J98" t="n">
-        <v>24.6276</v>
+        <v>24.12</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.07</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1783</v>
+        <v>0.2298</v>
       </c>
       <c r="J99" t="n">
-        <v>6.4188</v>
+        <v>8.2728</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.9</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4563</v>
+        <v>-0.3875</v>
       </c>
       <c r="J100" t="n">
-        <v>-16.4268</v>
+        <v>-13.95</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.71</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.9202</v>
+        <v>-0.8859</v>
       </c>
       <c r="J101" t="n">
-        <v>-33.1272</v>
+        <v>-31.8924</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.46</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6836</v>
+        <v>0.6008</v>
       </c>
       <c r="J102" t="n">
-        <v>19.8244</v>
+        <v>17.4232</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.32</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5117</v>
+        <v>0.4386</v>
       </c>
       <c r="J103" t="n">
-        <v>14.8393</v>
+        <v>12.7194</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.07</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1145</v>
+        <v>0.1192</v>
       </c>
       <c r="J104" t="n">
-        <v>3.3205</v>
+        <v>3.4568</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.96</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.149</v>
+        <v>-0.0741</v>
       </c>
       <c r="J105" t="n">
-        <v>-4.321</v>
+        <v>-2.1489</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.72</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5116000000000001</v>
+        <v>-0.3284</v>
       </c>
       <c r="J106" t="n">
-        <v>-14.8364</v>
+        <v>-9.5236</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.3</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5149</v>
+        <v>0.4676</v>
       </c>
       <c r="J107" t="n">
-        <v>14.9321</v>
+        <v>13.5604</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.25</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4482</v>
+        <v>0.4007</v>
       </c>
       <c r="J108" t="n">
-        <v>12.9978</v>
+        <v>11.6203</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.013</v>
+        <v>-0.001</v>
       </c>
       <c r="J109" t="n">
-        <v>-0.377</v>
+        <v>-0.029</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.88</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2659</v>
+        <v>-0.1579</v>
       </c>
       <c r="J110" t="n">
-        <v>-7.7111</v>
+        <v>-4.5791</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.65</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5867</v>
+        <v>-0.3849</v>
       </c>
       <c r="J111" t="n">
-        <v>-17.0143</v>
+        <v>-11.1621</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1</v>
       </c>
       <c r="I112" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.039</v>
       </c>
       <c r="J112" t="n">
-        <v>1.8312</v>
+        <v>0.9360000000000001</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.91</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1239</v>
+        <v>-0.107</v>
       </c>
       <c r="J113" t="n">
-        <v>-2.9736</v>
+        <v>-2.568</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.88</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1788</v>
+        <v>-0.1402</v>
       </c>
       <c r="J114" t="n">
-        <v>-4.2912</v>
+        <v>-3.3648</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.75</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4118</v>
+        <v>-0.2687</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.8832</v>
+        <v>-6.4488</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.68</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5119</v>
+        <v>-0.3357</v>
       </c>
       <c r="J116" t="n">
-        <v>-12.2856</v>
+        <v>-8.056800000000001</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.64</v>
       </c>
       <c r="I117" t="n">
-        <v>1.4358</v>
+        <v>1.2872</v>
       </c>
       <c r="J117" t="n">
-        <v>34.4592</v>
+        <v>30.8928</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.38</v>
       </c>
       <c r="I118" t="n">
-        <v>0.9053</v>
+        <v>0.9398</v>
       </c>
       <c r="J118" t="n">
-        <v>21.7272</v>
+        <v>22.5552</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.33</v>
       </c>
       <c r="I119" t="n">
-        <v>0.7822</v>
+        <v>0.8345</v>
       </c>
       <c r="J119" t="n">
-        <v>18.7728</v>
+        <v>20.028</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.31</v>
       </c>
       <c r="I120" t="n">
-        <v>0.7199</v>
+        <v>0.792</v>
       </c>
       <c r="J120" t="n">
-        <v>17.2776</v>
+        <v>19.008</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.95</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3635</v>
+        <v>-0.2795</v>
       </c>
       <c r="J121" t="n">
-        <v>-8.724</v>
+        <v>-6.708</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.09</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2429</v>
+        <v>0.2503</v>
       </c>
       <c r="J122" t="n">
-        <v>7.0441</v>
+        <v>7.2587</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.02</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1064</v>
+        <v>0.0849</v>
       </c>
       <c r="J123" t="n">
-        <v>3.0856</v>
+        <v>2.4621</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.01</v>
       </c>
       <c r="I124" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.0555</v>
       </c>
       <c r="J124" t="n">
-        <v>2.3519</v>
+        <v>1.6095</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.98</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.0147</v>
+        <v>-0.0283</v>
       </c>
       <c r="J125" t="n">
-        <v>-0.4263</v>
+        <v>-0.8207</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.48</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.7766999999999999</v>
+        <v>-0.5292</v>
       </c>
       <c r="J126" t="n">
-        <v>-22.5243</v>
+        <v>-15.3468</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.94</v>
       </c>
       <c r="I127" t="n">
-        <v>1.9746</v>
+        <v>1.6762</v>
       </c>
       <c r="J127" t="n">
-        <v>57.2634</v>
+        <v>48.6098</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.36</v>
       </c>
       <c r="I128" t="n">
-        <v>0.9179</v>
+        <v>0.923</v>
       </c>
       <c r="J128" t="n">
-        <v>26.6191</v>
+        <v>26.767</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.05</v>
       </c>
       <c r="I129" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.1474</v>
       </c>
       <c r="J129" t="n">
-        <v>2.1837</v>
+        <v>4.2746</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.01</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.0721</v>
+        <v>0.0013</v>
       </c>
       <c r="J130" t="n">
-        <v>-2.0909</v>
+        <v>0.0377</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.74</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.8719</v>
+        <v>-0.8310999999999999</v>
       </c>
       <c r="J131" t="n">
-        <v>-25.2851</v>
+        <v>-24.1019</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.31</v>
       </c>
       <c r="I132" t="n">
-        <v>0.8423</v>
+        <v>0.8315</v>
       </c>
       <c r="J132" t="n">
-        <v>25.269</v>
+        <v>24.945</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.28</v>
       </c>
       <c r="I133" t="n">
-        <v>0.7725</v>
+        <v>0.7611</v>
       </c>
       <c r="J133" t="n">
-        <v>23.175</v>
+        <v>22.833</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.25</v>
       </c>
       <c r="I134" t="n">
-        <v>0.7003</v>
+        <v>0.6899</v>
       </c>
       <c r="J134" t="n">
-        <v>21.009</v>
+        <v>20.697</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.99</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1632</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="J135" t="n">
-        <v>-4.896</v>
+        <v>-2.739</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.93</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3741</v>
+        <v>-0.3016</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.223</v>
+        <v>-9.048</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.24</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4573</v>
+        <v>0.5301</v>
       </c>
       <c r="J137" t="n">
-        <v>13.719</v>
+        <v>15.903</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.02</v>
       </c>
       <c r="I138" t="n">
-        <v>0.092</v>
+        <v>0.076</v>
       </c>
       <c r="J138" t="n">
-        <v>2.76</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.99</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.0047</v>
+        <v>-0.0166</v>
       </c>
       <c r="J139" t="n">
-        <v>-0.141</v>
+        <v>-0.498</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.92</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1723</v>
+        <v>-0.1065</v>
       </c>
       <c r="J140" t="n">
-        <v>-5.169</v>
+        <v>-3.195</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.58</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.6627</v>
+        <v>-0.4422</v>
       </c>
       <c r="J141" t="n">
-        <v>-19.881</v>
+        <v>-13.266</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.84</v>
       </c>
       <c r="I142" t="n">
-        <v>1.8384</v>
+        <v>1.5538</v>
       </c>
       <c r="J142" t="n">
-        <v>40.4448</v>
+        <v>34.1836</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.2</v>
       </c>
       <c r="I143" t="n">
-        <v>0.4974</v>
+        <v>0.5561</v>
       </c>
       <c r="J143" t="n">
-        <v>10.9428</v>
+        <v>12.2342</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.1</v>
       </c>
       <c r="I144" t="n">
-        <v>0.2231</v>
+        <v>0.2959</v>
       </c>
       <c r="J144" t="n">
-        <v>4.9082</v>
+        <v>6.5098</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.02</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0332</v>
+        <v>0.0404</v>
       </c>
       <c r="J145" t="n">
-        <v>-0.7304</v>
+        <v>0.8888</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.98</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2331</v>
+        <v>-0.1517</v>
       </c>
       <c r="J146" t="n">
-        <v>-5.1282</v>
+        <v>-3.3374</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.13</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3269</v>
+        <v>0.3528</v>
       </c>
       <c r="J147" t="n">
-        <v>7.1918</v>
+        <v>7.7616</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.97</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.0165</v>
+        <v>-0.0357</v>
       </c>
       <c r="J148" t="n">
-        <v>-0.363</v>
+        <v>-0.7854</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.9</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1549</v>
+        <v>-0.1214</v>
       </c>
       <c r="J149" t="n">
-        <v>-3.4078</v>
+        <v>-2.6708</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.5048</v>
+        <v>-0.3295</v>
       </c>
       <c r="J150" t="n">
-        <v>-11.1056</v>
+        <v>-7.249</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.65</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5585</v>
+        <v>-0.3673</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.287</v>
+        <v>-8.0806</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.88</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.0579</v>
+        <v>-0.0774</v>
       </c>
       <c r="J152" t="n">
-        <v>-1.2738</v>
+        <v>-1.7028</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.67</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.3895</v>
+        <v>-0.3093</v>
       </c>
       <c r="J153" t="n">
-        <v>-8.569000000000001</v>
+        <v>-6.8046</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.54</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.6204</v>
+        <v>-0.4279</v>
       </c>
       <c r="J154" t="n">
-        <v>-13.6488</v>
+        <v>-9.4138</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.46</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.7351</v>
+        <v>-0.5031</v>
       </c>
       <c r="J155" t="n">
-        <v>-16.1722</v>
+        <v>-11.0682</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.46</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.7351</v>
+        <v>-0.5031</v>
       </c>
       <c r="J156" t="n">
-        <v>-16.1722</v>
+        <v>-11.0682</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.77</v>
       </c>
       <c r="I157" t="n">
-        <v>1.6145</v>
+        <v>1.4121</v>
       </c>
       <c r="J157" t="n">
-        <v>35.519</v>
+        <v>31.0662</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.69</v>
       </c>
       <c r="I158" t="n">
-        <v>1.4687</v>
+        <v>1.3198</v>
       </c>
       <c r="J158" t="n">
-        <v>32.3114</v>
+        <v>29.0356</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.44</v>
       </c>
       <c r="I159" t="n">
-        <v>0.9388</v>
+        <v>1.0237</v>
       </c>
       <c r="J159" t="n">
-        <v>20.6536</v>
+        <v>22.5214</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.24</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4905</v>
+        <v>0.6046</v>
       </c>
       <c r="J160" t="n">
-        <v>10.791</v>
+        <v>13.3012</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.16</v>
       </c>
       <c r="I161" t="n">
-        <v>0.3013</v>
+        <v>0.4062</v>
       </c>
       <c r="J161" t="n">
-        <v>6.6286</v>
+        <v>8.936400000000001</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.26</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4405</v>
+        <v>0.3714</v>
       </c>
       <c r="J162" t="n">
-        <v>12.334</v>
+        <v>10.3992</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.11</v>
       </c>
       <c r="I163" t="n">
-        <v>0.2118</v>
+        <v>0.1779</v>
       </c>
       <c r="J163" t="n">
-        <v>5.9304</v>
+        <v>4.9812</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.1</v>
       </c>
       <c r="I164" t="n">
-        <v>0.1934</v>
+        <v>0.1641</v>
       </c>
       <c r="J164" t="n">
-        <v>5.4152</v>
+        <v>4.5948</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.02</v>
       </c>
       <c r="I165" t="n">
-        <v>0.0205</v>
+        <v>0.039</v>
       </c>
       <c r="J165" t="n">
-        <v>0.574</v>
+        <v>1.092</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.91</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2331</v>
+        <v>-0.1318</v>
       </c>
       <c r="J166" t="n">
-        <v>-6.5268</v>
+        <v>-3.6904</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.29</v>
       </c>
       <c r="I167" t="n">
-        <v>0.528</v>
+        <v>0.4779</v>
       </c>
       <c r="J167" t="n">
-        <v>14.784</v>
+        <v>13.3812</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.1</v>
       </c>
       <c r="I168" t="n">
-        <v>0.2508</v>
+        <v>0.2016</v>
       </c>
       <c r="J168" t="n">
-        <v>7.0224</v>
+        <v>5.6448</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.91</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1866</v>
+        <v>-0.1167</v>
       </c>
       <c r="J169" t="n">
-        <v>-5.2248</v>
+        <v>-3.2676</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.86</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2746</v>
+        <v>-0.1705</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.6888</v>
+        <v>-4.774</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.54</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.7094</v>
+        <v>-0.4775</v>
       </c>
       <c r="J171" t="n">
-        <v>-19.8632</v>
+        <v>-13.37</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>0.98</v>
       </c>
       <c r="I172" t="n">
-        <v>0.0757</v>
+        <v>0.032</v>
       </c>
       <c r="J172" t="n">
-        <v>1.514</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.96</v>
       </c>
       <c r="I173" t="n">
-        <v>0.0323</v>
+        <v>-0.0127</v>
       </c>
       <c r="J173" t="n">
-        <v>0.646</v>
+        <v>-0.254</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.66</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.4913</v>
+        <v>-0.3349</v>
       </c>
       <c r="J174" t="n">
-        <v>-9.826000000000001</v>
+        <v>-6.698</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.51</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.7017</v>
+        <v>-0.475</v>
       </c>
       <c r="J175" t="n">
-        <v>-14.034</v>
+        <v>-9.5</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.44</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.7905</v>
+        <v>-0.5403</v>
       </c>
       <c r="J176" t="n">
-        <v>-15.81</v>
+        <v>-10.806</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.72</v>
       </c>
       <c r="I177" t="n">
-        <v>1.5572</v>
+        <v>1.3696</v>
       </c>
       <c r="J177" t="n">
-        <v>31.144</v>
+        <v>27.392</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.42</v>
       </c>
       <c r="I178" t="n">
-        <v>0.9597</v>
+        <v>1.0014</v>
       </c>
       <c r="J178" t="n">
-        <v>19.194</v>
+        <v>20.028</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.33</v>
       </c>
       <c r="I179" t="n">
-        <v>0.7286</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="J179" t="n">
-        <v>14.572</v>
+        <v>16.522</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.26</v>
       </c>
       <c r="I180" t="n">
-        <v>0.5651</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="J180" t="n">
-        <v>11.302</v>
+        <v>13.356</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.18</v>
       </c>
       <c r="I181" t="n">
-        <v>0.3741</v>
+        <v>0.4739</v>
       </c>
       <c r="J181" t="n">
-        <v>7.482</v>
+        <v>9.478</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>0.98</v>
       </c>
       <c r="I182" t="n">
-        <v>0.1084</v>
+        <v>0.078</v>
       </c>
       <c r="J182" t="n">
-        <v>2.2764</v>
+        <v>1.638</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.63</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.4997</v>
+        <v>-0.3528</v>
       </c>
       <c r="J183" t="n">
-        <v>-10.4937</v>
+        <v>-7.4088</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.6</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.5501</v>
+        <v>-0.38</v>
       </c>
       <c r="J184" t="n">
-        <v>-11.5521</v>
+        <v>-7.98</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.58</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.581</v>
+        <v>-0.3984</v>
       </c>
       <c r="J185" t="n">
-        <v>-12.201</v>
+        <v>-8.366400000000001</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.43</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.7876</v>
+        <v>-0.5392</v>
       </c>
       <c r="J186" t="n">
-        <v>-16.5396</v>
+        <v>-11.3232</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.63</v>
       </c>
       <c r="I187" t="n">
-        <v>1.3706</v>
+        <v>1.2554</v>
       </c>
       <c r="J187" t="n">
-        <v>28.7826</v>
+        <v>26.3634</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.52</v>
       </c>
       <c r="I188" t="n">
-        <v>1.1524</v>
+        <v>1.1248</v>
       </c>
       <c r="J188" t="n">
-        <v>24.2004</v>
+        <v>23.6208</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.41</v>
       </c>
       <c r="I189" t="n">
-        <v>0.8914</v>
+        <v>0.9808</v>
       </c>
       <c r="J189" t="n">
-        <v>18.7194</v>
+        <v>20.5968</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.33</v>
       </c>
       <c r="I190" t="n">
-        <v>0.7066</v>
+        <v>0.8179</v>
       </c>
       <c r="J190" t="n">
-        <v>14.8386</v>
+        <v>17.1759</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.24</v>
       </c>
       <c r="I191" t="n">
-        <v>0.5018</v>
+        <v>0.6116</v>
       </c>
       <c r="J191" t="n">
-        <v>10.5378</v>
+        <v>12.8436</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.41</v>
       </c>
       <c r="I192" t="n">
-        <v>0.6654</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="J192" t="n">
-        <v>19.962</v>
+        <v>17.403</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.04</v>
       </c>
       <c r="I193" t="n">
-        <v>0.1245</v>
+        <v>0.0859</v>
       </c>
       <c r="J193" t="n">
-        <v>3.735</v>
+        <v>2.577</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.91</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.2028</v>
+        <v>-0.1207</v>
       </c>
       <c r="J194" t="n">
-        <v>-6.084</v>
+        <v>-3.621</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3637</v>
+        <v>-0.2264</v>
       </c>
       <c r="J195" t="n">
-        <v>-10.911</v>
+        <v>-6.792</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.72</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4897</v>
+        <v>-0.3147</v>
       </c>
       <c r="J196" t="n">
-        <v>-14.691</v>
+        <v>-9.441000000000001</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.28</v>
       </c>
       <c r="I197" t="n">
-        <v>0.4793</v>
+        <v>0.4338</v>
       </c>
       <c r="J197" t="n">
-        <v>14.379</v>
+        <v>13.014</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.19</v>
       </c>
       <c r="I198" t="n">
-        <v>0.3537</v>
+        <v>0.3118</v>
       </c>
       <c r="J198" t="n">
-        <v>10.611</v>
+        <v>9.353999999999999</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.1</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2102</v>
+        <v>0.181</v>
       </c>
       <c r="J199" t="n">
-        <v>6.306</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.89</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2572</v>
+        <v>-0.1502</v>
       </c>
       <c r="J200" t="n">
-        <v>-7.716</v>
+        <v>-4.506</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.76</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4486</v>
+        <v>-0.2835</v>
       </c>
       <c r="J201" t="n">
-        <v>-13.458</v>
+        <v>-8.505000000000001</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.01</v>
       </c>
       <c r="I202" t="n">
-        <v>0.1414</v>
+        <v>0.1103</v>
       </c>
       <c r="J202" t="n">
-        <v>3.1108</v>
+        <v>2.4266</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.92</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.0725</v>
+        <v>-0.0819</v>
       </c>
       <c r="J203" t="n">
-        <v>-1.595</v>
+        <v>-1.8018</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.84</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2108</v>
+        <v>-0.1721</v>
       </c>
       <c r="J204" t="n">
-        <v>-4.6376</v>
+        <v>-3.7862</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.6</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.6001</v>
+        <v>-0.4006</v>
       </c>
       <c r="J205" t="n">
-        <v>-13.2022</v>
+        <v>-8.8132</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.49</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.5028</v>
       </c>
       <c r="J206" t="n">
-        <v>-16.3108</v>
+        <v>-11.0616</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.77</v>
       </c>
       <c r="I207" t="n">
-        <v>1.6523</v>
+        <v>1.4309</v>
       </c>
       <c r="J207" t="n">
-        <v>36.3506</v>
+        <v>31.4798</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.68</v>
       </c>
       <c r="I208" t="n">
-        <v>1.4891</v>
+        <v>1.3248</v>
       </c>
       <c r="J208" t="n">
-        <v>32.7602</v>
+        <v>29.1456</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.67</v>
       </c>
       <c r="I209" t="n">
-        <v>1.4705</v>
+        <v>1.313</v>
       </c>
       <c r="J209" t="n">
-        <v>32.351</v>
+        <v>28.886</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.87</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.5965</v>
+        <v>-0.5265</v>
       </c>
       <c r="J210" t="n">
-        <v>-13.123</v>
+        <v>-11.583</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.86</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6216</v>
+        <v>-0.5538</v>
       </c>
       <c r="J211" t="n">
-        <v>-13.6752</v>
+        <v>-12.1836</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.94</v>
       </c>
       <c r="I212" t="n">
-        <v>1.8774</v>
+        <v>1.5902</v>
       </c>
       <c r="J212" t="n">
-        <v>33.7932</v>
+        <v>28.6236</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.75</v>
       </c>
       <c r="I213" t="n">
-        <v>1.5495</v>
+        <v>1.3774</v>
       </c>
       <c r="J213" t="n">
-        <v>27.891</v>
+        <v>24.7932</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.45</v>
       </c>
       <c r="I214" t="n">
-        <v>0.9222</v>
+        <v>1.0302</v>
       </c>
       <c r="J214" t="n">
-        <v>16.5996</v>
+        <v>18.5436</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.28</v>
       </c>
       <c r="I215" t="n">
-        <v>0.5588</v>
+        <v>0.6843</v>
       </c>
       <c r="J215" t="n">
-        <v>10.0584</v>
+        <v>12.3174</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.23</v>
       </c>
       <c r="I216" t="n">
-        <v>0.4473</v>
+        <v>0.5665</v>
       </c>
       <c r="J216" t="n">
-        <v>8.051399999999999</v>
+        <v>10.197</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.88</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.043</v>
+        <v>-0.0655</v>
       </c>
       <c r="J217" t="n">
-        <v>-0.774</v>
+        <v>-1.179</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.66</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.3888</v>
+        <v>-0.3127</v>
       </c>
       <c r="J218" t="n">
-        <v>-6.9984</v>
+        <v>-5.6286</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.62</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.4527</v>
+        <v>-0.3518</v>
       </c>
       <c r="J219" t="n">
-        <v>-8.1486</v>
+        <v>-6.3324</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.42</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.7806</v>
+        <v>-0.5362</v>
       </c>
       <c r="J220" t="n">
-        <v>-14.0508</v>
+        <v>-9.6516</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.3</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.9361</v>
+        <v>-0.6523</v>
       </c>
       <c r="J221" t="n">
-        <v>-16.8498</v>
+        <v>-11.7414</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.03</v>
       </c>
       <c r="I222" t="n">
-        <v>0.1396</v>
+        <v>0.0916</v>
       </c>
       <c r="J222" t="n">
-        <v>4.0484</v>
+        <v>2.6564</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.95</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.06859999999999999</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="J223" t="n">
-        <v>-1.9894</v>
+        <v>-1.9024</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.92</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1285</v>
+        <v>-0.1016</v>
       </c>
       <c r="J224" t="n">
-        <v>-3.7265</v>
+        <v>-2.9464</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.86</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2534</v>
+        <v>-0.165</v>
       </c>
       <c r="J225" t="n">
-        <v>-7.3486</v>
+        <v>-4.785</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5104</v>
+        <v>-0.3324</v>
       </c>
       <c r="J226" t="n">
-        <v>-14.8016</v>
+        <v>-9.6396</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.33</v>
       </c>
       <c r="I227" t="n">
-        <v>0.5164</v>
+        <v>0.4452</v>
       </c>
       <c r="J227" t="n">
-        <v>14.9756</v>
+        <v>12.9108</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.31</v>
       </c>
       <c r="I228" t="n">
-        <v>0.4904</v>
+        <v>0.4217</v>
       </c>
       <c r="J228" t="n">
-        <v>14.2216</v>
+        <v>12.2293</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.29</v>
       </c>
       <c r="I229" t="n">
-        <v>0.464</v>
+        <v>0.398</v>
       </c>
       <c r="J229" t="n">
-        <v>13.456</v>
+        <v>11.542</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.89</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.277</v>
+        <v>-0.1596</v>
       </c>
       <c r="J230" t="n">
-        <v>-8.032999999999999</v>
+        <v>-4.6284</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.84</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3526</v>
+        <v>-0.2127</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.2254</v>
+        <v>-6.1683</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.32</v>
       </c>
       <c r="I232" t="n">
-        <v>0.8981</v>
+        <v>0.8779</v>
       </c>
       <c r="J232" t="n">
-        <v>31.4335</v>
+        <v>30.7265</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.21</v>
       </c>
       <c r="I233" t="n">
-        <v>0.6371</v>
+        <v>0.6107</v>
       </c>
       <c r="J233" t="n">
-        <v>22.2985</v>
+        <v>21.3745</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.11</v>
       </c>
       <c r="I234" t="n">
-        <v>0.3578</v>
+        <v>0.3512</v>
       </c>
       <c r="J234" t="n">
-        <v>12.523</v>
+        <v>12.292</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.3193</v>
+        <v>-0.2542</v>
       </c>
       <c r="J235" t="n">
-        <v>-11.1755</v>
+        <v>-8.897</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.88</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.495</v>
+        <v>-0.4321</v>
       </c>
       <c r="J236" t="n">
-        <v>-17.325</v>
+        <v>-15.1235</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.07</v>
       </c>
       <c r="I237" t="n">
-        <v>0.1817</v>
+        <v>0.1878</v>
       </c>
       <c r="J237" t="n">
-        <v>6.3595</v>
+        <v>6.573</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.06</v>
       </c>
       <c r="I238" t="n">
-        <v>0.1629</v>
+        <v>0.1658</v>
       </c>
       <c r="J238" t="n">
-        <v>5.7015</v>
+        <v>5.803</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.05</v>
       </c>
       <c r="I239" t="n">
-        <v>0.1433</v>
+        <v>0.1431</v>
       </c>
       <c r="J239" t="n">
-        <v>5.0155</v>
+        <v>5.0085</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.91</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2043</v>
+        <v>-0.1211</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.1505</v>
+        <v>-4.2385</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.82</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3499</v>
+        <v>-0.2167</v>
       </c>
       <c r="J241" t="n">
-        <v>-12.2465</v>
+        <v>-7.5845</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.53</v>
       </c>
       <c r="I242" t="n">
-        <v>1.3733</v>
+        <v>1.236</v>
       </c>
       <c r="J242" t="n">
-        <v>57.6786</v>
+        <v>51.912</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.0318</v>
+        <v>-0.0047</v>
       </c>
       <c r="J243" t="n">
-        <v>-1.3356</v>
+        <v>-0.1974</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.95</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.2525</v>
+        <v>-0.2041</v>
       </c>
       <c r="J244" t="n">
-        <v>-10.605</v>
+        <v>-8.5722</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2862</v>
+        <v>-0.2361</v>
       </c>
       <c r="J245" t="n">
-        <v>-12.0204</v>
+        <v>-9.9162</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.71</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.8905999999999999</v>
+        <v>-0.8566</v>
       </c>
       <c r="J246" t="n">
-        <v>-37.4052</v>
+        <v>-35.9772</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.43</v>
       </c>
       <c r="I247" t="n">
-        <v>0.6586</v>
+        <v>0.8079</v>
       </c>
       <c r="J247" t="n">
-        <v>27.6612</v>
+        <v>33.9318</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.12</v>
       </c>
       <c r="I248" t="n">
-        <v>0.2329</v>
+        <v>0.2704</v>
       </c>
       <c r="J248" t="n">
-        <v>9.7818</v>
+        <v>11.3568</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.02</v>
       </c>
       <c r="I249" t="n">
-        <v>0.0235</v>
+        <v>0.0562</v>
       </c>
       <c r="J249" t="n">
-        <v>0.987</v>
+        <v>2.3604</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.01</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.002</v>
+        <v>0.0274</v>
       </c>
       <c r="J250" t="n">
-        <v>-0.08400000000000001</v>
+        <v>1.1508</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.78</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4265</v>
+        <v>-0.2669</v>
       </c>
       <c r="J251" t="n">
-        <v>-17.913</v>
+        <v>-11.2098</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.78</v>
       </c>
       <c r="I252" t="n">
-        <v>1.7623</v>
+        <v>1.5013</v>
       </c>
       <c r="J252" t="n">
-        <v>45.8198</v>
+        <v>39.0338</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.06</v>
       </c>
       <c r="I253" t="n">
-        <v>0.1293</v>
+        <v>0.1915</v>
       </c>
       <c r="J253" t="n">
-        <v>3.3618</v>
+        <v>4.979</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.04</v>
       </c>
       <c r="I254" t="n">
-        <v>0.0629</v>
+        <v>0.1267</v>
       </c>
       <c r="J254" t="n">
-        <v>1.6354</v>
+        <v>3.2942</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.02</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.0105</v>
+        <v>0.0549</v>
       </c>
       <c r="J255" t="n">
-        <v>-0.273</v>
+        <v>1.4274</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.95</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.3182</v>
+        <v>-0.2428</v>
       </c>
       <c r="J256" t="n">
-        <v>-8.273199999999999</v>
+        <v>-6.3128</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.27</v>
       </c>
       <c r="I257" t="n">
-        <v>0.4719</v>
+        <v>0.5555</v>
       </c>
       <c r="J257" t="n">
-        <v>12.2694</v>
+        <v>14.443</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.17</v>
       </c>
       <c r="I258" t="n">
-        <v>0.3303</v>
+        <v>0.3755</v>
       </c>
       <c r="J258" t="n">
-        <v>8.5878</v>
+        <v>9.763</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.09</v>
       </c>
       <c r="I259" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="J259" t="n">
-        <v>5.2</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.96</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.1248</v>
+        <v>-0.0658</v>
       </c>
       <c r="J260" t="n">
-        <v>-3.2448</v>
+        <v>-1.7108</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.64</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.6006</v>
+        <v>-0.3952</v>
       </c>
       <c r="J261" t="n">
-        <v>-15.6156</v>
+        <v>-10.2752</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.62</v>
       </c>
       <c r="I262" t="n">
-        <v>1.4436</v>
+        <v>1.2865</v>
       </c>
       <c r="J262" t="n">
-        <v>38.9772</v>
+        <v>34.7355</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.5</v>
       </c>
       <c r="I263" t="n">
-        <v>1.2104</v>
+        <v>1.1358</v>
       </c>
       <c r="J263" t="n">
-        <v>32.6808</v>
+        <v>30.6666</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.22</v>
       </c>
       <c r="I264" t="n">
-        <v>0.5592</v>
+        <v>0.6039</v>
       </c>
       <c r="J264" t="n">
-        <v>15.0984</v>
+        <v>16.3053</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.97</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.269</v>
+        <v>-0.188</v>
       </c>
       <c r="J265" t="n">
-        <v>-7.263</v>
+        <v>-5.076</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.7119</v>
+        <v>-0.6549</v>
       </c>
       <c r="J266" t="n">
-        <v>-19.2213</v>
+        <v>-17.6823</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.75</v>
       </c>
       <c r="I267" t="n">
-        <v>1.0352</v>
+        <v>1.2068</v>
       </c>
       <c r="J267" t="n">
-        <v>27.9504</v>
+        <v>32.5836</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.92</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1934</v>
+        <v>-0.1119</v>
       </c>
       <c r="J268" t="n">
-        <v>-5.2218</v>
+        <v>-3.0213</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.89</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2454</v>
+        <v>-0.1455</v>
       </c>
       <c r="J269" t="n">
-        <v>-6.6258</v>
+        <v>-3.9285</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3696</v>
+        <v>-0.2292</v>
       </c>
       <c r="J270" t="n">
-        <v>-9.979200000000001</v>
+        <v>-6.1884</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.64</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.597</v>
+        <v>-0.3926</v>
       </c>
       <c r="J271" t="n">
-        <v>-16.119</v>
+        <v>-10.6002</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.09</v>
       </c>
       <c r="I272" t="n">
-        <v>0.1923</v>
+        <v>0.1656</v>
       </c>
       <c r="J272" t="n">
-        <v>6.7305</v>
+        <v>5.796</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.06</v>
       </c>
       <c r="I273" t="n">
-        <v>0.134</v>
+        <v>0.1177</v>
       </c>
       <c r="J273" t="n">
-        <v>4.69</v>
+        <v>4.1195</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.06</v>
       </c>
       <c r="I274" t="n">
-        <v>0.134</v>
+        <v>0.1177</v>
       </c>
       <c r="J274" t="n">
-        <v>4.69</v>
+        <v>4.1195</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.05</v>
       </c>
       <c r="I275" t="n">
-        <v>0.1119</v>
+        <v>0.1011</v>
       </c>
       <c r="J275" t="n">
-        <v>3.9165</v>
+        <v>3.5385</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.96</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.1311</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="J276" t="n">
-        <v>-4.5885</v>
+        <v>-2.366</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.24</v>
       </c>
       <c r="I277" t="n">
-        <v>0.4143</v>
+        <v>0.3475</v>
       </c>
       <c r="J277" t="n">
-        <v>14.5005</v>
+        <v>12.1625</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.23</v>
       </c>
       <c r="I278" t="n">
-        <v>0.4003</v>
+        <v>0.335</v>
       </c>
       <c r="J278" t="n">
-        <v>14.0105</v>
+        <v>11.725</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.07</v>
       </c>
       <c r="I279" t="n">
-        <v>0.1302</v>
+        <v>0.122</v>
       </c>
       <c r="J279" t="n">
-        <v>4.557</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.0382</v>
+        <v>-0.0064</v>
       </c>
       <c r="J280" t="n">
-        <v>-1.337</v>
+        <v>-0.224</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.84</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3419</v>
+        <v>-0.2069</v>
       </c>
       <c r="J281" t="n">
-        <v>-11.9665</v>
+        <v>-7.2415</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.95</v>
       </c>
       <c r="I282" t="n">
-        <v>1.941</v>
+        <v>1.6386</v>
       </c>
       <c r="J282" t="n">
-        <v>46.584</v>
+        <v>39.3264</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.44</v>
       </c>
       <c r="I283" t="n">
-        <v>1.0108</v>
+        <v>1.0325</v>
       </c>
       <c r="J283" t="n">
-        <v>24.2592</v>
+        <v>24.78</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.41</v>
       </c>
       <c r="I284" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.9865</v>
       </c>
       <c r="J284" t="n">
-        <v>22.632</v>
+        <v>23.676</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.04</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.0062</v>
+        <v>0.0788</v>
       </c>
       <c r="J285" t="n">
-        <v>-0.1488</v>
+        <v>1.8912</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>1.02</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.0766</v>
+        <v>0.007</v>
       </c>
       <c r="J286" t="n">
-        <v>-1.8384</v>
+        <v>0.168</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.18</v>
       </c>
       <c r="I287" t="n">
-        <v>0.4564</v>
+        <v>0.5304</v>
       </c>
       <c r="J287" t="n">
-        <v>10.9536</v>
+        <v>12.7296</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.88</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.1277</v>
+        <v>-0.1218</v>
       </c>
       <c r="J288" t="n">
-        <v>-3.0648</v>
+        <v>-2.9232</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.8</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.2606</v>
+        <v>-0.2079</v>
       </c>
       <c r="J289" t="n">
-        <v>-6.2544</v>
+        <v>-4.9896</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.55</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.6575</v>
+        <v>-0.4424</v>
       </c>
       <c r="J290" t="n">
-        <v>-15.78</v>
+        <v>-10.6176</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.29</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.9729</v>
+        <v>-0.6828</v>
       </c>
       <c r="J291" t="n">
-        <v>-23.3496</v>
+        <v>-16.3872</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.21</v>
       </c>
       <c r="I292" t="n">
-        <v>0.43</v>
+        <v>0.4913</v>
       </c>
       <c r="J292" t="n">
-        <v>9.890000000000001</v>
+        <v>11.2999</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>0.96</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.0572</v>
+        <v>-0.0553</v>
       </c>
       <c r="J293" t="n">
-        <v>-1.3156</v>
+        <v>-1.2719</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.88</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.2275</v>
+        <v>-0.1462</v>
       </c>
       <c r="J294" t="n">
-        <v>-5.2325</v>
+        <v>-3.3626</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.88</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.2275</v>
+        <v>-0.1462</v>
       </c>
       <c r="J295" t="n">
-        <v>-5.2325</v>
+        <v>-3.3626</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.62</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.6062</v>
+        <v>-0.4007</v>
       </c>
       <c r="J296" t="n">
-        <v>-13.9426</v>
+        <v>-9.216100000000001</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.57</v>
       </c>
       <c r="I297" t="n">
-        <v>1.3481</v>
+        <v>1.2242</v>
       </c>
       <c r="J297" t="n">
-        <v>31.0063</v>
+        <v>28.1566</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.47</v>
       </c>
       <c r="I298" t="n">
-        <v>1.1497</v>
+        <v>1.0975</v>
       </c>
       <c r="J298" t="n">
-        <v>26.4431</v>
+        <v>25.2425</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.17</v>
       </c>
       <c r="I299" t="n">
-        <v>0.4182</v>
+        <v>0.483</v>
       </c>
       <c r="J299" t="n">
-        <v>9.618600000000001</v>
+        <v>11.109</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.98</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.2318</v>
+        <v>-0.1507</v>
       </c>
       <c r="J300" t="n">
-        <v>-5.3314</v>
+        <v>-3.4661</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.93</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3976</v>
+        <v>-0.3199</v>
       </c>
       <c r="J301" t="n">
-        <v>-9.1448</v>
+        <v>-7.3577</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.38</v>
       </c>
       <c r="I302" t="n">
-        <v>0.593</v>
+        <v>0.5131</v>
       </c>
       <c r="J302" t="n">
-        <v>21.348</v>
+        <v>18.4716</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.11</v>
       </c>
       <c r="I303" t="n">
-        <v>0.2078</v>
+        <v>0.177</v>
       </c>
       <c r="J303" t="n">
-        <v>7.4808</v>
+        <v>6.372</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.09</v>
       </c>
       <c r="I304" t="n">
-        <v>0.1678</v>
+        <v>0.1495</v>
       </c>
       <c r="J304" t="n">
-        <v>6.0408</v>
+        <v>5.382</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.08</v>
       </c>
       <c r="I305" t="n">
-        <v>0.1434</v>
+        <v>0.1356</v>
       </c>
       <c r="J305" t="n">
-        <v>5.1624</v>
+        <v>4.8816</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.78</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.4293</v>
+        <v>-0.2686</v>
       </c>
       <c r="J306" t="n">
-        <v>-15.4548</v>
+        <v>-9.669600000000001</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.21</v>
       </c>
       <c r="I307" t="n">
-        <v>0.4205</v>
+        <v>0.3676</v>
       </c>
       <c r="J307" t="n">
-        <v>15.138</v>
+        <v>13.2336</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.02</v>
       </c>
       <c r="I308" t="n">
-        <v>0.098</v>
+        <v>0.0608</v>
       </c>
       <c r="J308" t="n">
-        <v>3.528</v>
+        <v>2.1888</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.88</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.2393</v>
+        <v>-0.1489</v>
       </c>
       <c r="J309" t="n">
-        <v>-8.614800000000001</v>
+        <v>-5.3604</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.85</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.2895</v>
+        <v>-0.1805</v>
       </c>
       <c r="J310" t="n">
-        <v>-10.422</v>
+        <v>-6.498</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.72</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4806</v>
+        <v>-0.3096</v>
       </c>
       <c r="J311" t="n">
-        <v>-17.3016</v>
+        <v>-11.1456</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.12</v>
       </c>
       <c r="I312" t="n">
-        <v>0.2859</v>
+        <v>0.3065</v>
       </c>
       <c r="J312" t="n">
-        <v>8.0052</v>
+        <v>8.582000000000001</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.02</v>
       </c>
       <c r="I313" t="n">
-        <v>0.0989</v>
+        <v>0.08</v>
       </c>
       <c r="J313" t="n">
-        <v>2.7692</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>0.96</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.0696</v>
+        <v>-0.058</v>
       </c>
       <c r="J314" t="n">
-        <v>-1.9488</v>
+        <v>-1.624</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.88</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.2385</v>
+        <v>-0.1487</v>
       </c>
       <c r="J315" t="n">
-        <v>-6.678</v>
+        <v>-4.1636</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.5204</v>
+        <v>-0.338</v>
       </c>
       <c r="J316" t="n">
-        <v>-14.5712</v>
+        <v>-9.464</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.69</v>
       </c>
       <c r="I317" t="n">
-        <v>1.5882</v>
+        <v>1.3821</v>
       </c>
       <c r="J317" t="n">
-        <v>44.4696</v>
+        <v>38.6988</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.26</v>
       </c>
       <c r="I318" t="n">
-        <v>0.6989</v>
+        <v>0.7023</v>
       </c>
       <c r="J318" t="n">
-        <v>19.5692</v>
+        <v>19.6644</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.1</v>
       </c>
       <c r="I319" t="n">
-        <v>0.2392</v>
+        <v>0.3039</v>
       </c>
       <c r="J319" t="n">
-        <v>6.6976</v>
+        <v>8.5092</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>1.03</v>
       </c>
       <c r="I320" t="n">
-        <v>0.0173</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="J320" t="n">
-        <v>0.4844</v>
+        <v>2.408</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.89</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5017</v>
+        <v>-0.4307</v>
       </c>
       <c r="J321" t="n">
-        <v>-14.0476</v>
+        <v>-12.0596</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.27</v>
       </c>
       <c r="I322" t="n">
-        <v>0.4573</v>
+        <v>0.5417</v>
       </c>
       <c r="J322" t="n">
-        <v>18.7493</v>
+        <v>22.2097</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.11</v>
       </c>
       <c r="I323" t="n">
-        <v>0.2164</v>
+        <v>0.2515</v>
       </c>
       <c r="J323" t="n">
-        <v>8.872400000000001</v>
+        <v>10.3115</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.08</v>
       </c>
       <c r="I324" t="n">
-        <v>0.1598</v>
+        <v>0.1921</v>
       </c>
       <c r="J324" t="n">
-        <v>6.5518</v>
+        <v>7.8761</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>0.97</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.1184</v>
+        <v>-0.0569</v>
       </c>
       <c r="J325" t="n">
-        <v>-4.8544</v>
+        <v>-2.3329</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.92</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.2135</v>
+        <v>-0.1192</v>
       </c>
       <c r="J326" t="n">
-        <v>-8.753500000000001</v>
+        <v>-4.8872</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.35</v>
       </c>
       <c r="I327" t="n">
-        <v>1.0188</v>
+        <v>0.9883</v>
       </c>
       <c r="J327" t="n">
-        <v>41.7708</v>
+        <v>40.5203</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.07</v>
       </c>
       <c r="I328" t="n">
-        <v>0.3062</v>
+        <v>0.2612</v>
       </c>
       <c r="J328" t="n">
-        <v>12.5542</v>
+        <v>10.7092</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.93</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.3008</v>
+        <v>-0.2589</v>
       </c>
       <c r="J329" t="n">
-        <v>-12.3328</v>
+        <v>-10.6149</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.89</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.4238</v>
+        <v>-0.3763</v>
       </c>
       <c r="J330" t="n">
-        <v>-17.3758</v>
+        <v>-15.4283</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.74</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.8115</v>
+        <v>-0.7732</v>
       </c>
       <c r="J331" t="n">
-        <v>-33.2715</v>
+        <v>-31.7012</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.77</v>
       </c>
       <c r="I332" t="n">
-        <v>0.9581</v>
+        <v>0.8776</v>
       </c>
       <c r="J332" t="n">
-        <v>22.9944</v>
+        <v>21.0624</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.68</v>
       </c>
       <c r="I333" t="n">
-        <v>0.8643999999999999</v>
+        <v>0.7864</v>
       </c>
       <c r="J333" t="n">
-        <v>20.7456</v>
+        <v>18.8736</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.14</v>
       </c>
       <c r="I334" t="n">
-        <v>0.1662</v>
+        <v>0.1914</v>
       </c>
       <c r="J334" t="n">
-        <v>3.9888</v>
+        <v>4.5936</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>1.1</v>
       </c>
       <c r="I335" t="n">
-        <v>0.1049</v>
+        <v>0.1362</v>
       </c>
       <c r="J335" t="n">
-        <v>2.5176</v>
+        <v>3.2688</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.99</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.1284</v>
+        <v>-0.0523</v>
       </c>
       <c r="J336" t="n">
-        <v>-3.0816</v>
+        <v>-1.2552</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>0.9</v>
       </c>
       <c r="I337" t="n">
-        <v>-0.07920000000000001</v>
+        <v>-0.0906</v>
       </c>
       <c r="J337" t="n">
-        <v>-1.9008</v>
+        <v>-2.1744</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>0.86</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.1469</v>
+        <v>-0.1373</v>
       </c>
       <c r="J338" t="n">
-        <v>-3.5256</v>
+        <v>-3.2952</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>0.66</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.4913</v>
+        <v>-0.3349</v>
       </c>
       <c r="J339" t="n">
-        <v>-11.7912</v>
+        <v>-8.037599999999999</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.62</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.5514</v>
+        <v>-0.3722</v>
       </c>
       <c r="J340" t="n">
-        <v>-13.2336</v>
+        <v>-8.9328</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.51</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.7017</v>
+        <v>-0.475</v>
       </c>
       <c r="J341" t="n">
-        <v>-16.8408</v>
+        <v>-11.4</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.54</v>
       </c>
       <c r="I342" t="n">
-        <v>0.7915</v>
+        <v>0.9835</v>
       </c>
       <c r="J342" t="n">
-        <v>27.7025</v>
+        <v>34.4225</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.09</v>
       </c>
       <c r="I343" t="n">
-        <v>0.1877</v>
+        <v>0.2147</v>
       </c>
       <c r="J343" t="n">
-        <v>6.5695</v>
+        <v>7.5145</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.03</v>
       </c>
       <c r="I344" t="n">
-        <v>0.0547</v>
+        <v>0.0848</v>
       </c>
       <c r="J344" t="n">
-        <v>1.9145</v>
+        <v>2.968</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>0.95</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.1542</v>
+        <v>-0.0815</v>
       </c>
       <c r="J345" t="n">
-        <v>-5.397</v>
+        <v>-2.8525</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.66</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.5799</v>
+        <v>-0.3795</v>
       </c>
       <c r="J346" t="n">
-        <v>-20.2965</v>
+        <v>-13.2825</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>1.21</v>
       </c>
       <c r="I347" t="n">
-        <v>0.6828</v>
+        <v>0.6399</v>
       </c>
       <c r="J347" t="n">
-        <v>23.898</v>
+        <v>22.3965</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>1.11</v>
       </c>
       <c r="I348" t="n">
-        <v>0.4152</v>
+        <v>0.3719</v>
       </c>
       <c r="J348" t="n">
-        <v>14.532</v>
+        <v>13.0165</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>1.05</v>
       </c>
       <c r="I349" t="n">
-        <v>0.2226</v>
+        <v>0.1929</v>
       </c>
       <c r="J349" t="n">
-        <v>7.791</v>
+        <v>6.7515</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.98</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.132</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="J350" t="n">
-        <v>-4.62</v>
+        <v>-3.3985</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.73</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.8416</v>
+        <v>-0.8041</v>
       </c>
       <c r="J351" t="n">
-        <v>-29.456</v>
+        <v>-28.1435</v>
       </c>
     </row>
     <row r="352">
@@ -16429,10 +16429,10 @@
         <v>1.85</v>
       </c>
       <c r="I352" t="n">
-        <v>1.7667</v>
+        <v>1.5094</v>
       </c>
       <c r="J352" t="n">
-        <v>37.1007</v>
+        <v>31.6974</v>
       </c>
     </row>
     <row r="353">
@@ -16469,10 +16469,10 @@
         <v>1.72</v>
       </c>
       <c r="I353" t="n">
-        <v>1.5359</v>
+        <v>1.3596</v>
       </c>
       <c r="J353" t="n">
-        <v>32.2539</v>
+        <v>28.5516</v>
       </c>
     </row>
     <row r="354">
@@ -16509,10 +16509,10 @@
         <v>1.24</v>
       </c>
       <c r="I354" t="n">
-        <v>0.4997</v>
+        <v>0.6103</v>
       </c>
       <c r="J354" t="n">
-        <v>10.4937</v>
+        <v>12.8163</v>
       </c>
     </row>
     <row r="355">
@@ -16549,10 +16549,10 @@
         <v>1.19</v>
       </c>
       <c r="I355" t="n">
-        <v>0.3822</v>
+        <v>0.4884</v>
       </c>
       <c r="J355" t="n">
-        <v>8.026199999999999</v>
+        <v>10.2564</v>
       </c>
     </row>
     <row r="356">
@@ -16589,10 +16589,10 @@
         <v>1.16</v>
       </c>
       <c r="I356" t="n">
-        <v>0.3092</v>
+        <v>0.412</v>
       </c>
       <c r="J356" t="n">
-        <v>6.4932</v>
+        <v>8.651999999999999</v>
       </c>
     </row>
     <row r="357">
@@ -16629,10 +16629,10 @@
         <v>1.09</v>
       </c>
       <c r="I357" t="n">
-        <v>0.317</v>
+        <v>0.3378</v>
       </c>
       <c r="J357" t="n">
-        <v>6.657</v>
+        <v>7.0938</v>
       </c>
     </row>
     <row r="358">
@@ -16669,10 +16669,10 @@
         <v>0.8</v>
       </c>
       <c r="I358" t="n">
-        <v>-0.2584</v>
+        <v>-0.2072</v>
       </c>
       <c r="J358" t="n">
-        <v>-5.4264</v>
+        <v>-4.3512</v>
       </c>
     </row>
     <row r="359">
@@ -16709,10 +16709,10 @@
         <v>0.72</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.4074</v>
+        <v>-0.2831</v>
       </c>
       <c r="J359" t="n">
-        <v>-8.555400000000001</v>
+        <v>-5.9451</v>
       </c>
     </row>
     <row r="360">
@@ -16749,10 +16749,10 @@
         <v>0.6</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.5891</v>
+        <v>-0.395</v>
       </c>
       <c r="J360" t="n">
-        <v>-12.3711</v>
+        <v>-8.295</v>
       </c>
     </row>
     <row r="361">
@@ -16789,10 +16789,10 @@
         <v>0.47</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.7587</v>
+        <v>-0.5163</v>
       </c>
       <c r="J361" t="n">
-        <v>-15.9327</v>
+        <v>-10.8423</v>
       </c>
     </row>
     <row r="362">
@@ -16829,10 +16829,10 @@
         <v>1.33</v>
       </c>
       <c r="I362" t="n">
-        <v>0.954</v>
+        <v>0.9287</v>
       </c>
       <c r="J362" t="n">
-        <v>38.16</v>
+        <v>37.148</v>
       </c>
     </row>
     <row r="363">
@@ -16869,10 +16869,10 @@
         <v>1.14</v>
       </c>
       <c r="I363" t="n">
-        <v>0.49</v>
+        <v>0.4493</v>
       </c>
       <c r="J363" t="n">
-        <v>19.6</v>
+        <v>17.972</v>
       </c>
     </row>
     <row r="364">
@@ -16909,10 +16909,10 @@
         <v>1.06</v>
       </c>
       <c r="I364" t="n">
-        <v>0.2444</v>
+        <v>0.2205</v>
       </c>
       <c r="J364" t="n">
-        <v>9.776</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="365">
@@ -16949,10 +16949,10 @@
         <v>0.83</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.6041</v>
+        <v>-0.5517</v>
       </c>
       <c r="J365" t="n">
-        <v>-24.164</v>
+        <v>-22.068</v>
       </c>
     </row>
     <row r="366">
@@ -16989,10 +16989,10 @@
         <v>0.8</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.6798</v>
+        <v>-0.6307</v>
       </c>
       <c r="J366" t="n">
-        <v>-27.192</v>
+        <v>-25.228</v>
       </c>
     </row>
     <row r="367">
@@ -17029,10 +17029,10 @@
         <v>1.22</v>
       </c>
       <c r="I367" t="n">
-        <v>0.3778</v>
+        <v>0.447</v>
       </c>
       <c r="J367" t="n">
-        <v>15.112</v>
+        <v>17.88</v>
       </c>
     </row>
     <row r="368">
@@ -17069,10 +17069,10 @@
         <v>1.16</v>
       </c>
       <c r="I368" t="n">
-        <v>0.2873</v>
+        <v>0.34</v>
       </c>
       <c r="J368" t="n">
-        <v>11.492</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="369">
@@ -17109,10 +17109,10 @@
         <v>1.12</v>
       </c>
       <c r="I369" t="n">
-        <v>0.2198</v>
+        <v>0.2659</v>
       </c>
       <c r="J369" t="n">
-        <v>8.792</v>
+        <v>10.636</v>
       </c>
     </row>
     <row r="370">
@@ -17149,10 +17149,10 @@
         <v>1.11</v>
       </c>
       <c r="I370" t="n">
-        <v>0.201</v>
+        <v>0.247</v>
       </c>
       <c r="J370" t="n">
-        <v>8.039999999999999</v>
+        <v>9.880000000000001</v>
       </c>
     </row>
     <row r="371">
@@ -17189,10 +17189,10 @@
         <v>0.89</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.2704</v>
+        <v>-0.1562</v>
       </c>
       <c r="J371" t="n">
-        <v>-10.816</v>
+        <v>-6.248</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/6334/event_6334_evp_summary.xlsx
+++ b/database/event/6334/event_6334_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.7451</v>
+        <v>4.8083</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9277</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5042</v>
+        <v>1.5646</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7451</v>
+        <v>4.8083</v>
       </c>
       <c r="F2" t="n">
-        <v>4.7451</v>
+        <v>4.8083</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>7.0595</v>
+        <v>7.7989</v>
       </c>
       <c r="I2" t="n">
-        <v>9.7455</v>
+        <v>9.5594</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>9.7455</v>
+        <v>9.5594</v>
       </c>
       <c r="N2" t="n">
         <v>257</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.9159</v>
+        <v>3.7741</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.7378</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1298</v>
+        <v>1.0938</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9159</v>
+        <v>3.7741</v>
       </c>
       <c r="F3" t="n">
-        <v>3.9159</v>
+        <v>3.7741</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5.2387</v>
+        <v>5.5354</v>
       </c>
       <c r="I3" t="n">
-        <v>6.4083</v>
+        <v>6.2863</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>6.4083</v>
+        <v>6.2863</v>
       </c>
       <c r="N3" t="n">
         <v>266</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.4398</v>
+        <v>3.3695</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6725</v>
+        <v>0.6587</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9149</v>
+        <v>0.9097</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4398</v>
+        <v>3.3695</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4398</v>
+        <v>3.3695</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1934</v>
+        <v>4.6499</v>
       </c>
       <c r="I4" t="n">
-        <v>5.7889</v>
+        <v>5.6996</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5.7889</v>
+        <v>5.6996</v>
       </c>
       <c r="N4" t="n">
         <v>257</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.4338</v>
+        <v>3.3549</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6713</v>
+        <v>0.6559</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9122</v>
+        <v>0.903</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4338</v>
+        <v>3.3549</v>
       </c>
       <c r="F5" t="n">
-        <v>3.4338</v>
+        <v>3.3549</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4.1802</v>
+        <v>4.618</v>
       </c>
       <c r="I5" t="n">
-        <v>5.7706</v>
+        <v>5.6604</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>5.7706</v>
+        <v>5.6604</v>
       </c>
       <c r="N5" t="n">
         <v>257</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.3095</v>
+        <v>3.1165</v>
       </c>
       <c r="C6" t="n">
-        <v>0.647</v>
+        <v>0.6093</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8561</v>
+        <v>0.7945</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3095</v>
+        <v>3.1165</v>
       </c>
       <c r="F6" t="n">
-        <v>3.3095</v>
+        <v>3.1165</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3.9073</v>
+        <v>4.096</v>
       </c>
       <c r="I6" t="n">
-        <v>4.7796</v>
+        <v>4.6517</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4.7796</v>
+        <v>4.6517</v>
       </c>
       <c r="N6" t="n">
         <v>292</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.2504</v>
+        <v>3.0312</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6355</v>
+        <v>0.5926</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8294</v>
+        <v>0.7557</v>
       </c>
       <c r="E7" t="n">
-        <v>3.2504</v>
+        <v>3.0312</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2504</v>
+        <v>3.0312</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3.7775</v>
+        <v>3.9095</v>
       </c>
       <c r="I7" t="n">
-        <v>4.4383</v>
+        <v>4.3283</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>4.4383</v>
+        <v>4.3283</v>
       </c>
       <c r="N7" t="n">
         <v>264</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>Lack1</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.1448</v>
+        <v>3.0038</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6148</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7817</v>
+        <v>0.7432</v>
       </c>
       <c r="E8" t="n">
-        <v>3.1448</v>
+        <v>3.0038</v>
       </c>
       <c r="F8" t="n">
-        <v>3.1448</v>
+        <v>3.0038</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5458</v>
+        <v>3.8494</v>
       </c>
       <c r="I8" t="n">
-        <v>4.3374</v>
+        <v>4.8399</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>292</v>
+        <v>440</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.3374</v>
+        <v>4.8399</v>
       </c>
       <c r="N8" t="n">
-        <v>292</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Lack1</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.132</v>
+        <v>2.9361</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6123</v>
+        <v>0.574</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7759</v>
+        <v>0.7124</v>
       </c>
       <c r="E9" t="n">
-        <v>3.132</v>
+        <v>2.9361</v>
       </c>
       <c r="F9" t="n">
-        <v>3.132</v>
+        <v>2.9361</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5175</v>
+        <v>3.7013</v>
       </c>
       <c r="I9" t="n">
-        <v>5.0555</v>
+        <v>4.2034</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>440</v>
+        <v>292</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>5.0555</v>
+        <v>4.2034</v>
       </c>
       <c r="N9" t="n">
-        <v>440</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.0405</v>
+        <v>2.8639</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5944</v>
+        <v>0.5599</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7346</v>
+        <v>0.6795</v>
       </c>
       <c r="E10" t="n">
-        <v>3.0405</v>
+        <v>2.8639</v>
       </c>
       <c r="F10" t="n">
-        <v>3.0405</v>
+        <v>2.8639</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.3168</v>
+        <v>3.5433</v>
       </c>
       <c r="I10" t="n">
-        <v>4.767</v>
+        <v>4.4551</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.767</v>
+        <v>4.4551</v>
       </c>
       <c r="N10" t="n">
         <v>440</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.3976</v>
+        <v>2.3738</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4687</v>
+        <v>0.4641</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4444</v>
+        <v>0.4564</v>
       </c>
       <c r="E11" t="n">
-        <v>2.3976</v>
+        <v>2.3738</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3976</v>
+        <v>2.3738</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.3976</v>
+        <v>2.4706</v>
       </c>
       <c r="I11" t="n">
-        <v>2.817</v>
+        <v>2.7353</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.817</v>
+        <v>2.7353</v>
       </c>
       <c r="N11" t="n">
         <v>264</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.2631</v>
+        <v>2.2243</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4424</v>
+        <v>0.4349</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3837</v>
+        <v>0.3883</v>
       </c>
       <c r="E12" t="n">
-        <v>2.2631</v>
+        <v>2.2243</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2631</v>
+        <v>2.2243</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.2631</v>
+        <v>2.2243</v>
       </c>
       <c r="I12" t="n">
-        <v>2.3562</v>
+        <v>2.2816</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.3562</v>
+        <v>2.2816</v>
       </c>
       <c r="N12" t="n">
         <v>154</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.146</v>
+        <v>2.1772</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4195</v>
+        <v>0.4256</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3308</v>
+        <v>0.3669</v>
       </c>
       <c r="E13" t="n">
-        <v>2.146</v>
+        <v>2.1772</v>
       </c>
       <c r="F13" t="n">
-        <v>2.146</v>
+        <v>2.1772</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.146</v>
+        <v>2.1772</v>
       </c>
       <c r="I13" t="n">
-        <v>2.6251</v>
+        <v>2.4726</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6251</v>
+        <v>2.4726</v>
       </c>
       <c r="N13" t="n">
         <v>292</v>
@@ -1044,93 +1044,93 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WolfY</t>
+          <t>El1an</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.749</v>
+        <v>1.8578</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3419</v>
+        <v>0.3632</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1516</v>
+        <v>0.2215</v>
       </c>
       <c r="E14" t="n">
-        <v>1.749</v>
+        <v>1.8578</v>
       </c>
       <c r="F14" t="n">
-        <v>1.749</v>
+        <v>1.8578</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.749</v>
+        <v>1.8578</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1395</v>
+        <v>2.3358</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>266</v>
+        <v>440</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.1395</v>
+        <v>2.3358</v>
       </c>
       <c r="N14" t="n">
-        <v>266</v>
+        <v>440</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>El1an</t>
+          <t>WolfY</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.6626</v>
+        <v>1.8331</v>
       </c>
       <c r="C15" t="n">
-        <v>0.325</v>
+        <v>0.3584</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1126</v>
+        <v>0.2103</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6626</v>
+        <v>1.8331</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6626</v>
+        <v>1.8331</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6626</v>
+        <v>1.8331</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3895</v>
+        <v>2.0818</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>440</v>
+        <v>266</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.3895</v>
+        <v>2.0818</v>
       </c>
       <c r="N15" t="n">
-        <v>440</v>
+        <v>266</v>
       </c>
     </row>
     <row r="16">
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.5414</v>
+        <v>1.5575</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3013</v>
+        <v>0.3045</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0579</v>
+        <v>0.0848</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5414</v>
+        <v>1.5575</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5414</v>
+        <v>1.5575</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5414</v>
+        <v>1.5575</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8855</v>
+        <v>1.7688</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.8855</v>
+        <v>1.7688</v>
       </c>
       <c r="N16" t="n">
         <v>292</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.0479</v>
+        <v>1.1986</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2049</v>
+        <v>0.2343</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1649</v>
+        <v>-0.0786</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0479</v>
+        <v>1.1986</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0479</v>
+        <v>1.1986</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0479</v>
+        <v>1.1986</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4466</v>
+        <v>1.4692</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4466</v>
+        <v>1.4692</v>
       </c>
       <c r="N17" t="n">
         <v>257</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9324</v>
+        <v>1.1067</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1823</v>
+        <v>0.2164</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2171</v>
+        <v>-0.1204</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9324</v>
+        <v>1.1067</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9324</v>
+        <v>1.1067</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9324</v>
+        <v>1.1067</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2871</v>
+        <v>1.3565</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.2871</v>
+        <v>1.3565</v>
       </c>
       <c r="N18" t="n">
         <v>257</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9256</v>
+        <v>0.9941</v>
       </c>
       <c r="C19" t="n">
-        <v>0.181</v>
+        <v>0.1943</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2202</v>
+        <v>-0.1717</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9256</v>
+        <v>0.9941</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9256</v>
+        <v>0.9941</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9256</v>
+        <v>0.9941</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0875</v>
+        <v>1.1006</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0875</v>
+        <v>1.1006</v>
       </c>
       <c r="N19" t="n">
         <v>264</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7544999999999999</v>
+        <v>0.7329</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1475</v>
+        <v>0.1433</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2974</v>
+        <v>-0.2906</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7544999999999999</v>
+        <v>0.7329</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7544999999999999</v>
+        <v>0.7329</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7544999999999999</v>
+        <v>0.7329</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8865</v>
+        <v>0.8114</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8865</v>
+        <v>0.8114</v>
       </c>
       <c r="N20" t="n">
         <v>264</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5894</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1152</v>
+        <v>0.1181</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3719</v>
+        <v>-0.3491</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5894</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5894</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5894</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6389</v>
+        <v>0.6358</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6389</v>
+        <v>0.6358</v>
       </c>
       <c r="N21" t="n">
         <v>169</v>
@@ -1412,185 +1412,185 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>birdfromsky</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5534</v>
+        <v>0.5676</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1082</v>
+        <v>0.111</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3882</v>
+        <v>-0.3658</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5534</v>
+        <v>0.5676</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5534</v>
+        <v>0.5676</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5534</v>
+        <v>0.5676</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5999</v>
+        <v>0.6446</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>169</v>
+        <v>266</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5999</v>
+        <v>0.6446</v>
       </c>
       <c r="N22" t="n">
-        <v>169</v>
+        <v>266</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>birdfromsky</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5409</v>
+        <v>0.5387</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1057</v>
+        <v>0.1053</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3938</v>
+        <v>-0.379</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5409</v>
+        <v>0.5387</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5409</v>
+        <v>0.5387</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5409</v>
+        <v>0.5387</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6616</v>
+        <v>0.5668</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>266</v>
+        <v>169</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6616</v>
+        <v>0.5668</v>
       </c>
       <c r="N23" t="n">
-        <v>266</v>
+        <v>169</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>xsepower</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4237</v>
+        <v>0.3791</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0828</v>
+        <v>0.0741</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4467</v>
+        <v>-0.4516</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4237</v>
+        <v>0.3791</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4237</v>
+        <v>0.3791</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4237</v>
+        <v>0.3791</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4781</v>
+        <v>0.4305</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>222</v>
+        <v>292</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4781</v>
+        <v>0.4305</v>
       </c>
       <c r="N24" t="n">
-        <v>222</v>
+        <v>292</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>xsepower</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3766</v>
+        <v>0.3157</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0736</v>
+        <v>0.0617</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.468</v>
+        <v>-0.4805</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3766</v>
+        <v>0.3157</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3766</v>
+        <v>0.3157</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3766</v>
+        <v>0.3157</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4607</v>
+        <v>0.3407</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>292</v>
+        <v>222</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4607</v>
+        <v>0.3407</v>
       </c>
       <c r="N25" t="n">
-        <v>292</v>
+        <v>222</v>
       </c>
     </row>
     <row r="26">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2619</v>
+        <v>0.2621</v>
       </c>
       <c r="C26" t="n">
         <v>0.0512</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5198</v>
+        <v>-0.5049</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2619</v>
+        <v>0.2621</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2619</v>
+        <v>0.2621</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2619</v>
+        <v>0.2621</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2727</v>
+        <v>0.2689</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2727</v>
+        <v>0.2689</v>
       </c>
       <c r="N26" t="n">
         <v>154</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.1413</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0178</v>
+        <v>0.0276</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.597</v>
+        <v>-0.5599</v>
       </c>
       <c r="E27" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.1413</v>
       </c>
       <c r="F27" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.1413</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.1413</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1112</v>
+        <v>0.1605</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1112</v>
+        <v>0.1605</v>
       </c>
       <c r="N27" t="n">
         <v>266</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0192</v>
+        <v>-0.056</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0038</v>
+        <v>-0.0109</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6497000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0192</v>
+        <v>-0.056</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0192</v>
+        <v>-0.056</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.0192</v>
+        <v>-0.056</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0208</v>
+        <v>-0.0589</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.0208</v>
+        <v>-0.0589</v>
       </c>
       <c r="N28" t="n">
         <v>169</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0451</v>
+        <v>-0.0733</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0143</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6584</v>
+        <v>-0.6576</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0451</v>
+        <v>-0.0733</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0451</v>
+        <v>-0.0733</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0451</v>
+        <v>-0.0733</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.053</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.053</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="N29" t="n">
         <v>264</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0839</v>
+        <v>-0.1365</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0164</v>
+        <v>-0.0267</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.6863</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0839</v>
+        <v>-0.1365</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0839</v>
+        <v>-0.1365</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.0839</v>
+        <v>-0.1365</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0873</v>
+        <v>-0.14</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.0873</v>
+        <v>-0.14</v>
       </c>
       <c r="N30" t="n">
         <v>154</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1647</v>
+        <v>-0.17</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0322</v>
+        <v>-0.0332</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7124</v>
+        <v>-0.7016</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1647</v>
+        <v>-0.17</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1647</v>
+        <v>-0.17</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.1647</v>
+        <v>-0.17</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2367</v>
+        <v>-0.2137</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2367</v>
+        <v>-0.2137</v>
       </c>
       <c r="N31" t="n">
         <v>440</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>junior</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.2395</v>
+        <v>-0.2821</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0468</v>
+        <v>-0.0552</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7461</v>
+        <v>-0.7526</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2395</v>
+        <v>-0.2821</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.2395</v>
+        <v>-0.2821</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.2395</v>
+        <v>-0.2821</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.2703</v>
+        <v>-0.2894</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>222</v>
+        <v>154</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.2703</v>
+        <v>-0.2894</v>
       </c>
       <c r="N32" t="n">
-        <v>222</v>
+        <v>154</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>junior</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.2591</v>
+        <v>-0.2839</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0507</v>
+        <v>-0.0555</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.755</v>
+        <v>-0.7534</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.2591</v>
+        <v>-0.2839</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.2591</v>
+        <v>-0.2839</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.2591</v>
+        <v>-0.2839</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2698</v>
+        <v>-0.3064</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>154</v>
+        <v>222</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.2698</v>
+        <v>-0.3064</v>
       </c>
       <c r="N33" t="n">
-        <v>154</v>
+        <v>222</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.4551</v>
+        <v>-0.485</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.089</v>
+        <v>-0.0948</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8435</v>
+        <v>-0.845</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.4551</v>
+        <v>-0.485</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.4551</v>
+        <v>-0.485</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.4551</v>
+        <v>-0.485</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4933</v>
+        <v>-0.5103</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4933</v>
+        <v>-0.5103</v>
       </c>
       <c r="N34" t="n">
         <v>169</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6528</v>
+        <v>-0.6473</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1276</v>
+        <v>-0.1265</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9327</v>
+        <v>-0.9189000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6528</v>
+        <v>-0.6473</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6528</v>
+        <v>-0.6473</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.6528</v>
+        <v>-0.6473</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7986</v>
+        <v>-0.7351</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7986</v>
+        <v>-0.7351</v>
       </c>
       <c r="N35" t="n">
         <v>266</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.6651</v>
+        <v>-0.6918</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.13</v>
+        <v>-0.1352</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9383</v>
+        <v>-0.9391</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.6651</v>
+        <v>-0.6918</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.6651</v>
+        <v>-0.6918</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.6651</v>
+        <v>-0.6918</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6925</v>
+        <v>-0.7096</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.6925</v>
+        <v>-0.7096</v>
       </c>
       <c r="N36" t="n">
         <v>154</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7992</v>
+        <v>-0.9103</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1562</v>
+        <v>-0.178</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9988</v>
+        <v>-1.0386</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7992</v>
+        <v>-0.9103</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7992</v>
+        <v>-0.9103</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7992</v>
+        <v>-0.9103</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.1487</v>
+        <v>-1.1446</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.1487</v>
+        <v>-1.1446</v>
       </c>
       <c r="N37" t="n">
         <v>440</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.8964</v>
+        <v>-1.0077</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1752</v>
+        <v>-0.197</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0427</v>
+        <v>-1.0829</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.8964</v>
+        <v>-1.0077</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.8964</v>
+        <v>-1.0077</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.8964</v>
+        <v>-1.0077</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.0116</v>
+        <v>-1.0876</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0116</v>
+        <v>-1.0876</v>
       </c>
       <c r="N38" t="n">
         <v>222</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.1997</v>
+        <v>-1.2905</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2345</v>
+        <v>-0.2523</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1796</v>
+        <v>-1.2117</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.1997</v>
+        <v>-1.2905</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.1997</v>
+        <v>-1.2905</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.1997</v>
+        <v>-1.2905</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.3004</v>
+        <v>-1.3579</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.3004</v>
+        <v>-1.3579</v>
       </c>
       <c r="N39" t="n">
         <v>169</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.2488</v>
+        <v>-1.3659</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2441</v>
+        <v>-0.267</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2018</v>
+        <v>-1.246</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.2488</v>
+        <v>-1.3659</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.2488</v>
+        <v>-1.3659</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.2488</v>
+        <v>-1.3659</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.4093</v>
+        <v>-1.4742</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.4093</v>
+        <v>-1.4742</v>
       </c>
       <c r="N40" t="n">
         <v>222</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.8109</v>
+        <v>-1.9169</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.354</v>
+        <v>-0.3748</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4555</v>
+        <v>-1.4968</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.8109</v>
+        <v>-1.9169</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.8109</v>
+        <v>-1.9169</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.8109</v>
+        <v>-1.9169</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.0437</v>
+        <v>-2.0689</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.0437</v>
+        <v>-2.0689</v>
       </c>
       <c r="N41" t="n">
         <v>222</v>
@@ -2429,10 +2429,10 @@
         <v>1.61</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2877</v>
+        <v>1.2591</v>
       </c>
       <c r="J2" t="n">
-        <v>29.6171</v>
+        <v>28.9593</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.33</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8698</v>
+        <v>0.8184</v>
       </c>
       <c r="J3" t="n">
-        <v>20.0054</v>
+        <v>18.8232</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.03</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0905</v>
+        <v>0.1083</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0815</v>
+        <v>2.4909</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0425</v>
+        <v>-0.0293</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9775</v>
+        <v>-0.6739000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.91</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3682</v>
+        <v>-0.3489</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.4686</v>
+        <v>-8.024699999999999</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4919</v>
+        <v>0.4729</v>
       </c>
       <c r="J7" t="n">
-        <v>11.3137</v>
+        <v>10.8767</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.96</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0494</v>
+        <v>-0.0619</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1362</v>
+        <v>-1.4237</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.82</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.203</v>
+        <v>-0.2201</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.669</v>
+        <v>-5.0623</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3295</v>
+        <v>-0.3441</v>
       </c>
       <c r="J10" t="n">
-        <v>-7.5785</v>
+        <v>-7.9143</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.67</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3484</v>
+        <v>-0.3624</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.013199999999999</v>
+        <v>-8.3352</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.26</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7274</v>
+        <v>0.6895</v>
       </c>
       <c r="J12" t="n">
-        <v>20.3672</v>
+        <v>19.306</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.13</v>
       </c>
       <c r="I13" t="n">
-        <v>0.401</v>
+        <v>0.3968</v>
       </c>
       <c r="J13" t="n">
-        <v>11.228</v>
+        <v>11.1104</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.08</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2655</v>
+        <v>0.2709</v>
       </c>
       <c r="J14" t="n">
-        <v>7.434</v>
+        <v>7.5852</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.08</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2655</v>
+        <v>0.2709</v>
       </c>
       <c r="J15" t="n">
-        <v>7.434</v>
+        <v>7.5852</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0255</v>
+        <v>-0.0175</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.714</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.07</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1946</v>
+        <v>0.1995</v>
       </c>
       <c r="J17" t="n">
-        <v>5.4488</v>
+        <v>5.586</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.98</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0329</v>
+        <v>-0.0404</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.9212</v>
+        <v>-1.1312</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0839</v>
+        <v>-0.0958</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.3492</v>
+        <v>-2.6824</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.91</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1183</v>
+        <v>-0.1318</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.3124</v>
+        <v>-3.6904</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.88</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1511</v>
+        <v>-0.1654</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.2308</v>
+        <v>-4.6312</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.48</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7128</v>
+        <v>0.6875</v>
       </c>
       <c r="J22" t="n">
-        <v>20.6712</v>
+        <v>19.9375</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.05</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1102</v>
+        <v>0.1185</v>
       </c>
       <c r="J23" t="n">
-        <v>3.1958</v>
+        <v>3.4365</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.93</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0978</v>
+        <v>-0.1098</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.8362</v>
+        <v>-3.1842</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.77</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2662</v>
+        <v>-0.2798</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.7198</v>
+        <v>-8.1142</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.66</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3714</v>
+        <v>-0.3821</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.7706</v>
+        <v>-11.0809</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.62</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7942</v>
+        <v>0.7769</v>
       </c>
       <c r="J27" t="n">
-        <v>23.0318</v>
+        <v>22.5301</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.95</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.08210000000000001</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>-2.3809</v>
+        <v>-2.6332</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0944</v>
+        <v>-0.1039</v>
       </c>
       <c r="J29" t="n">
-        <v>-2.7376</v>
+        <v>-3.0131</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.91</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1296</v>
+        <v>-0.1405</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.7584</v>
+        <v>-4.0745</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.88</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1628</v>
+        <v>-0.1745</v>
       </c>
       <c r="J31" t="n">
-        <v>-4.7212</v>
+        <v>-5.0605</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.37</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9868</v>
+        <v>0.9221</v>
       </c>
       <c r="J32" t="n">
-        <v>28.6172</v>
+        <v>26.7409</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.29</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8072</v>
+        <v>0.7582</v>
       </c>
       <c r="J33" t="n">
-        <v>23.4088</v>
+        <v>21.9878</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.08</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2693</v>
+        <v>0.2735</v>
       </c>
       <c r="J34" t="n">
-        <v>7.8097</v>
+        <v>7.9315</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2537</v>
+        <v>-0.2475</v>
       </c>
       <c r="J35" t="n">
-        <v>-7.3573</v>
+        <v>-7.1775</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.77</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7241</v>
+        <v>-0.6738</v>
       </c>
       <c r="J36" t="n">
-        <v>-20.9989</v>
+        <v>-19.5402</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.21</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4673</v>
+        <v>0.4583</v>
       </c>
       <c r="J37" t="n">
-        <v>13.5517</v>
+        <v>13.2907</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.08</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2124</v>
+        <v>0.2178</v>
       </c>
       <c r="J38" t="n">
-        <v>6.1596</v>
+        <v>6.3162</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.06</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1687</v>
+        <v>0.1751</v>
       </c>
       <c r="J39" t="n">
-        <v>4.8923</v>
+        <v>5.0779</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.92</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1085</v>
+        <v>-0.1212</v>
       </c>
       <c r="J40" t="n">
-        <v>-3.1465</v>
+        <v>-3.5148</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.58</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4443</v>
+        <v>-0.4522</v>
       </c>
       <c r="J41" t="n">
-        <v>-12.8847</v>
+        <v>-13.1138</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.3</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8873</v>
+        <v>0.8186</v>
       </c>
       <c r="J42" t="n">
-        <v>26.619</v>
+        <v>24.558</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.13</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4433</v>
+        <v>0.4261</v>
       </c>
       <c r="J43" t="n">
-        <v>13.299</v>
+        <v>12.783</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.02</v>
       </c>
       <c r="I44" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.1035</v>
       </c>
       <c r="J44" t="n">
-        <v>2.988</v>
+        <v>3.105</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.84</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5081</v>
+        <v>-0.4881</v>
       </c>
       <c r="J45" t="n">
-        <v>-15.243</v>
+        <v>-14.643</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.59</v>
       </c>
       <c r="I46" t="n">
-        <v>-1.1327</v>
+        <v>-1.0332</v>
       </c>
       <c r="J46" t="n">
-        <v>-33.981</v>
+        <v>-30.996</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.39</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7419</v>
+        <v>0.7147</v>
       </c>
       <c r="J47" t="n">
-        <v>22.257</v>
+        <v>21.441</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.27</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5405</v>
+        <v>0.5319</v>
       </c>
       <c r="J48" t="n">
-        <v>16.215</v>
+        <v>15.957</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.14</v>
       </c>
       <c r="I49" t="n">
-        <v>0.308</v>
+        <v>0.3152</v>
       </c>
       <c r="J49" t="n">
-        <v>9.24</v>
+        <v>9.456</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.08</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1916</v>
+        <v>0.2029</v>
       </c>
       <c r="J50" t="n">
-        <v>5.748</v>
+        <v>6.087</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.49</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5345</v>
+        <v>-0.5363</v>
       </c>
       <c r="J51" t="n">
-        <v>-16.035</v>
+        <v>-16.089</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.65</v>
       </c>
       <c r="I52" t="n">
-        <v>1.288</v>
+        <v>1.2682</v>
       </c>
       <c r="J52" t="n">
-        <v>27.048</v>
+        <v>26.6322</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.58</v>
       </c>
       <c r="I53" t="n">
-        <v>1.2043</v>
+        <v>1.1787</v>
       </c>
       <c r="J53" t="n">
-        <v>25.2903</v>
+        <v>24.7527</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.51</v>
       </c>
       <c r="I54" t="n">
-        <v>1.1196</v>
+        <v>1.0875</v>
       </c>
       <c r="J54" t="n">
-        <v>23.5116</v>
+        <v>22.8375</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.14</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3716</v>
+        <v>0.3825</v>
       </c>
       <c r="J55" t="n">
-        <v>7.8036</v>
+        <v>8.032500000000001</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.0898</v>
+        <v>-0.0624</v>
       </c>
       <c r="J56" t="n">
-        <v>-1.8858</v>
+        <v>-1.3104</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.26</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6792</v>
+        <v>0.6313</v>
       </c>
       <c r="J57" t="n">
-        <v>14.2632</v>
+        <v>13.2573</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.75</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.2578</v>
+        <v>-0.2773</v>
       </c>
       <c r="J58" t="n">
-        <v>-5.4138</v>
+        <v>-5.8233</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.67</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3325</v>
+        <v>-0.35</v>
       </c>
       <c r="J59" t="n">
-        <v>-6.9825</v>
+        <v>-7.35</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.66</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3419</v>
+        <v>-0.359</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.1799</v>
+        <v>-7.539</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.44</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5468</v>
+        <v>-0.5527</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.4828</v>
+        <v>-11.6067</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.3</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8068</v>
+        <v>0.7622</v>
       </c>
       <c r="J62" t="n">
-        <v>20.9768</v>
+        <v>19.8172</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.25</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6887</v>
+        <v>0.6581</v>
       </c>
       <c r="J63" t="n">
-        <v>17.9062</v>
+        <v>17.1106</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.24</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.6369</v>
       </c>
       <c r="J64" t="n">
-        <v>17.2848</v>
+        <v>16.5594</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.18</v>
       </c>
       <c r="I65" t="n">
-        <v>0.5189</v>
+        <v>0.5063</v>
       </c>
       <c r="J65" t="n">
-        <v>13.4914</v>
+        <v>13.1638</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6384</v>
+        <v>-0.5947</v>
       </c>
       <c r="J66" t="n">
-        <v>-16.5984</v>
+        <v>-15.4622</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.17</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4115</v>
+        <v>0.4028</v>
       </c>
       <c r="J67" t="n">
-        <v>10.699</v>
+        <v>10.4728</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="J68" t="n">
-        <v>-2.1112</v>
+        <v>-2.4388</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.86</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.168</v>
+        <v>-0.1836</v>
       </c>
       <c r="J69" t="n">
-        <v>-4.368</v>
+        <v>-4.7736</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.82</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.209</v>
+        <v>-0.2247</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.434</v>
+        <v>-5.8422</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.8</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2291</v>
+        <v>-0.2447</v>
       </c>
       <c r="J71" t="n">
-        <v>-5.9566</v>
+        <v>-6.3622</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.22</v>
       </c>
       <c r="I72" t="n">
-        <v>0.5049</v>
+        <v>0.4893</v>
       </c>
       <c r="J72" t="n">
-        <v>13.6323</v>
+        <v>13.2111</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.16</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3905</v>
+        <v>0.3835</v>
       </c>
       <c r="J73" t="n">
-        <v>10.5435</v>
+        <v>10.3545</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.88</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1474</v>
+        <v>-0.1626</v>
       </c>
       <c r="J74" t="n">
-        <v>-3.9798</v>
+        <v>-4.3902</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.77</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2593</v>
+        <v>-0.2744</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.0011</v>
+        <v>-7.4088</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.58</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.439</v>
+        <v>-0.448</v>
       </c>
       <c r="J76" t="n">
-        <v>-11.853</v>
+        <v>-12.096</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.24</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6688</v>
+        <v>0.6397</v>
       </c>
       <c r="J77" t="n">
-        <v>18.0576</v>
+        <v>17.2719</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.19</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5466</v>
+        <v>0.5306</v>
       </c>
       <c r="J78" t="n">
-        <v>14.7582</v>
+        <v>14.3262</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.16</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4718</v>
+        <v>0.463</v>
       </c>
       <c r="J79" t="n">
-        <v>12.7386</v>
+        <v>12.501</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.08</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2585</v>
+        <v>0.2661</v>
       </c>
       <c r="J80" t="n">
-        <v>6.9795</v>
+        <v>7.1847</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1.04</v>
       </c>
       <c r="I81" t="n">
-        <v>0.1337</v>
+        <v>0.1478</v>
       </c>
       <c r="J81" t="n">
-        <v>3.6099</v>
+        <v>3.9906</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.55</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6475</v>
+        <v>0.6524</v>
       </c>
       <c r="J82" t="n">
-        <v>14.245</v>
+        <v>14.3528</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.52</v>
       </c>
       <c r="I83" t="n">
-        <v>0.6163999999999999</v>
+        <v>0.6233</v>
       </c>
       <c r="J83" t="n">
-        <v>13.5608</v>
+        <v>13.7126</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.32</v>
       </c>
       <c r="I84" t="n">
-        <v>0.4056</v>
+        <v>0.4229</v>
       </c>
       <c r="J84" t="n">
-        <v>8.9232</v>
+        <v>9.303800000000001</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.29</v>
       </c>
       <c r="I85" t="n">
-        <v>0.3719</v>
+        <v>0.3904</v>
       </c>
       <c r="J85" t="n">
-        <v>8.181800000000001</v>
+        <v>8.588800000000001</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.16</v>
       </c>
       <c r="I86" t="n">
-        <v>0.2142</v>
+        <v>0.2366</v>
       </c>
       <c r="J86" t="n">
-        <v>4.7124</v>
+        <v>5.2052</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.13</v>
       </c>
       <c r="I87" t="n">
-        <v>0.2877</v>
+        <v>0.2826</v>
       </c>
       <c r="J87" t="n">
-        <v>6.3294</v>
+        <v>6.2172</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2077</v>
+        <v>-0.226</v>
       </c>
       <c r="J88" t="n">
-        <v>-4.5694</v>
+        <v>-4.972</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.78</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2366</v>
+        <v>-0.2547</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.2052</v>
+        <v>-5.6034</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.71</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3038</v>
+        <v>-0.3205</v>
       </c>
       <c r="J90" t="n">
-        <v>-6.6836</v>
+        <v>-7.051</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.67</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3418</v>
+        <v>-0.3572</v>
       </c>
       <c r="J91" t="n">
-        <v>-7.5196</v>
+        <v>-7.8584</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.17</v>
       </c>
       <c r="I92" t="n">
-        <v>0.38</v>
+        <v>0.3796</v>
       </c>
       <c r="J92" t="n">
-        <v>13.68</v>
+        <v>13.6656</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.07</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1814</v>
+        <v>0.19</v>
       </c>
       <c r="J93" t="n">
-        <v>6.5304</v>
+        <v>6.84</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.05</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1374</v>
+        <v>0.1465</v>
       </c>
       <c r="J94" t="n">
-        <v>4.9464</v>
+        <v>5.274</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.92</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1127</v>
+        <v>-0.1245</v>
       </c>
       <c r="J95" t="n">
-        <v>-4.0572</v>
+        <v>-4.482</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.84</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1995</v>
+        <v>-0.2128</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.182</v>
+        <v>-7.6608</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.77</v>
       </c>
       <c r="I97" t="n">
-        <v>1.501</v>
+        <v>1.4817</v>
       </c>
       <c r="J97" t="n">
-        <v>54.036</v>
+        <v>53.3412</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.24</v>
       </c>
       <c r="I98" t="n">
-        <v>0.67</v>
+        <v>0.6405</v>
       </c>
       <c r="J98" t="n">
-        <v>24.12</v>
+        <v>23.058</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.07</v>
       </c>
       <c r="I99" t="n">
-        <v>0.2298</v>
+        <v>0.2389</v>
       </c>
       <c r="J99" t="n">
-        <v>8.2728</v>
+        <v>8.6004</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.9</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3875</v>
+        <v>-0.3689</v>
       </c>
       <c r="J100" t="n">
-        <v>-13.95</v>
+        <v>-13.2804</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.71</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.8859</v>
+        <v>-0.8136</v>
       </c>
       <c r="J101" t="n">
-        <v>-31.8924</v>
+        <v>-29.2896</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.46</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6008</v>
+        <v>0.6002999999999999</v>
       </c>
       <c r="J102" t="n">
-        <v>17.4232</v>
+        <v>17.4087</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.32</v>
       </c>
       <c r="I103" t="n">
-        <v>0.4386</v>
+        <v>0.4477</v>
       </c>
       <c r="J103" t="n">
-        <v>12.7194</v>
+        <v>12.9833</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.07</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1192</v>
+        <v>0.1338</v>
       </c>
       <c r="J104" t="n">
-        <v>3.4568</v>
+        <v>3.8802</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.96</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.0741</v>
+        <v>-0.0809</v>
       </c>
       <c r="J105" t="n">
-        <v>-2.1489</v>
+        <v>-2.3461</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.72</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3284</v>
+        <v>-0.338</v>
       </c>
       <c r="J106" t="n">
-        <v>-9.5236</v>
+        <v>-9.802</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.3</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4676</v>
+        <v>0.4645</v>
       </c>
       <c r="J107" t="n">
-        <v>13.5604</v>
+        <v>13.4705</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.25</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4007</v>
+        <v>0.4019</v>
       </c>
       <c r="J108" t="n">
-        <v>11.6203</v>
+        <v>11.6551</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.001</v>
+        <v>-0.0007</v>
       </c>
       <c r="J109" t="n">
-        <v>-0.029</v>
+        <v>-0.0203</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.88</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1579</v>
+        <v>-0.1707</v>
       </c>
       <c r="J110" t="n">
-        <v>-4.5791</v>
+        <v>-4.9503</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.65</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3849</v>
+        <v>-0.3944</v>
       </c>
       <c r="J111" t="n">
-        <v>-11.1621</v>
+        <v>-11.4376</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1</v>
       </c>
       <c r="I112" t="n">
-        <v>0.039</v>
+        <v>0.0282</v>
       </c>
       <c r="J112" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.6768</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.91</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.107</v>
+        <v>-0.1232</v>
       </c>
       <c r="J113" t="n">
-        <v>-2.568</v>
+        <v>-2.9568</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.88</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1402</v>
+        <v>-0.1572</v>
       </c>
       <c r="J114" t="n">
-        <v>-3.3648</v>
+        <v>-3.7728</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.75</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2687</v>
+        <v>-0.2856</v>
       </c>
       <c r="J115" t="n">
-        <v>-6.4488</v>
+        <v>-6.8544</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.68</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3357</v>
+        <v>-0.3507</v>
       </c>
       <c r="J116" t="n">
-        <v>-8.056800000000001</v>
+        <v>-8.4168</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.64</v>
       </c>
       <c r="I117" t="n">
-        <v>1.2872</v>
+        <v>1.2652</v>
       </c>
       <c r="J117" t="n">
-        <v>30.8928</v>
+        <v>30.3648</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.38</v>
       </c>
       <c r="I118" t="n">
-        <v>0.9398</v>
+        <v>0.8884</v>
       </c>
       <c r="J118" t="n">
-        <v>22.5552</v>
+        <v>21.3216</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.33</v>
       </c>
       <c r="I119" t="n">
-        <v>0.8345</v>
+        <v>0.7941</v>
       </c>
       <c r="J119" t="n">
-        <v>20.028</v>
+        <v>19.0584</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.31</v>
       </c>
       <c r="I120" t="n">
-        <v>0.792</v>
+        <v>0.7564</v>
       </c>
       <c r="J120" t="n">
-        <v>19.008</v>
+        <v>18.1536</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.95</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2795</v>
+        <v>-0.2576</v>
       </c>
       <c r="J121" t="n">
-        <v>-6.708</v>
+        <v>-6.1824</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.09</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2503</v>
+        <v>0.2505</v>
       </c>
       <c r="J122" t="n">
-        <v>7.2587</v>
+        <v>7.2645</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.02</v>
       </c>
       <c r="I123" t="n">
-        <v>0.0849</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="J123" t="n">
-        <v>2.4621</v>
+        <v>2.523</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.01</v>
       </c>
       <c r="I124" t="n">
-        <v>0.0555</v>
+        <v>0.0561</v>
       </c>
       <c r="J124" t="n">
-        <v>1.6095</v>
+        <v>1.6269</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.98</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.0283</v>
+        <v>-0.0369</v>
       </c>
       <c r="J125" t="n">
-        <v>-0.8207</v>
+        <v>-1.0701</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.48</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5292</v>
+        <v>-0.5334</v>
       </c>
       <c r="J126" t="n">
-        <v>-15.3468</v>
+        <v>-15.4686</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.94</v>
       </c>
       <c r="I127" t="n">
-        <v>1.6762</v>
+        <v>1.6693</v>
       </c>
       <c r="J127" t="n">
-        <v>48.6098</v>
+        <v>48.4097</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.36</v>
       </c>
       <c r="I128" t="n">
-        <v>0.923</v>
+        <v>0.8681</v>
       </c>
       <c r="J128" t="n">
-        <v>26.767</v>
+        <v>25.1749</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.05</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1474</v>
+        <v>0.1661</v>
       </c>
       <c r="J129" t="n">
-        <v>4.2746</v>
+        <v>4.8169</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.01</v>
       </c>
       <c r="I130" t="n">
-        <v>0.0013</v>
+        <v>0.0228</v>
       </c>
       <c r="J130" t="n">
-        <v>0.0377</v>
+        <v>0.6612</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.74</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.8310999999999999</v>
+        <v>-0.7624</v>
       </c>
       <c r="J131" t="n">
-        <v>-24.1019</v>
+        <v>-22.1096</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.31</v>
       </c>
       <c r="I132" t="n">
-        <v>0.8315</v>
+        <v>0.7836</v>
       </c>
       <c r="J132" t="n">
-        <v>24.945</v>
+        <v>23.508</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.28</v>
       </c>
       <c r="I133" t="n">
-        <v>0.7611</v>
+        <v>0.7218</v>
       </c>
       <c r="J133" t="n">
-        <v>22.833</v>
+        <v>21.654</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.25</v>
       </c>
       <c r="I134" t="n">
-        <v>0.6899</v>
+        <v>0.6589</v>
       </c>
       <c r="J134" t="n">
-        <v>20.697</v>
+        <v>19.767</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.99</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.0848</v>
       </c>
       <c r="J135" t="n">
-        <v>-2.739</v>
+        <v>-2.544</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.93</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3016</v>
+        <v>-0.2885</v>
       </c>
       <c r="J136" t="n">
-        <v>-9.048</v>
+        <v>-8.654999999999999</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.24</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5301</v>
+        <v>0.5145</v>
       </c>
       <c r="J137" t="n">
-        <v>15.903</v>
+        <v>15.435</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.02</v>
       </c>
       <c r="I138" t="n">
-        <v>0.076</v>
+        <v>0.0805</v>
       </c>
       <c r="J138" t="n">
-        <v>2.28</v>
+        <v>2.415</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.99</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.0166</v>
+        <v>-0.0222</v>
       </c>
       <c r="J139" t="n">
-        <v>-0.498</v>
+        <v>-0.666</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.92</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1065</v>
+        <v>-0.1197</v>
       </c>
       <c r="J140" t="n">
-        <v>-3.195</v>
+        <v>-3.591</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.58</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4422</v>
+        <v>-0.4505</v>
       </c>
       <c r="J141" t="n">
-        <v>-13.266</v>
+        <v>-13.515</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.84</v>
       </c>
       <c r="I142" t="n">
-        <v>1.5538</v>
+        <v>1.5421</v>
       </c>
       <c r="J142" t="n">
-        <v>34.1836</v>
+        <v>33.9262</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.2</v>
       </c>
       <c r="I143" t="n">
-        <v>0.5561</v>
+        <v>0.5425</v>
       </c>
       <c r="J143" t="n">
-        <v>12.2342</v>
+        <v>11.935</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.1</v>
       </c>
       <c r="I144" t="n">
-        <v>0.2959</v>
+        <v>0.3057</v>
       </c>
       <c r="J144" t="n">
-        <v>6.5098</v>
+        <v>6.7254</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.02</v>
       </c>
       <c r="I145" t="n">
-        <v>0.0404</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="J145" t="n">
-        <v>0.8888</v>
+        <v>1.3816</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.98</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.1517</v>
+        <v>-0.1398</v>
       </c>
       <c r="J146" t="n">
-        <v>-3.3374</v>
+        <v>-3.0756</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.13</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3528</v>
+        <v>0.3437</v>
       </c>
       <c r="J147" t="n">
-        <v>7.7616</v>
+        <v>7.5614</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.97</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.0357</v>
+        <v>-0.0472</v>
       </c>
       <c r="J148" t="n">
-        <v>-0.7854</v>
+        <v>-1.0384</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.9</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1214</v>
+        <v>-0.1372</v>
       </c>
       <c r="J149" t="n">
-        <v>-2.6708</v>
+        <v>-3.0184</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3295</v>
+        <v>-0.3441</v>
       </c>
       <c r="J150" t="n">
-        <v>-7.249</v>
+        <v>-7.5702</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.65</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3673</v>
+        <v>-0.3805</v>
       </c>
       <c r="J151" t="n">
-        <v>-8.0806</v>
+        <v>-8.371</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.88</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.0774</v>
+        <v>-0.1079</v>
       </c>
       <c r="J152" t="n">
-        <v>-1.7028</v>
+        <v>-2.3738</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.67</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.3093</v>
+        <v>-0.3322</v>
       </c>
       <c r="J153" t="n">
-        <v>-6.8046</v>
+        <v>-7.3084</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.54</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.4279</v>
+        <v>-0.4453</v>
       </c>
       <c r="J154" t="n">
-        <v>-9.4138</v>
+        <v>-9.7966</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.46</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.5031</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="J155" t="n">
-        <v>-11.0682</v>
+        <v>-11.3432</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.46</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5031</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="J156" t="n">
-        <v>-11.0682</v>
+        <v>-11.3432</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.77</v>
       </c>
       <c r="I157" t="n">
-        <v>1.4121</v>
+        <v>1.4029</v>
       </c>
       <c r="J157" t="n">
-        <v>31.0662</v>
+        <v>30.8638</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.69</v>
       </c>
       <c r="I158" t="n">
-        <v>1.3198</v>
+        <v>1.3049</v>
       </c>
       <c r="J158" t="n">
-        <v>29.0356</v>
+        <v>28.7078</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.44</v>
       </c>
       <c r="I159" t="n">
-        <v>1.0237</v>
+        <v>0.9792</v>
       </c>
       <c r="J159" t="n">
-        <v>22.5214</v>
+        <v>21.5424</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.24</v>
       </c>
       <c r="I160" t="n">
-        <v>0.6046</v>
+        <v>0.5955</v>
       </c>
       <c r="J160" t="n">
-        <v>13.3012</v>
+        <v>13.101</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.16</v>
       </c>
       <c r="I161" t="n">
-        <v>0.4062</v>
+        <v>0.4176</v>
       </c>
       <c r="J161" t="n">
-        <v>8.936400000000001</v>
+        <v>9.187200000000001</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.26</v>
       </c>
       <c r="I162" t="n">
-        <v>0.3714</v>
+        <v>0.3826</v>
       </c>
       <c r="J162" t="n">
-        <v>10.3992</v>
+        <v>10.7128</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.11</v>
       </c>
       <c r="I163" t="n">
-        <v>0.1779</v>
+        <v>0.193</v>
       </c>
       <c r="J163" t="n">
-        <v>4.9812</v>
+        <v>5.404</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.1</v>
       </c>
       <c r="I164" t="n">
-        <v>0.1641</v>
+        <v>0.1791</v>
       </c>
       <c r="J164" t="n">
-        <v>4.5948</v>
+        <v>5.0148</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.02</v>
       </c>
       <c r="I165" t="n">
-        <v>0.039</v>
+        <v>0.0486</v>
       </c>
       <c r="J165" t="n">
-        <v>1.092</v>
+        <v>1.3608</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.91</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.1318</v>
+        <v>-0.1422</v>
       </c>
       <c r="J166" t="n">
-        <v>-3.6904</v>
+        <v>-3.9816</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.29</v>
       </c>
       <c r="I167" t="n">
-        <v>0.4779</v>
+        <v>0.4698</v>
       </c>
       <c r="J167" t="n">
-        <v>13.3812</v>
+        <v>13.1544</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.1</v>
       </c>
       <c r="I168" t="n">
-        <v>0.2016</v>
+        <v>0.2075</v>
       </c>
       <c r="J168" t="n">
-        <v>5.6448</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.91</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1167</v>
+        <v>-0.1306</v>
       </c>
       <c r="J169" t="n">
-        <v>-3.2676</v>
+        <v>-3.6568</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.86</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1705</v>
+        <v>-0.1855</v>
       </c>
       <c r="J170" t="n">
-        <v>-4.774</v>
+        <v>-5.194</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.54</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4775</v>
+        <v>-0.4842</v>
       </c>
       <c r="J171" t="n">
-        <v>-13.37</v>
+        <v>-13.5576</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>0.98</v>
       </c>
       <c r="I172" t="n">
-        <v>0.032</v>
+        <v>-0.0011</v>
       </c>
       <c r="J172" t="n">
-        <v>0.64</v>
+        <v>-0.022</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.96</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.0127</v>
+        <v>-0.0332</v>
       </c>
       <c r="J173" t="n">
-        <v>-0.254</v>
+        <v>-0.664</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.66</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3349</v>
+        <v>-0.3536</v>
       </c>
       <c r="J174" t="n">
-        <v>-6.698</v>
+        <v>-7.072</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.51</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.475</v>
+        <v>-0.4865</v>
       </c>
       <c r="J175" t="n">
-        <v>-9.5</v>
+        <v>-9.73</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.44</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5403</v>
+        <v>-0.5476</v>
       </c>
       <c r="J176" t="n">
-        <v>-10.806</v>
+        <v>-10.952</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.72</v>
       </c>
       <c r="I177" t="n">
-        <v>1.3696</v>
+        <v>1.3551</v>
       </c>
       <c r="J177" t="n">
-        <v>27.392</v>
+        <v>27.102</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.42</v>
       </c>
       <c r="I178" t="n">
-        <v>1.0014</v>
+        <v>0.9527</v>
       </c>
       <c r="J178" t="n">
-        <v>20.028</v>
+        <v>19.054</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.33</v>
       </c>
       <c r="I179" t="n">
-        <v>0.8260999999999999</v>
+        <v>0.7884</v>
       </c>
       <c r="J179" t="n">
-        <v>16.522</v>
+        <v>15.768</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.26</v>
       </c>
       <c r="I180" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.6486</v>
       </c>
       <c r="J180" t="n">
-        <v>13.356</v>
+        <v>12.972</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.18</v>
       </c>
       <c r="I181" t="n">
-        <v>0.4739</v>
+        <v>0.4754</v>
       </c>
       <c r="J181" t="n">
-        <v>9.478</v>
+        <v>9.507999999999999</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>0.98</v>
       </c>
       <c r="I182" t="n">
-        <v>0.078</v>
+        <v>0.0322</v>
       </c>
       <c r="J182" t="n">
-        <v>1.638</v>
+        <v>0.6762</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.63</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.3528</v>
+        <v>-0.3727</v>
       </c>
       <c r="J183" t="n">
-        <v>-7.4088</v>
+        <v>-7.8267</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.6</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.38</v>
+        <v>-0.3986</v>
       </c>
       <c r="J184" t="n">
-        <v>-7.98</v>
+        <v>-8.3706</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.58</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3984</v>
+        <v>-0.4161</v>
       </c>
       <c r="J185" t="n">
-        <v>-8.366400000000001</v>
+        <v>-8.738099999999999</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.43</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5392</v>
+        <v>-0.548</v>
       </c>
       <c r="J186" t="n">
-        <v>-11.3232</v>
+        <v>-11.508</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.63</v>
       </c>
       <c r="I187" t="n">
-        <v>1.2554</v>
+        <v>1.235</v>
       </c>
       <c r="J187" t="n">
-        <v>26.3634</v>
+        <v>25.935</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.52</v>
       </c>
       <c r="I188" t="n">
-        <v>1.1248</v>
+        <v>1.0946</v>
       </c>
       <c r="J188" t="n">
-        <v>23.6208</v>
+        <v>22.9866</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.41</v>
       </c>
       <c r="I189" t="n">
-        <v>0.9808</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="J189" t="n">
-        <v>20.5968</v>
+        <v>19.572</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.33</v>
       </c>
       <c r="I190" t="n">
-        <v>0.8179</v>
+        <v>0.7829</v>
       </c>
       <c r="J190" t="n">
-        <v>17.1759</v>
+        <v>16.4409</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.24</v>
       </c>
       <c r="I191" t="n">
-        <v>0.6116</v>
+        <v>0.6004</v>
       </c>
       <c r="J191" t="n">
-        <v>12.8436</v>
+        <v>12.6084</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.41</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.5749</v>
       </c>
       <c r="J192" t="n">
-        <v>17.403</v>
+        <v>17.247</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.04</v>
       </c>
       <c r="I193" t="n">
-        <v>0.0859</v>
+        <v>0.095</v>
       </c>
       <c r="J193" t="n">
-        <v>2.577</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.91</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1207</v>
+        <v>-0.1336</v>
       </c>
       <c r="J194" t="n">
-        <v>-3.621</v>
+        <v>-4.008</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2264</v>
+        <v>-0.2404</v>
       </c>
       <c r="J195" t="n">
-        <v>-6.792</v>
+        <v>-7.212</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.72</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3147</v>
+        <v>-0.3272</v>
       </c>
       <c r="J196" t="n">
-        <v>-9.441000000000001</v>
+        <v>-9.816000000000001</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.28</v>
       </c>
       <c r="I197" t="n">
-        <v>0.4338</v>
+        <v>0.4342</v>
       </c>
       <c r="J197" t="n">
-        <v>13.014</v>
+        <v>13.026</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.19</v>
       </c>
       <c r="I198" t="n">
-        <v>0.3118</v>
+        <v>0.319</v>
       </c>
       <c r="J198" t="n">
-        <v>9.353999999999999</v>
+        <v>9.57</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.1</v>
       </c>
       <c r="I199" t="n">
-        <v>0.181</v>
+        <v>0.1922</v>
       </c>
       <c r="J199" t="n">
-        <v>5.43</v>
+        <v>5.766</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.89</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1502</v>
+        <v>-0.162</v>
       </c>
       <c r="J200" t="n">
-        <v>-4.506</v>
+        <v>-4.86</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.76</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.2835</v>
+        <v>-0.2953</v>
       </c>
       <c r="J201" t="n">
-        <v>-8.505000000000001</v>
+        <v>-8.859</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.01</v>
       </c>
       <c r="I202" t="n">
-        <v>0.1103</v>
+        <v>0.0963</v>
       </c>
       <c r="J202" t="n">
-        <v>2.4266</v>
+        <v>2.1186</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.92</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.0819</v>
+        <v>-0.1007</v>
       </c>
       <c r="J203" t="n">
-        <v>-1.8018</v>
+        <v>-2.2154</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.84</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1721</v>
+        <v>-0.1917</v>
       </c>
       <c r="J204" t="n">
-        <v>-3.7862</v>
+        <v>-4.2174</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.6</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4006</v>
+        <v>-0.4147</v>
       </c>
       <c r="J205" t="n">
-        <v>-8.8132</v>
+        <v>-9.1234</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.49</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5028</v>
+        <v>-0.5112</v>
       </c>
       <c r="J206" t="n">
-        <v>-11.0616</v>
+        <v>-11.2464</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.77</v>
       </c>
       <c r="I207" t="n">
-        <v>1.4309</v>
+        <v>1.4194</v>
       </c>
       <c r="J207" t="n">
-        <v>31.4798</v>
+        <v>31.2268</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.68</v>
       </c>
       <c r="I208" t="n">
-        <v>1.3248</v>
+        <v>1.3071</v>
       </c>
       <c r="J208" t="n">
-        <v>29.1456</v>
+        <v>28.7562</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.67</v>
       </c>
       <c r="I209" t="n">
-        <v>1.313</v>
+        <v>1.2945</v>
       </c>
       <c r="J209" t="n">
-        <v>28.886</v>
+        <v>28.479</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.87</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.5265</v>
+        <v>-0.4846</v>
       </c>
       <c r="J210" t="n">
-        <v>-11.583</v>
+        <v>-10.6612</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.86</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5538</v>
+        <v>-0.5094</v>
       </c>
       <c r="J211" t="n">
-        <v>-12.1836</v>
+        <v>-11.2068</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.94</v>
       </c>
       <c r="I212" t="n">
-        <v>1.5902</v>
+        <v>1.593</v>
       </c>
       <c r="J212" t="n">
-        <v>28.6236</v>
+        <v>28.674</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.75</v>
       </c>
       <c r="I213" t="n">
-        <v>1.3774</v>
+        <v>1.3682</v>
       </c>
       <c r="J213" t="n">
-        <v>24.7932</v>
+        <v>24.6276</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.45</v>
       </c>
       <c r="I214" t="n">
-        <v>1.0302</v>
+        <v>0.9885</v>
       </c>
       <c r="J214" t="n">
-        <v>18.5436</v>
+        <v>17.793</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.28</v>
       </c>
       <c r="I215" t="n">
-        <v>0.6843</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="J215" t="n">
-        <v>12.3174</v>
+        <v>12.0402</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.23</v>
       </c>
       <c r="I216" t="n">
-        <v>0.5665</v>
+        <v>0.5643</v>
       </c>
       <c r="J216" t="n">
-        <v>10.197</v>
+        <v>10.1574</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.88</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.0655</v>
+        <v>-0.0984</v>
       </c>
       <c r="J217" t="n">
-        <v>-1.179</v>
+        <v>-1.7712</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.66</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.3127</v>
+        <v>-0.3365</v>
       </c>
       <c r="J218" t="n">
-        <v>-5.6286</v>
+        <v>-6.057</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.62</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.3518</v>
+        <v>-0.3737</v>
       </c>
       <c r="J219" t="n">
-        <v>-6.3324</v>
+        <v>-6.7266</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.42</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.5362</v>
+        <v>-0.547</v>
       </c>
       <c r="J220" t="n">
-        <v>-9.6516</v>
+        <v>-9.846</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.3</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6523</v>
+        <v>-0.6535</v>
       </c>
       <c r="J221" t="n">
-        <v>-11.7414</v>
+        <v>-11.763</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.03</v>
       </c>
       <c r="I222" t="n">
-        <v>0.0916</v>
+        <v>0.0941</v>
       </c>
       <c r="J222" t="n">
-        <v>2.6564</v>
+        <v>2.7289</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.95</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="J223" t="n">
-        <v>-1.9024</v>
+        <v>-2.2678</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.92</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1016</v>
+        <v>-0.1159</v>
       </c>
       <c r="J224" t="n">
-        <v>-2.9464</v>
+        <v>-3.3611</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.86</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.165</v>
+        <v>-0.1813</v>
       </c>
       <c r="J225" t="n">
-        <v>-4.785</v>
+        <v>-5.2577</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3324</v>
+        <v>-0.3464</v>
       </c>
       <c r="J226" t="n">
-        <v>-9.6396</v>
+        <v>-10.0456</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.33</v>
       </c>
       <c r="I227" t="n">
-        <v>0.4452</v>
+        <v>0.455</v>
       </c>
       <c r="J227" t="n">
-        <v>12.9108</v>
+        <v>13.195</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.31</v>
       </c>
       <c r="I228" t="n">
-        <v>0.4217</v>
+        <v>0.4326</v>
       </c>
       <c r="J228" t="n">
-        <v>12.2293</v>
+        <v>12.5454</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.29</v>
       </c>
       <c r="I229" t="n">
-        <v>0.398</v>
+        <v>0.4099</v>
       </c>
       <c r="J229" t="n">
-        <v>11.542</v>
+        <v>11.8871</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.89</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.1596</v>
+        <v>-0.1694</v>
       </c>
       <c r="J230" t="n">
-        <v>-4.6284</v>
+        <v>-4.9126</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.84</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2127</v>
+        <v>-0.2232</v>
       </c>
       <c r="J231" t="n">
-        <v>-6.1683</v>
+        <v>-6.4728</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.32</v>
       </c>
       <c r="I232" t="n">
-        <v>0.8779</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="J232" t="n">
-        <v>30.7265</v>
+        <v>28.7035</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.21</v>
       </c>
       <c r="I233" t="n">
-        <v>0.6107</v>
+        <v>0.585</v>
       </c>
       <c r="J233" t="n">
-        <v>21.3745</v>
+        <v>20.475</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.11</v>
       </c>
       <c r="I234" t="n">
-        <v>0.3512</v>
+        <v>0.3501</v>
       </c>
       <c r="J234" t="n">
-        <v>12.292</v>
+        <v>12.2535</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.2542</v>
+        <v>-0.2479</v>
       </c>
       <c r="J235" t="n">
-        <v>-8.897</v>
+        <v>-8.676500000000001</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.88</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4321</v>
+        <v>-0.4124</v>
       </c>
       <c r="J236" t="n">
-        <v>-15.1235</v>
+        <v>-14.434</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.07</v>
       </c>
       <c r="I237" t="n">
-        <v>0.1878</v>
+        <v>0.1946</v>
       </c>
       <c r="J237" t="n">
-        <v>6.573</v>
+        <v>6.811</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.06</v>
       </c>
       <c r="I238" t="n">
-        <v>0.1658</v>
+        <v>0.173</v>
       </c>
       <c r="J238" t="n">
-        <v>5.803</v>
+        <v>6.055</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.05</v>
       </c>
       <c r="I239" t="n">
-        <v>0.1431</v>
+        <v>0.1506</v>
       </c>
       <c r="J239" t="n">
-        <v>5.0085</v>
+        <v>5.271</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.91</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.1211</v>
+        <v>-0.1339</v>
       </c>
       <c r="J240" t="n">
-        <v>-4.2385</v>
+        <v>-4.6865</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.82</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2167</v>
+        <v>-0.2307</v>
       </c>
       <c r="J241" t="n">
-        <v>-7.5845</v>
+        <v>-8.0745</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.53</v>
       </c>
       <c r="I242" t="n">
-        <v>1.236</v>
+        <v>1.1951</v>
       </c>
       <c r="J242" t="n">
-        <v>51.912</v>
+        <v>50.1942</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.0047</v>
+        <v>-0.0032</v>
       </c>
       <c r="J243" t="n">
-        <v>-0.1974</v>
+        <v>-0.1344</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.95</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.2041</v>
+        <v>-0.205</v>
       </c>
       <c r="J244" t="n">
-        <v>-8.5722</v>
+        <v>-8.609999999999999</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2361</v>
+        <v>-0.2353</v>
       </c>
       <c r="J245" t="n">
-        <v>-9.9162</v>
+        <v>-9.8826</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.71</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.8566</v>
+        <v>-0.7929</v>
       </c>
       <c r="J246" t="n">
-        <v>-35.9772</v>
+        <v>-33.3018</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.43</v>
       </c>
       <c r="I247" t="n">
-        <v>0.8079</v>
+        <v>0.7739</v>
       </c>
       <c r="J247" t="n">
-        <v>33.9318</v>
+        <v>32.5038</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.12</v>
       </c>
       <c r="I248" t="n">
-        <v>0.2704</v>
+        <v>0.2793</v>
       </c>
       <c r="J248" t="n">
-        <v>11.3568</v>
+        <v>11.7306</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.02</v>
       </c>
       <c r="I249" t="n">
-        <v>0.0562</v>
+        <v>0.0664</v>
       </c>
       <c r="J249" t="n">
-        <v>2.3604</v>
+        <v>2.7888</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.01</v>
       </c>
       <c r="I250" t="n">
-        <v>0.0274</v>
+        <v>0.0361</v>
       </c>
       <c r="J250" t="n">
-        <v>1.1508</v>
+        <v>1.5162</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.78</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2669</v>
+        <v>-0.2784</v>
       </c>
       <c r="J251" t="n">
-        <v>-11.2098</v>
+        <v>-11.6928</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.78</v>
       </c>
       <c r="I252" t="n">
-        <v>1.5013</v>
+        <v>1.4839</v>
       </c>
       <c r="J252" t="n">
-        <v>39.0338</v>
+        <v>38.5814</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.06</v>
       </c>
       <c r="I253" t="n">
-        <v>0.1915</v>
+        <v>0.2048</v>
       </c>
       <c r="J253" t="n">
-        <v>4.979</v>
+        <v>5.3248</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.04</v>
       </c>
       <c r="I254" t="n">
-        <v>0.1267</v>
+        <v>0.143</v>
       </c>
       <c r="J254" t="n">
-        <v>3.2942</v>
+        <v>3.718</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.02</v>
       </c>
       <c r="I255" t="n">
-        <v>0.0549</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="J255" t="n">
-        <v>1.4274</v>
+        <v>1.8954</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.95</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.2428</v>
+        <v>-0.2319</v>
       </c>
       <c r="J256" t="n">
-        <v>-6.3128</v>
+        <v>-6.0294</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.27</v>
       </c>
       <c r="I257" t="n">
-        <v>0.5555</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="J257" t="n">
-        <v>14.443</v>
+        <v>14.1128</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.17</v>
       </c>
       <c r="I258" t="n">
-        <v>0.3755</v>
+        <v>0.3764</v>
       </c>
       <c r="J258" t="n">
-        <v>9.763</v>
+        <v>9.7864</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.09</v>
       </c>
       <c r="I259" t="n">
-        <v>0.22</v>
+        <v>0.2285</v>
       </c>
       <c r="J259" t="n">
-        <v>5.72</v>
+        <v>5.941</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.96</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.0658</v>
+        <v>-0.0745</v>
       </c>
       <c r="J260" t="n">
-        <v>-1.7108</v>
+        <v>-1.937</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.64</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3952</v>
+        <v>-0.4041</v>
       </c>
       <c r="J261" t="n">
-        <v>-10.2752</v>
+        <v>-10.5066</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.62</v>
       </c>
       <c r="I262" t="n">
-        <v>1.2865</v>
+        <v>1.2603</v>
       </c>
       <c r="J262" t="n">
-        <v>34.7355</v>
+        <v>34.0281</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.5</v>
       </c>
       <c r="I263" t="n">
-        <v>1.1358</v>
+        <v>1.0992</v>
       </c>
       <c r="J263" t="n">
-        <v>30.6666</v>
+        <v>29.6784</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.22</v>
       </c>
       <c r="I264" t="n">
-        <v>0.6039</v>
+        <v>0.5854</v>
       </c>
       <c r="J264" t="n">
-        <v>16.3053</v>
+        <v>15.8058</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.97</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.188</v>
+        <v>-0.1757</v>
       </c>
       <c r="J265" t="n">
-        <v>-5.076</v>
+        <v>-4.7439</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.6549</v>
+        <v>-0.6063</v>
       </c>
       <c r="J266" t="n">
-        <v>-17.6823</v>
+        <v>-16.3701</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.75</v>
       </c>
       <c r="I267" t="n">
-        <v>1.2068</v>
+        <v>1.1838</v>
       </c>
       <c r="J267" t="n">
-        <v>32.5836</v>
+        <v>31.9626</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.92</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1119</v>
+        <v>-0.1238</v>
       </c>
       <c r="J268" t="n">
-        <v>-3.0213</v>
+        <v>-3.3426</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.89</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1455</v>
+        <v>-0.1584</v>
       </c>
       <c r="J269" t="n">
-        <v>-3.9285</v>
+        <v>-4.2768</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.2292</v>
+        <v>-0.2426</v>
       </c>
       <c r="J270" t="n">
-        <v>-6.1884</v>
+        <v>-6.5502</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.64</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3926</v>
+        <v>-0.4021</v>
       </c>
       <c r="J271" t="n">
-        <v>-10.6002</v>
+        <v>-10.8567</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.09</v>
       </c>
       <c r="I272" t="n">
-        <v>0.1656</v>
+        <v>0.1769</v>
       </c>
       <c r="J272" t="n">
-        <v>5.796</v>
+        <v>6.1915</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.06</v>
       </c>
       <c r="I273" t="n">
-        <v>0.1177</v>
+        <v>0.1288</v>
       </c>
       <c r="J273" t="n">
-        <v>4.1195</v>
+        <v>4.508</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.06</v>
       </c>
       <c r="I274" t="n">
-        <v>0.1177</v>
+        <v>0.1288</v>
       </c>
       <c r="J274" t="n">
-        <v>4.1195</v>
+        <v>4.508</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.05</v>
       </c>
       <c r="I275" t="n">
-        <v>0.1011</v>
+        <v>0.1118</v>
       </c>
       <c r="J275" t="n">
-        <v>3.5385</v>
+        <v>3.913</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.96</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0759</v>
       </c>
       <c r="J276" t="n">
-        <v>-2.366</v>
+        <v>-2.6565</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.24</v>
       </c>
       <c r="I277" t="n">
-        <v>0.3475</v>
+        <v>0.3594</v>
       </c>
       <c r="J277" t="n">
-        <v>12.1625</v>
+        <v>12.579</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.23</v>
       </c>
       <c r="I278" t="n">
-        <v>0.335</v>
+        <v>0.3474</v>
       </c>
       <c r="J278" t="n">
-        <v>11.725</v>
+        <v>12.159</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.07</v>
       </c>
       <c r="I279" t="n">
-        <v>0.122</v>
+        <v>0.1359</v>
       </c>
       <c r="J279" t="n">
-        <v>4.27</v>
+        <v>4.7565</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.0064</v>
+        <v>-0.0049</v>
       </c>
       <c r="J280" t="n">
-        <v>-0.224</v>
+        <v>-0.1715</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.84</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.2069</v>
+        <v>-0.2186</v>
       </c>
       <c r="J281" t="n">
-        <v>-7.2415</v>
+        <v>-7.651</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.95</v>
       </c>
       <c r="I282" t="n">
-        <v>1.6386</v>
+        <v>1.6377</v>
       </c>
       <c r="J282" t="n">
-        <v>39.3264</v>
+        <v>39.3048</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.44</v>
       </c>
       <c r="I283" t="n">
-        <v>1.0325</v>
+        <v>0.9871</v>
       </c>
       <c r="J283" t="n">
-        <v>24.78</v>
+        <v>23.6904</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.41</v>
       </c>
       <c r="I284" t="n">
-        <v>0.9865</v>
+        <v>0.9365</v>
       </c>
       <c r="J284" t="n">
-        <v>23.676</v>
+        <v>22.476</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.04</v>
       </c>
       <c r="I285" t="n">
-        <v>0.0788</v>
+        <v>0.1096</v>
       </c>
       <c r="J285" t="n">
-        <v>1.8912</v>
+        <v>2.6304</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>1.02</v>
       </c>
       <c r="I286" t="n">
-        <v>0.007</v>
+        <v>0.0394</v>
       </c>
       <c r="J286" t="n">
-        <v>0.168</v>
+        <v>0.9456</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.18</v>
       </c>
       <c r="I287" t="n">
-        <v>0.5304</v>
+        <v>0.4943</v>
       </c>
       <c r="J287" t="n">
-        <v>12.7296</v>
+        <v>11.8632</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.88</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.1218</v>
+        <v>-0.1428</v>
       </c>
       <c r="J288" t="n">
-        <v>-2.9232</v>
+        <v>-3.4272</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.8</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.2079</v>
+        <v>-0.2285</v>
       </c>
       <c r="J289" t="n">
-        <v>-4.9896</v>
+        <v>-5.484</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.55</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.4424</v>
+        <v>-0.4551</v>
       </c>
       <c r="J290" t="n">
-        <v>-10.6176</v>
+        <v>-10.9224</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.29</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.6828</v>
+        <v>-0.6788999999999999</v>
       </c>
       <c r="J291" t="n">
-        <v>-16.3872</v>
+        <v>-16.2936</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.21</v>
       </c>
       <c r="I292" t="n">
-        <v>0.4913</v>
+        <v>0.4759</v>
       </c>
       <c r="J292" t="n">
-        <v>11.2999</v>
+        <v>10.9457</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>0.96</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.0553</v>
+        <v>-0.0665</v>
       </c>
       <c r="J293" t="n">
-        <v>-1.2719</v>
+        <v>-1.5295</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.88</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.1462</v>
+        <v>-0.1616</v>
       </c>
       <c r="J294" t="n">
-        <v>-3.3626</v>
+        <v>-3.7168</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.88</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1462</v>
+        <v>-0.1616</v>
       </c>
       <c r="J295" t="n">
-        <v>-3.3626</v>
+        <v>-3.7168</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.62</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.4007</v>
+        <v>-0.4116</v>
       </c>
       <c r="J296" t="n">
-        <v>-9.216100000000001</v>
+        <v>-9.466799999999999</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.57</v>
       </c>
       <c r="I297" t="n">
-        <v>1.2242</v>
+        <v>1.1938</v>
       </c>
       <c r="J297" t="n">
-        <v>28.1566</v>
+        <v>27.4574</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.47</v>
       </c>
       <c r="I298" t="n">
-        <v>1.0975</v>
+        <v>1.0574</v>
       </c>
       <c r="J298" t="n">
-        <v>25.2425</v>
+        <v>24.3202</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.17</v>
       </c>
       <c r="I299" t="n">
-        <v>0.483</v>
+        <v>0.4764</v>
       </c>
       <c r="J299" t="n">
-        <v>11.109</v>
+        <v>10.9572</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.98</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.1507</v>
+        <v>-0.1391</v>
       </c>
       <c r="J300" t="n">
-        <v>-3.4661</v>
+        <v>-3.1993</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.93</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3199</v>
+        <v>-0.3013</v>
       </c>
       <c r="J301" t="n">
-        <v>-7.3577</v>
+        <v>-6.9299</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.38</v>
       </c>
       <c r="I302" t="n">
-        <v>0.5131</v>
+        <v>0.5174</v>
       </c>
       <c r="J302" t="n">
-        <v>18.4716</v>
+        <v>18.6264</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.11</v>
       </c>
       <c r="I303" t="n">
-        <v>0.177</v>
+        <v>0.1924</v>
       </c>
       <c r="J303" t="n">
-        <v>6.372</v>
+        <v>6.9264</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.09</v>
       </c>
       <c r="I304" t="n">
-        <v>0.1495</v>
+        <v>0.1645</v>
       </c>
       <c r="J304" t="n">
-        <v>5.382</v>
+        <v>5.922</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.08</v>
       </c>
       <c r="I305" t="n">
-        <v>0.1356</v>
+        <v>0.1501</v>
       </c>
       <c r="J305" t="n">
-        <v>4.8816</v>
+        <v>5.4036</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.78</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.2686</v>
+        <v>-0.2797</v>
       </c>
       <c r="J306" t="n">
-        <v>-9.669600000000001</v>
+        <v>-10.0692</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.21</v>
       </c>
       <c r="I307" t="n">
-        <v>0.3676</v>
+        <v>0.3664</v>
       </c>
       <c r="J307" t="n">
-        <v>13.2336</v>
+        <v>13.1904</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.02</v>
       </c>
       <c r="I308" t="n">
-        <v>0.0608</v>
+        <v>0.065</v>
       </c>
       <c r="J308" t="n">
-        <v>2.1888</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.88</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.1489</v>
+        <v>-0.1637</v>
       </c>
       <c r="J309" t="n">
-        <v>-5.3604</v>
+        <v>-5.8932</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.85</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1805</v>
+        <v>-0.1957</v>
       </c>
       <c r="J310" t="n">
-        <v>-6.498</v>
+        <v>-7.0452</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.72</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.3096</v>
+        <v>-0.3232</v>
       </c>
       <c r="J311" t="n">
-        <v>-11.1456</v>
+        <v>-11.6352</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.12</v>
       </c>
       <c r="I312" t="n">
-        <v>0.3065</v>
+        <v>0.3055</v>
       </c>
       <c r="J312" t="n">
-        <v>8.582000000000001</v>
+        <v>8.554</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.02</v>
       </c>
       <c r="I313" t="n">
-        <v>0.08</v>
+        <v>0.0834</v>
       </c>
       <c r="J313" t="n">
-        <v>2.24</v>
+        <v>2.3352</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>0.96</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.058</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="J314" t="n">
-        <v>-1.624</v>
+        <v>-1.9208</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.88</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.1487</v>
+        <v>-0.1636</v>
       </c>
       <c r="J315" t="n">
-        <v>-4.1636</v>
+        <v>-4.5808</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.338</v>
+        <v>-0.3508</v>
       </c>
       <c r="J316" t="n">
-        <v>-9.464</v>
+        <v>-9.8224</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.69</v>
       </c>
       <c r="I317" t="n">
-        <v>1.3821</v>
+        <v>1.3599</v>
       </c>
       <c r="J317" t="n">
-        <v>38.6988</v>
+        <v>38.0772</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.26</v>
       </c>
       <c r="I318" t="n">
-        <v>0.7023</v>
+        <v>0.6721</v>
       </c>
       <c r="J318" t="n">
-        <v>19.6644</v>
+        <v>18.8188</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.1</v>
       </c>
       <c r="I319" t="n">
-        <v>0.3039</v>
+        <v>0.3112</v>
       </c>
       <c r="J319" t="n">
-        <v>8.5092</v>
+        <v>8.7136</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>1.03</v>
       </c>
       <c r="I320" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.1052</v>
       </c>
       <c r="J320" t="n">
-        <v>2.408</v>
+        <v>2.9456</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.89</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.4307</v>
+        <v>-0.4054</v>
       </c>
       <c r="J321" t="n">
-        <v>-12.0596</v>
+        <v>-11.3512</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.27</v>
       </c>
       <c r="I322" t="n">
-        <v>0.5417</v>
+        <v>0.5327</v>
       </c>
       <c r="J322" t="n">
-        <v>22.2097</v>
+        <v>21.8407</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.11</v>
       </c>
       <c r="I323" t="n">
-        <v>0.2515</v>
+        <v>0.261</v>
       </c>
       <c r="J323" t="n">
-        <v>10.3115</v>
+        <v>10.701</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.08</v>
       </c>
       <c r="I324" t="n">
-        <v>0.1921</v>
+        <v>0.2032</v>
       </c>
       <c r="J324" t="n">
-        <v>7.8761</v>
+        <v>8.331200000000001</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>0.97</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.0569</v>
+        <v>-0.0635</v>
       </c>
       <c r="J325" t="n">
-        <v>-2.3329</v>
+        <v>-2.6035</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.92</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.1192</v>
+        <v>-0.1295</v>
       </c>
       <c r="J326" t="n">
-        <v>-4.8872</v>
+        <v>-5.3095</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.35</v>
       </c>
       <c r="I327" t="n">
-        <v>0.9883</v>
+        <v>0.916</v>
       </c>
       <c r="J327" t="n">
-        <v>40.5203</v>
+        <v>37.556</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.07</v>
       </c>
       <c r="I328" t="n">
-        <v>0.2612</v>
+        <v>0.2604</v>
       </c>
       <c r="J328" t="n">
-        <v>10.7092</v>
+        <v>10.6764</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.93</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.2589</v>
+        <v>-0.2587</v>
       </c>
       <c r="J329" t="n">
-        <v>-10.6149</v>
+        <v>-10.6067</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.89</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.3763</v>
+        <v>-0.3674</v>
       </c>
       <c r="J330" t="n">
-        <v>-15.4283</v>
+        <v>-15.0634</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.74</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.7732</v>
+        <v>-0.7216</v>
       </c>
       <c r="J331" t="n">
-        <v>-31.7012</v>
+        <v>-29.5856</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.77</v>
       </c>
       <c r="I332" t="n">
-        <v>0.8776</v>
+        <v>0.8643</v>
       </c>
       <c r="J332" t="n">
-        <v>21.0624</v>
+        <v>20.7432</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.68</v>
       </c>
       <c r="I333" t="n">
-        <v>0.7864</v>
+        <v>0.7804</v>
       </c>
       <c r="J333" t="n">
-        <v>18.8736</v>
+        <v>18.7296</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.14</v>
       </c>
       <c r="I334" t="n">
-        <v>0.1914</v>
+        <v>0.2133</v>
       </c>
       <c r="J334" t="n">
-        <v>4.5936</v>
+        <v>5.1192</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>1.1</v>
       </c>
       <c r="I335" t="n">
-        <v>0.1362</v>
+        <v>0.1581</v>
       </c>
       <c r="J335" t="n">
-        <v>3.2688</v>
+        <v>3.7944</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.99</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.0523</v>
+        <v>-0.0499</v>
       </c>
       <c r="J336" t="n">
-        <v>-1.2552</v>
+        <v>-1.1976</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>0.9</v>
       </c>
       <c r="I337" t="n">
-        <v>-0.0906</v>
+        <v>-0.1132</v>
       </c>
       <c r="J337" t="n">
-        <v>-2.1744</v>
+        <v>-2.7168</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>0.86</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.1373</v>
+        <v>-0.1599</v>
       </c>
       <c r="J338" t="n">
-        <v>-3.2952</v>
+        <v>-3.8376</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>0.66</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.3349</v>
+        <v>-0.3536</v>
       </c>
       <c r="J339" t="n">
-        <v>-8.037599999999999</v>
+        <v>-8.4864</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.62</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.3722</v>
+        <v>-0.3893</v>
       </c>
       <c r="J340" t="n">
-        <v>-8.9328</v>
+        <v>-9.3432</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.51</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.475</v>
+        <v>-0.4865</v>
       </c>
       <c r="J341" t="n">
-        <v>-11.4</v>
+        <v>-11.676</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.54</v>
       </c>
       <c r="I342" t="n">
-        <v>0.9835</v>
+        <v>0.9357</v>
       </c>
       <c r="J342" t="n">
-        <v>34.4225</v>
+        <v>32.7495</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.09</v>
       </c>
       <c r="I343" t="n">
-        <v>0.2147</v>
+        <v>0.2246</v>
       </c>
       <c r="J343" t="n">
-        <v>7.5145</v>
+        <v>7.861</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.03</v>
       </c>
       <c r="I344" t="n">
-        <v>0.0848</v>
+        <v>0.0951</v>
       </c>
       <c r="J344" t="n">
-        <v>2.968</v>
+        <v>3.3285</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>0.95</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.0815</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="J345" t="n">
-        <v>-2.8525</v>
+        <v>-3.1605</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.66</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.3795</v>
+        <v>-0.3885</v>
       </c>
       <c r="J346" t="n">
-        <v>-13.2825</v>
+        <v>-13.5975</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>1.21</v>
       </c>
       <c r="I347" t="n">
-        <v>0.6399</v>
+        <v>0.6054</v>
       </c>
       <c r="J347" t="n">
-        <v>22.3965</v>
+        <v>21.189</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>1.11</v>
       </c>
       <c r="I348" t="n">
-        <v>0.3719</v>
+        <v>0.3643</v>
       </c>
       <c r="J348" t="n">
-        <v>13.0165</v>
+        <v>12.7505</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>1.05</v>
       </c>
       <c r="I349" t="n">
-        <v>0.1929</v>
+        <v>0.1973</v>
       </c>
       <c r="J349" t="n">
-        <v>6.7515</v>
+        <v>6.9055</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.98</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.1018</v>
       </c>
       <c r="J350" t="n">
-        <v>-3.3985</v>
+        <v>-3.563</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.73</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.8041</v>
+        <v>-0.7476</v>
       </c>
       <c r="J351" t="n">
-        <v>-28.1435</v>
+        <v>-26.166</v>
       </c>
     </row>
     <row r="352">
@@ -16429,10 +16429,10 @@
         <v>1.85</v>
       </c>
       <c r="I352" t="n">
-        <v>1.5094</v>
+        <v>1.5046</v>
       </c>
       <c r="J352" t="n">
-        <v>31.6974</v>
+        <v>31.5966</v>
       </c>
     </row>
     <row r="353">
@@ -16469,10 +16469,10 @@
         <v>1.72</v>
       </c>
       <c r="I353" t="n">
-        <v>1.3596</v>
+        <v>1.3463</v>
       </c>
       <c r="J353" t="n">
-        <v>28.5516</v>
+        <v>28.2723</v>
       </c>
     </row>
     <row r="354">
@@ -16509,10 +16509,10 @@
         <v>1.24</v>
       </c>
       <c r="I354" t="n">
-        <v>0.6103</v>
+        <v>0.5995</v>
       </c>
       <c r="J354" t="n">
-        <v>12.8163</v>
+        <v>12.5895</v>
       </c>
     </row>
     <row r="355">
@@ -16549,10 +16549,10 @@
         <v>1.19</v>
       </c>
       <c r="I355" t="n">
-        <v>0.4884</v>
+        <v>0.4905</v>
       </c>
       <c r="J355" t="n">
-        <v>10.2564</v>
+        <v>10.3005</v>
       </c>
     </row>
     <row r="356">
@@ -16589,10 +16589,10 @@
         <v>1.16</v>
       </c>
       <c r="I356" t="n">
-        <v>0.412</v>
+        <v>0.4217</v>
       </c>
       <c r="J356" t="n">
-        <v>8.651999999999999</v>
+        <v>8.855700000000001</v>
       </c>
     </row>
     <row r="357">
@@ -16629,10 +16629,10 @@
         <v>1.09</v>
       </c>
       <c r="I357" t="n">
-        <v>0.3378</v>
+        <v>0.315</v>
       </c>
       <c r="J357" t="n">
-        <v>7.0938</v>
+        <v>6.615</v>
       </c>
     </row>
     <row r="358">
@@ -16669,10 +16669,10 @@
         <v>0.8</v>
       </c>
       <c r="I358" t="n">
-        <v>-0.2072</v>
+        <v>-0.2279</v>
       </c>
       <c r="J358" t="n">
-        <v>-4.3512</v>
+        <v>-4.7859</v>
       </c>
     </row>
     <row r="359">
@@ -16709,10 +16709,10 @@
         <v>0.72</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.2831</v>
+        <v>-0.3026</v>
       </c>
       <c r="J359" t="n">
-        <v>-5.9451</v>
+        <v>-6.3546</v>
       </c>
     </row>
     <row r="360">
@@ -16749,10 +16749,10 @@
         <v>0.6</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.395</v>
+        <v>-0.4103</v>
       </c>
       <c r="J360" t="n">
-        <v>-8.295</v>
+        <v>-8.616300000000001</v>
       </c>
     </row>
     <row r="361">
@@ -16789,10 +16789,10 @@
         <v>0.47</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.5163</v>
+        <v>-0.5246</v>
       </c>
       <c r="J361" t="n">
-        <v>-10.8423</v>
+        <v>-11.0166</v>
       </c>
     </row>
     <row r="362">
@@ -16829,10 +16829,10 @@
         <v>1.33</v>
       </c>
       <c r="I362" t="n">
-        <v>0.9287</v>
+        <v>0.8605</v>
       </c>
       <c r="J362" t="n">
-        <v>37.148</v>
+        <v>34.42</v>
       </c>
     </row>
     <row r="363">
@@ -16869,10 +16869,10 @@
         <v>1.14</v>
       </c>
       <c r="I363" t="n">
-        <v>0.4493</v>
+        <v>0.436</v>
       </c>
       <c r="J363" t="n">
-        <v>17.972</v>
+        <v>17.44</v>
       </c>
     </row>
     <row r="364">
@@ -16909,10 +16909,10 @@
         <v>1.06</v>
       </c>
       <c r="I364" t="n">
-        <v>0.2205</v>
+        <v>0.2246</v>
       </c>
       <c r="J364" t="n">
-        <v>8.82</v>
+        <v>8.984</v>
       </c>
     </row>
     <row r="365">
@@ -16949,10 +16949,10 @@
         <v>0.83</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.5517</v>
+        <v>-0.5238</v>
       </c>
       <c r="J365" t="n">
-        <v>-22.068</v>
+        <v>-20.952</v>
       </c>
     </row>
     <row r="366">
@@ -16989,10 +16989,10 @@
         <v>0.8</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.6307</v>
+        <v>-0.5941</v>
       </c>
       <c r="J366" t="n">
-        <v>-25.228</v>
+        <v>-23.764</v>
       </c>
     </row>
     <row r="367">
@@ -17029,10 +17029,10 @@
         <v>1.22</v>
       </c>
       <c r="I367" t="n">
-        <v>0.447</v>
+        <v>0.4469</v>
       </c>
       <c r="J367" t="n">
-        <v>17.88</v>
+        <v>17.876</v>
       </c>
     </row>
     <row r="368">
@@ -17069,10 +17069,10 @@
         <v>1.16</v>
       </c>
       <c r="I368" t="n">
-        <v>0.34</v>
+        <v>0.3467</v>
       </c>
       <c r="J368" t="n">
-        <v>13.6</v>
+        <v>13.868</v>
       </c>
     </row>
     <row r="369">
@@ -17109,10 +17109,10 @@
         <v>1.12</v>
       </c>
       <c r="I369" t="n">
-        <v>0.2659</v>
+        <v>0.276</v>
       </c>
       <c r="J369" t="n">
-        <v>10.636</v>
+        <v>11.04</v>
       </c>
     </row>
     <row r="370">
@@ -17149,10 +17149,10 @@
         <v>1.11</v>
       </c>
       <c r="I370" t="n">
-        <v>0.247</v>
+        <v>0.2578</v>
       </c>
       <c r="J370" t="n">
-        <v>9.880000000000001</v>
+        <v>10.312</v>
       </c>
     </row>
     <row r="371">
@@ -17189,10 +17189,10 @@
         <v>0.89</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.1562</v>
+        <v>-0.1668</v>
       </c>
       <c r="J371" t="n">
-        <v>-6.248</v>
+        <v>-6.672</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/6334/event_6334_evp_summary.xlsx
+++ b/database/event/6334/event_6334_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.8083</v>
+        <v>4.6787</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9147</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5646</v>
+        <v>1.5256</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8083</v>
+        <v>4.6787</v>
       </c>
       <c r="F2" t="n">
-        <v>4.8083</v>
+        <v>4.6787</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>7.7989</v>
+        <v>7.772</v>
       </c>
       <c r="I2" t="n">
-        <v>9.5594</v>
+        <v>9.5975</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>9.5594</v>
+        <v>9.5975</v>
       </c>
       <c r="N2" t="n">
         <v>257</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.7741</v>
+        <v>3.6224</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7378</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0938</v>
+        <v>1.0444</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7741</v>
+        <v>3.6224</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7741</v>
+        <v>3.6224</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5.5354</v>
+        <v>5.3514</v>
       </c>
       <c r="I3" t="n">
-        <v>6.2863</v>
+        <v>6.1057</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>6.2863</v>
+        <v>6.1057</v>
       </c>
       <c r="N3" t="n">
         <v>266</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.3695</v>
+        <v>3.315</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6587</v>
+        <v>0.6481</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9097</v>
+        <v>0.9044</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3695</v>
+        <v>3.315</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3695</v>
+        <v>3.315</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>4.6499</v>
+        <v>4.6469</v>
       </c>
       <c r="I4" t="n">
-        <v>5.6996</v>
+        <v>5.7383</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5.6996</v>
+        <v>5.7383</v>
       </c>
       <c r="N4" t="n">
         <v>257</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.3549</v>
+        <v>3.2858</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6559</v>
+        <v>0.6424</v>
       </c>
       <c r="D5" t="n">
-        <v>0.903</v>
+        <v>0.8911</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3549</v>
+        <v>3.2858</v>
       </c>
       <c r="F5" t="n">
-        <v>3.3549</v>
+        <v>3.2858</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4.618</v>
+        <v>4.58</v>
       </c>
       <c r="I5" t="n">
-        <v>5.6604</v>
+        <v>5.6557</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>5.6604</v>
+        <v>5.6557</v>
       </c>
       <c r="N5" t="n">
         <v>257</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.1165</v>
+        <v>3.0326</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6093</v>
+        <v>0.5929</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7945</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>3.1165</v>
+        <v>3.0326</v>
       </c>
       <c r="F6" t="n">
-        <v>3.1165</v>
+        <v>3.0326</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>4.096</v>
+        <v>3.9996</v>
       </c>
       <c r="I6" t="n">
-        <v>4.6517</v>
+        <v>4.5633</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4.6517</v>
+        <v>4.5633</v>
       </c>
       <c r="N6" t="n">
         <v>292</v>
@@ -722,139 +722,139 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>Lack1</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.0312</v>
+        <v>2.9324</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5926</v>
+        <v>0.5733</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7557</v>
+        <v>0.7301</v>
       </c>
       <c r="E7" t="n">
-        <v>3.0312</v>
+        <v>2.9324</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0312</v>
+        <v>2.9324</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3.9095</v>
+        <v>3.7701</v>
       </c>
       <c r="I7" t="n">
-        <v>4.3283</v>
+        <v>4.78</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>264</v>
+        <v>440</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>4.3283</v>
+        <v>4.78</v>
       </c>
       <c r="N7" t="n">
-        <v>264</v>
+        <v>440</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lack1</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.0038</v>
+        <v>2.8899</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5872000000000001</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7432</v>
+        <v>0.7107</v>
       </c>
       <c r="E8" t="n">
-        <v>3.0038</v>
+        <v>2.8899</v>
       </c>
       <c r="F8" t="n">
-        <v>3.0038</v>
+        <v>2.8899</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3.8494</v>
+        <v>3.6726</v>
       </c>
       <c r="I8" t="n">
-        <v>4.8399</v>
+        <v>4.1903</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>440</v>
+        <v>292</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.8399</v>
+        <v>4.1903</v>
       </c>
       <c r="N8" t="n">
-        <v>440</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.9361</v>
+        <v>2.8557</v>
       </c>
       <c r="C9" t="n">
-        <v>0.574</v>
+        <v>0.5583</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7124</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9361</v>
+        <v>2.8557</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9361</v>
+        <v>2.8557</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3.7013</v>
+        <v>3.5944</v>
       </c>
       <c r="I9" t="n">
-        <v>4.2034</v>
+        <v>3.9943</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>292</v>
+        <v>264</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.2034</v>
+        <v>3.9943</v>
       </c>
       <c r="N9" t="n">
-        <v>292</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.8639</v>
+        <v>2.7653</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5599</v>
+        <v>0.5406</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6795</v>
+        <v>0.6539</v>
       </c>
       <c r="E10" t="n">
-        <v>2.8639</v>
+        <v>2.7653</v>
       </c>
       <c r="F10" t="n">
-        <v>2.8639</v>
+        <v>2.7653</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.5433</v>
+        <v>3.3872</v>
       </c>
       <c r="I10" t="n">
-        <v>4.4551</v>
+        <v>4.2945</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.4551</v>
+        <v>4.2945</v>
       </c>
       <c r="N10" t="n">
         <v>440</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.3738</v>
+        <v>2.3432</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4641</v>
+        <v>0.4581</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4564</v>
+        <v>0.4617</v>
       </c>
       <c r="E11" t="n">
-        <v>2.3738</v>
+        <v>2.3432</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3738</v>
+        <v>2.3432</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.4706</v>
+        <v>2.4198</v>
       </c>
       <c r="I11" t="n">
-        <v>2.7353</v>
+        <v>2.689</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7353</v>
+        <v>2.689</v>
       </c>
       <c r="N11" t="n">
         <v>264</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>k1to</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.2243</v>
+        <v>2.1907</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4349</v>
+        <v>0.4283</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3883</v>
+        <v>0.3922</v>
       </c>
       <c r="E12" t="n">
-        <v>2.2243</v>
+        <v>2.1907</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2243</v>
+        <v>2.1907</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.2243</v>
+        <v>2.1907</v>
       </c>
       <c r="I12" t="n">
-        <v>2.2816</v>
+        <v>2.4994</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>154</v>
+        <v>292</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.2816</v>
+        <v>2.4994</v>
       </c>
       <c r="N12" t="n">
-        <v>154</v>
+        <v>292</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>k1to</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.1772</v>
+        <v>2.0811</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4256</v>
+        <v>0.4069</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3669</v>
+        <v>0.3423</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1772</v>
+        <v>2.0811</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1772</v>
+        <v>2.0811</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.1772</v>
+        <v>2.0811</v>
       </c>
       <c r="I13" t="n">
-        <v>2.4726</v>
+        <v>2.1367</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>292</v>
+        <v>154</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.4726</v>
+        <v>2.1367</v>
       </c>
       <c r="N13" t="n">
-        <v>292</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.8578</v>
+        <v>1.8689</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3632</v>
+        <v>0.3654</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2215</v>
+        <v>0.2456</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8578</v>
+        <v>1.8689</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8578</v>
+        <v>1.8689</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8578</v>
+        <v>1.8689</v>
       </c>
       <c r="I14" t="n">
-        <v>2.3358</v>
+        <v>2.3696</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.3358</v>
+        <v>2.3696</v>
       </c>
       <c r="N14" t="n">
         <v>440</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.8331</v>
+        <v>1.6336</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3584</v>
+        <v>0.3194</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2103</v>
+        <v>0.1384</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8331</v>
+        <v>1.6336</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8331</v>
+        <v>1.6336</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8331</v>
+        <v>1.6336</v>
       </c>
       <c r="I15" t="n">
-        <v>2.0818</v>
+        <v>1.8639</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.0818</v>
+        <v>1.8639</v>
       </c>
       <c r="N15" t="n">
         <v>266</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.5575</v>
+        <v>1.4241</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3045</v>
+        <v>0.2784</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0848</v>
+        <v>0.043</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5575</v>
+        <v>1.4241</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5575</v>
+        <v>1.4241</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5575</v>
+        <v>1.4241</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7688</v>
+        <v>1.6248</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.7688</v>
+        <v>1.6248</v>
       </c>
       <c r="N16" t="n">
         <v>292</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.1986</v>
+        <v>1.1532</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2343</v>
+        <v>0.2255</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0786</v>
+        <v>-0.0805</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1986</v>
+        <v>1.1532</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1986</v>
+        <v>1.1532</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1986</v>
+        <v>1.1532</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4692</v>
+        <v>1.4241</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4692</v>
+        <v>1.4241</v>
       </c>
       <c r="N17" t="n">
         <v>257</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.1067</v>
+        <v>1.0399</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2164</v>
+        <v>0.2033</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1204</v>
+        <v>-0.1321</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1067</v>
+        <v>1.0399</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1067</v>
+        <v>1.0399</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1067</v>
+        <v>1.0399</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3565</v>
+        <v>1.2841</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3565</v>
+        <v>1.2841</v>
       </c>
       <c r="N18" t="n">
         <v>257</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9941</v>
+        <v>0.9307</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1943</v>
+        <v>0.182</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1717</v>
+        <v>-0.1818</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9941</v>
+        <v>0.9307</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9941</v>
+        <v>0.9307</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9941</v>
+        <v>0.9307</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1006</v>
+        <v>1.0343</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1006</v>
+        <v>1.0343</v>
       </c>
       <c r="N19" t="n">
         <v>264</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7329</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1433</v>
+        <v>0.1245</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2906</v>
+        <v>-0.3158</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7329</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7329</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7329</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8114</v>
+        <v>0.7075</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8114</v>
+        <v>0.7075</v>
       </c>
       <c r="N20" t="n">
         <v>264</v>
@@ -1366,93 +1366,93 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>smooya</t>
+          <t>birdfromsky</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.5201</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1181</v>
+        <v>0.1017</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3491</v>
+        <v>-0.3689</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.5201</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.5201</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.5201</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6358</v>
+        <v>0.5934</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>169</v>
+        <v>266</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6358</v>
+        <v>0.5934</v>
       </c>
       <c r="N21" t="n">
-        <v>169</v>
+        <v>266</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>birdfromsky</t>
+          <t>smooya</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5676</v>
+        <v>0.4435</v>
       </c>
       <c r="C22" t="n">
-        <v>0.111</v>
+        <v>0.0867</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3658</v>
+        <v>-0.4038</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5676</v>
+        <v>0.4435</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5676</v>
+        <v>0.4435</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5676</v>
+        <v>0.4435</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6446</v>
+        <v>0.4675</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>266</v>
+        <v>169</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6446</v>
+        <v>0.4675</v>
       </c>
       <c r="N22" t="n">
-        <v>266</v>
+        <v>169</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5387</v>
+        <v>0.4157</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1053</v>
+        <v>0.0813</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.379</v>
+        <v>-0.4164</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5387</v>
+        <v>0.4157</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5387</v>
+        <v>0.4157</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5387</v>
+        <v>0.4157</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5668</v>
+        <v>0.4382</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5668</v>
+        <v>0.4382</v>
       </c>
       <c r="N23" t="n">
         <v>169</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3791</v>
+        <v>0.3111</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0741</v>
+        <v>0.0608</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4516</v>
+        <v>-0.4641</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3791</v>
+        <v>0.3111</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3791</v>
+        <v>0.3111</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3791</v>
+        <v>0.3111</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4305</v>
+        <v>0.3549</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4305</v>
+        <v>0.3549</v>
       </c>
       <c r="N24" t="n">
         <v>292</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3157</v>
+        <v>0.291</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0617</v>
+        <v>0.0569</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4805</v>
+        <v>-0.4732</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3157</v>
+        <v>0.291</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3157</v>
+        <v>0.291</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3157</v>
+        <v>0.291</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3407</v>
+        <v>0.315</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3407</v>
+        <v>0.315</v>
       </c>
       <c r="N25" t="n">
         <v>222</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2621</v>
+        <v>0.1763</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0512</v>
+        <v>0.0345</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5049</v>
+        <v>-0.5255</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2621</v>
+        <v>0.1763</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2621</v>
+        <v>0.1763</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2621</v>
+        <v>0.1763</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2689</v>
+        <v>0.181</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2689</v>
+        <v>0.181</v>
       </c>
       <c r="N26" t="n">
         <v>154</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1413</v>
+        <v>0.0439</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0276</v>
+        <v>0.0086</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5599</v>
+        <v>-0.5858</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1413</v>
+        <v>0.0439</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1413</v>
+        <v>0.0439</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1413</v>
+        <v>0.0439</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1605</v>
+        <v>0.0501</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1605</v>
+        <v>0.0501</v>
       </c>
       <c r="N27" t="n">
         <v>266</v>
@@ -1688,47 +1688,47 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ALEX</t>
+          <t>NickelBack</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.056</v>
+        <v>0.0296</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0109</v>
+        <v>0.0058</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6497000000000001</v>
+        <v>-0.5923</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.056</v>
+        <v>0.0296</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.056</v>
+        <v>0.0296</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.056</v>
+        <v>0.0296</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0589</v>
+        <v>0.0375</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>169</v>
+        <v>440</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.0589</v>
+        <v>0.0375</v>
       </c>
       <c r="N28" t="n">
-        <v>169</v>
+        <v>440</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0733</v>
+        <v>-0.0675</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0143</v>
+        <v>-0.0132</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6576</v>
+        <v>-0.6365</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0733</v>
+        <v>-0.0675</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0733</v>
+        <v>-0.0675</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0733</v>
+        <v>-0.0675</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.08110000000000001</v>
+        <v>-0.075</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.08110000000000001</v>
+        <v>-0.075</v>
       </c>
       <c r="N29" t="n">
         <v>264</v>
@@ -1780,93 +1780,93 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FaNg</t>
+          <t>ALEX</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1365</v>
+        <v>-0.1443</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0267</v>
+        <v>-0.0282</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6863</v>
+        <v>-0.6715</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1365</v>
+        <v>-0.1443</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1365</v>
+        <v>-0.1443</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1365</v>
+        <v>-0.1443</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.14</v>
+        <v>-0.1522</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.14</v>
+        <v>-0.1522</v>
       </c>
       <c r="N30" t="n">
-        <v>154</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>NickelBack</t>
+          <t>FaNg</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.17</v>
+        <v>-0.2253</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0332</v>
+        <v>-0.044</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7016</v>
+        <v>-0.7084</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.17</v>
+        <v>-0.2253</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.17</v>
+        <v>-0.2253</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.17</v>
+        <v>-0.2253</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2137</v>
+        <v>-0.2313</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>440</v>
+        <v>154</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2137</v>
+        <v>-0.2313</v>
       </c>
       <c r="N31" t="n">
-        <v>440</v>
+        <v>154</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.2821</v>
+        <v>-0.2754</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0552</v>
+        <v>-0.0538</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7526</v>
+        <v>-0.7312</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2821</v>
+        <v>-0.2754</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.2821</v>
+        <v>-0.2754</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.2821</v>
+        <v>-0.2754</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.2894</v>
+        <v>-0.2828</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.2894</v>
+        <v>-0.2828</v>
       </c>
       <c r="N32" t="n">
         <v>154</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.2839</v>
+        <v>-0.3617</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0555</v>
+        <v>-0.0707</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7534</v>
+        <v>-0.7706</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.2839</v>
+        <v>-0.3617</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.2839</v>
+        <v>-0.3617</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.2839</v>
+        <v>-0.3617</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3064</v>
+        <v>-0.3915</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3064</v>
+        <v>-0.3915</v>
       </c>
       <c r="N33" t="n">
         <v>222</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.485</v>
+        <v>-0.5493</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0948</v>
+        <v>-0.1074</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.845</v>
+        <v>-0.856</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.485</v>
+        <v>-0.5493</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.485</v>
+        <v>-0.5493</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.485</v>
+        <v>-0.5493</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5103</v>
+        <v>-0.579</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.5103</v>
+        <v>-0.579</v>
       </c>
       <c r="N34" t="n">
         <v>169</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6473</v>
+        <v>-0.6556</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1265</v>
+        <v>-0.1282</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9189000000000001</v>
+        <v>-0.9044</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6473</v>
+        <v>-0.6556</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6473</v>
+        <v>-0.6556</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.6473</v>
+        <v>-0.6556</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7351</v>
+        <v>-0.748</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7351</v>
+        <v>-0.748</v>
       </c>
       <c r="N35" t="n">
         <v>266</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.6918</v>
+        <v>-0.7348</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1352</v>
+        <v>-0.1437</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9391</v>
+        <v>-0.9405</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.6918</v>
+        <v>-0.7348</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.6918</v>
+        <v>-0.7348</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.6918</v>
+        <v>-0.7348</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7096</v>
+        <v>-0.7544</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7096</v>
+        <v>-0.7544</v>
       </c>
       <c r="N36" t="n">
         <v>154</v>
@@ -2102,93 +2102,93 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Krad</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9103</v>
+        <v>-0.9718</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.178</v>
+        <v>-0.19</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0386</v>
+        <v>-1.0485</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9103</v>
+        <v>-0.9718</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.9103</v>
+        <v>-0.9718</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.9103</v>
+        <v>-0.9718</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.1446</v>
+        <v>-1.0518</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>440</v>
+        <v>222</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.1446</v>
+        <v>-1.0518</v>
       </c>
       <c r="N37" t="n">
-        <v>440</v>
+        <v>222</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>Krad</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0077</v>
+        <v>-0.9733000000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.197</v>
+        <v>-0.1903</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0829</v>
+        <v>-1.0492</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0077</v>
+        <v>-0.9733000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.0077</v>
+        <v>-0.9733000000000001</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.0077</v>
+        <v>-0.9733000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.0876</v>
+        <v>-1.234</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>222</v>
+        <v>440</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0876</v>
+        <v>-1.234</v>
       </c>
       <c r="N38" t="n">
-        <v>222</v>
+        <v>440</v>
       </c>
     </row>
     <row r="39">
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.2905</v>
+        <v>-1.2416</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2523</v>
+        <v>-0.2427</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2117</v>
+        <v>-1.1714</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2905</v>
+        <v>-1.2416</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.2905</v>
+        <v>-1.2416</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.2905</v>
+        <v>-1.2416</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.3579</v>
+        <v>-1.3088</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.3579</v>
+        <v>-1.3088</v>
       </c>
       <c r="N39" t="n">
         <v>169</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.3659</v>
+        <v>-1.3723</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.267</v>
+        <v>-0.2683</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.246</v>
+        <v>-1.2309</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3659</v>
+        <v>-1.3723</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.3659</v>
+        <v>-1.3723</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.3659</v>
+        <v>-1.3723</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.4742</v>
+        <v>-1.4853</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.4742</v>
+        <v>-1.4853</v>
       </c>
       <c r="N40" t="n">
         <v>222</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.9169</v>
+        <v>-1.8823</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3748</v>
+        <v>-0.368</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4968</v>
+        <v>-1.4633</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.9169</v>
+        <v>-1.8823</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.9169</v>
+        <v>-1.8823</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.9169</v>
+        <v>-1.8823</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.0689</v>
+        <v>-2.0373</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.0689</v>
+        <v>-2.0373</v>
       </c>
       <c r="N41" t="n">
         <v>222</v>
@@ -2429,10 +2429,10 @@
         <v>1.61</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2591</v>
+        <v>1.2777</v>
       </c>
       <c r="J2" t="n">
-        <v>28.9593</v>
+        <v>29.3871</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.33</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8184</v>
+        <v>0.7945</v>
       </c>
       <c r="J3" t="n">
-        <v>18.8232</v>
+        <v>18.2735</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.03</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1083</v>
+        <v>0.0877</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4909</v>
+        <v>2.0171</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0293</v>
+        <v>-0.0238</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6739000000000001</v>
+        <v>-0.5474</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.91</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3489</v>
+        <v>-0.3077</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.024699999999999</v>
+        <v>-7.0771</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4729</v>
+        <v>0.4189</v>
       </c>
       <c r="J7" t="n">
-        <v>10.8767</v>
+        <v>9.6347</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.96</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0619</v>
+        <v>-0.0509</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.4237</v>
+        <v>-1.1707</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.82</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2201</v>
+        <v>-0.2009</v>
       </c>
       <c r="J9" t="n">
-        <v>-5.0623</v>
+        <v>-4.6207</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3441</v>
+        <v>-0.3285</v>
       </c>
       <c r="J10" t="n">
-        <v>-7.9143</v>
+        <v>-7.5555</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.67</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3624</v>
+        <v>-0.348</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.3352</v>
+        <v>-8.004</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.26</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6895</v>
+        <v>0.6561</v>
       </c>
       <c r="J12" t="n">
-        <v>19.306</v>
+        <v>18.3708</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.13</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3968</v>
+        <v>0.3582</v>
       </c>
       <c r="J13" t="n">
-        <v>11.1104</v>
+        <v>10.0296</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.08</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2709</v>
+        <v>0.2368</v>
       </c>
       <c r="J14" t="n">
-        <v>7.5852</v>
+        <v>6.6304</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.08</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2709</v>
+        <v>0.2368</v>
       </c>
       <c r="J15" t="n">
-        <v>7.5852</v>
+        <v>6.6304</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0175</v>
+        <v>-0.0127</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.49</v>
+        <v>-0.3556</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.07</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1995</v>
+        <v>0.1581</v>
       </c>
       <c r="J17" t="n">
-        <v>5.586</v>
+        <v>4.4268</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.98</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0404</v>
+        <v>-0.0313</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1312</v>
+        <v>-0.8764</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0958</v>
+        <v>-0.08</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.6824</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.91</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1318</v>
+        <v>-0.1134</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.6904</v>
+        <v>-3.1752</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.88</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1654</v>
+        <v>-0.1457</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.6312</v>
+        <v>-4.0796</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.48</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6875</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>19.9375</v>
+        <v>21.2396</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.05</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1185</v>
+        <v>0.1023</v>
       </c>
       <c r="J23" t="n">
-        <v>3.4365</v>
+        <v>2.9667</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.93</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1098</v>
+        <v>-0.0924</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.1842</v>
+        <v>-2.6796</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.77</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2798</v>
+        <v>-0.2608</v>
       </c>
       <c r="J25" t="n">
-        <v>-8.1142</v>
+        <v>-7.5632</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.66</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3821</v>
+        <v>-0.37</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.0809</v>
+        <v>-10.73</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.62</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7769</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>22.5301</v>
+        <v>20.5958</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.95</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-0.0742</v>
       </c>
       <c r="J28" t="n">
-        <v>-2.6332</v>
+        <v>-2.1518</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1039</v>
+        <v>-0.0863</v>
       </c>
       <c r="J29" t="n">
-        <v>-3.0131</v>
+        <v>-2.5027</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.91</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1405</v>
+        <v>-0.1209</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.0745</v>
+        <v>-3.5061</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.88</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1745</v>
+        <v>-0.154</v>
       </c>
       <c r="J31" t="n">
-        <v>-5.0605</v>
+        <v>-4.466</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.37</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9221</v>
+        <v>0.9066</v>
       </c>
       <c r="J32" t="n">
-        <v>26.7409</v>
+        <v>26.2914</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.29</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7582</v>
+        <v>0.7286</v>
       </c>
       <c r="J33" t="n">
-        <v>21.9878</v>
+        <v>21.1294</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.08</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2735</v>
+        <v>0.2382</v>
       </c>
       <c r="J34" t="n">
-        <v>7.9315</v>
+        <v>6.9078</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2475</v>
+        <v>-0.2087</v>
       </c>
       <c r="J35" t="n">
-        <v>-7.1775</v>
+        <v>-6.0523</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.77</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6738</v>
+        <v>-0.6404</v>
       </c>
       <c r="J36" t="n">
-        <v>-19.5402</v>
+        <v>-18.5716</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.21</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4583</v>
+        <v>0.4004</v>
       </c>
       <c r="J37" t="n">
-        <v>13.2907</v>
+        <v>11.6116</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.08</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2178</v>
+        <v>0.1744</v>
       </c>
       <c r="J38" t="n">
-        <v>6.3162</v>
+        <v>5.0576</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.06</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1751</v>
+        <v>0.1368</v>
       </c>
       <c r="J39" t="n">
-        <v>5.0779</v>
+        <v>3.9672</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.92</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1212</v>
+        <v>-0.1032</v>
       </c>
       <c r="J40" t="n">
-        <v>-3.5148</v>
+        <v>-2.9928</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.58</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4522</v>
+        <v>-0.4473</v>
       </c>
       <c r="J41" t="n">
-        <v>-13.1138</v>
+        <v>-12.9717</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.3</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8186</v>
+        <v>0.796</v>
       </c>
       <c r="J42" t="n">
-        <v>24.558</v>
+        <v>23.88</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.13</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4261</v>
+        <v>0.383</v>
       </c>
       <c r="J43" t="n">
-        <v>12.783</v>
+        <v>11.49</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.02</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1035</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>3.105</v>
+        <v>2.376</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.84</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.4881</v>
+        <v>-0.4459</v>
       </c>
       <c r="J45" t="n">
-        <v>-14.643</v>
+        <v>-13.377</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.59</v>
       </c>
       <c r="I46" t="n">
-        <v>-1.0332</v>
+        <v>-1.0328</v>
       </c>
       <c r="J46" t="n">
-        <v>-30.996</v>
+        <v>-30.984</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.39</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7147</v>
+        <v>0.6569</v>
       </c>
       <c r="J47" t="n">
-        <v>21.441</v>
+        <v>19.707</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.27</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5319</v>
+        <v>0.4723</v>
       </c>
       <c r="J48" t="n">
-        <v>15.957</v>
+        <v>14.169</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.14</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3152</v>
+        <v>0.265</v>
       </c>
       <c r="J49" t="n">
-        <v>9.456</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.08</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2029</v>
+        <v>0.1639</v>
       </c>
       <c r="J50" t="n">
-        <v>6.087</v>
+        <v>4.917</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.49</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5363</v>
+        <v>-0.5442</v>
       </c>
       <c r="J51" t="n">
-        <v>-16.089</v>
+        <v>-16.326</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.65</v>
       </c>
       <c r="I52" t="n">
-        <v>1.2682</v>
+        <v>1.2864</v>
       </c>
       <c r="J52" t="n">
-        <v>26.6322</v>
+        <v>27.0144</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.58</v>
       </c>
       <c r="I53" t="n">
-        <v>1.1787</v>
+        <v>1.194</v>
       </c>
       <c r="J53" t="n">
-        <v>24.7527</v>
+        <v>25.074</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.51</v>
       </c>
       <c r="I54" t="n">
-        <v>1.0875</v>
+        <v>1.1005</v>
       </c>
       <c r="J54" t="n">
-        <v>22.8375</v>
+        <v>23.1105</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.14</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3825</v>
+        <v>0.3507</v>
       </c>
       <c r="J55" t="n">
-        <v>8.032500000000001</v>
+        <v>7.3647</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.0624</v>
+        <v>-0.0594</v>
       </c>
       <c r="J56" t="n">
-        <v>-1.3104</v>
+        <v>-1.2474</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.26</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6313</v>
+        <v>0.5949</v>
       </c>
       <c r="J57" t="n">
-        <v>13.2573</v>
+        <v>12.4929</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.75</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.2773</v>
+        <v>-0.2612</v>
       </c>
       <c r="J58" t="n">
-        <v>-5.8233</v>
+        <v>-5.4852</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.67</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.35</v>
+        <v>-0.3355</v>
       </c>
       <c r="J59" t="n">
-        <v>-7.35</v>
+        <v>-7.0455</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.66</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.359</v>
+        <v>-0.345</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.539</v>
+        <v>-7.245</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.44</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5527</v>
+        <v>-0.5587</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.6067</v>
+        <v>-11.7327</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.3</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7622</v>
+        <v>0.734</v>
       </c>
       <c r="J62" t="n">
-        <v>19.8172</v>
+        <v>19.084</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.25</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6581</v>
+        <v>0.6247</v>
       </c>
       <c r="J63" t="n">
-        <v>17.1106</v>
+        <v>16.2422</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.24</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6369</v>
+        <v>0.6027</v>
       </c>
       <c r="J64" t="n">
-        <v>16.5594</v>
+        <v>15.6702</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.18</v>
       </c>
       <c r="I65" t="n">
-        <v>0.5063</v>
+        <v>0.4694</v>
       </c>
       <c r="J65" t="n">
-        <v>13.1638</v>
+        <v>12.2044</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5947</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="J66" t="n">
-        <v>-15.4622</v>
+        <v>-14.508</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.17</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4028</v>
+        <v>0.3475</v>
       </c>
       <c r="J67" t="n">
-        <v>10.4728</v>
+        <v>9.035</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.0791</v>
       </c>
       <c r="J68" t="n">
-        <v>-2.4388</v>
+        <v>-2.0566</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.86</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1836</v>
+        <v>-0.1639</v>
       </c>
       <c r="J69" t="n">
-        <v>-4.7736</v>
+        <v>-4.2614</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.82</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2247</v>
+        <v>-0.2047</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.8422</v>
+        <v>-5.3222</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.8</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2447</v>
+        <v>-0.2249</v>
       </c>
       <c r="J71" t="n">
-        <v>-6.3622</v>
+        <v>-5.8474</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.22</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4893</v>
+        <v>0.4324</v>
       </c>
       <c r="J72" t="n">
-        <v>13.2111</v>
+        <v>11.6748</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.16</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3835</v>
+        <v>0.3288</v>
       </c>
       <c r="J73" t="n">
-        <v>10.3545</v>
+        <v>8.877599999999999</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.88</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1626</v>
+        <v>-0.1435</v>
       </c>
       <c r="J74" t="n">
-        <v>-4.3902</v>
+        <v>-3.8745</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.77</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2744</v>
+        <v>-0.2553</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.4088</v>
+        <v>-6.8931</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.58</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.448</v>
+        <v>-0.4421</v>
       </c>
       <c r="J76" t="n">
-        <v>-12.096</v>
+        <v>-11.9367</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.24</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6397</v>
+        <v>0.605</v>
       </c>
       <c r="J77" t="n">
-        <v>17.2719</v>
+        <v>16.335</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.19</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5306</v>
+        <v>0.4932</v>
       </c>
       <c r="J78" t="n">
-        <v>14.3262</v>
+        <v>13.3164</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.16</v>
       </c>
       <c r="I79" t="n">
-        <v>0.463</v>
+        <v>0.4253</v>
       </c>
       <c r="J79" t="n">
-        <v>12.501</v>
+        <v>11.4831</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.08</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2661</v>
+        <v>0.2335</v>
       </c>
       <c r="J80" t="n">
-        <v>7.1847</v>
+        <v>6.3045</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1.04</v>
       </c>
       <c r="I81" t="n">
-        <v>0.1478</v>
+        <v>0.1232</v>
       </c>
       <c r="J81" t="n">
-        <v>3.9906</v>
+        <v>3.3264</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.55</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6524</v>
+        <v>0.5816</v>
       </c>
       <c r="J82" t="n">
-        <v>14.3528</v>
+        <v>12.7952</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.52</v>
       </c>
       <c r="I83" t="n">
-        <v>0.6233</v>
+        <v>0.5533</v>
       </c>
       <c r="J83" t="n">
-        <v>13.7126</v>
+        <v>12.1726</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.32</v>
       </c>
       <c r="I84" t="n">
-        <v>0.4229</v>
+        <v>0.3634</v>
       </c>
       <c r="J84" t="n">
-        <v>9.303800000000001</v>
+        <v>7.9948</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.29</v>
       </c>
       <c r="I85" t="n">
-        <v>0.3904</v>
+        <v>0.3333</v>
       </c>
       <c r="J85" t="n">
-        <v>8.588800000000001</v>
+        <v>7.3326</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.16</v>
       </c>
       <c r="I86" t="n">
-        <v>0.2366</v>
+        <v>0.1931</v>
       </c>
       <c r="J86" t="n">
-        <v>5.2052</v>
+        <v>4.2482</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.13</v>
       </c>
       <c r="I87" t="n">
-        <v>0.2826</v>
+        <v>0.2743</v>
       </c>
       <c r="J87" t="n">
-        <v>6.2172</v>
+        <v>6.0346</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.226</v>
+        <v>-0.208</v>
       </c>
       <c r="J88" t="n">
-        <v>-4.972</v>
+        <v>-4.576</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.78</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2547</v>
+        <v>-0.2366</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.6034</v>
+        <v>-5.2052</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.71</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3205</v>
+        <v>-0.3039</v>
       </c>
       <c r="J90" t="n">
-        <v>-7.051</v>
+        <v>-6.6858</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.67</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3572</v>
+        <v>-0.3426</v>
       </c>
       <c r="J91" t="n">
-        <v>-7.8584</v>
+        <v>-7.5372</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.17</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3796</v>
+        <v>0.3242</v>
       </c>
       <c r="J92" t="n">
-        <v>13.6656</v>
+        <v>11.6712</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.07</v>
       </c>
       <c r="I93" t="n">
-        <v>0.19</v>
+        <v>0.1505</v>
       </c>
       <c r="J93" t="n">
-        <v>6.84</v>
+        <v>5.418</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.05</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1465</v>
+        <v>0.1129</v>
       </c>
       <c r="J94" t="n">
-        <v>5.274</v>
+        <v>4.0644</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.92</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1245</v>
+        <v>-0.1058</v>
       </c>
       <c r="J95" t="n">
-        <v>-4.482</v>
+        <v>-3.8088</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.84</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2128</v>
+        <v>-0.1922</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.6608</v>
+        <v>-6.9192</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.77</v>
       </c>
       <c r="I97" t="n">
-        <v>1.4817</v>
+        <v>1.5194</v>
       </c>
       <c r="J97" t="n">
-        <v>53.3412</v>
+        <v>54.6984</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.24</v>
       </c>
       <c r="I98" t="n">
-        <v>0.6405</v>
+        <v>0.6057</v>
       </c>
       <c r="J98" t="n">
-        <v>23.058</v>
+        <v>21.8052</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.07</v>
       </c>
       <c r="I99" t="n">
-        <v>0.2389</v>
+        <v>0.2076</v>
       </c>
       <c r="J99" t="n">
-        <v>8.6004</v>
+        <v>7.4736</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.9</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3689</v>
+        <v>-0.3268</v>
       </c>
       <c r="J100" t="n">
-        <v>-13.2804</v>
+        <v>-11.7648</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.71</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.8136</v>
+        <v>-0.7927999999999999</v>
       </c>
       <c r="J101" t="n">
-        <v>-29.2896</v>
+        <v>-28.5408</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.46</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6002999999999999</v>
+        <v>0.5295</v>
       </c>
       <c r="J102" t="n">
-        <v>17.4087</v>
+        <v>15.3555</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.32</v>
       </c>
       <c r="I103" t="n">
-        <v>0.4477</v>
+        <v>0.3816</v>
       </c>
       <c r="J103" t="n">
-        <v>12.9833</v>
+        <v>11.0664</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.07</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1338</v>
+        <v>0.1019</v>
       </c>
       <c r="J104" t="n">
-        <v>3.8802</v>
+        <v>2.9551</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.96</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.0809</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="J105" t="n">
-        <v>-2.3461</v>
+        <v>-1.8908</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.72</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.338</v>
+        <v>-0.3235</v>
       </c>
       <c r="J106" t="n">
-        <v>-9.802</v>
+        <v>-9.381500000000001</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.3</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4645</v>
+        <v>0.4692</v>
       </c>
       <c r="J107" t="n">
-        <v>13.4705</v>
+        <v>13.6068</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.25</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4019</v>
+        <v>0.3989</v>
       </c>
       <c r="J108" t="n">
-        <v>11.6551</v>
+        <v>11.5681</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.0007</v>
+        <v>-0.0003</v>
       </c>
       <c r="J109" t="n">
-        <v>-0.0203</v>
+        <v>-0.008699999999999999</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.88</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1707</v>
+        <v>-0.1503</v>
       </c>
       <c r="J110" t="n">
-        <v>-4.9503</v>
+        <v>-4.3587</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.65</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3944</v>
+        <v>-0.3838</v>
       </c>
       <c r="J111" t="n">
-        <v>-11.4376</v>
+        <v>-11.1302</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1</v>
       </c>
       <c r="I112" t="n">
-        <v>0.0282</v>
+        <v>0.0225</v>
       </c>
       <c r="J112" t="n">
-        <v>0.6768</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.91</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1232</v>
+        <v>-0.1079</v>
       </c>
       <c r="J113" t="n">
-        <v>-2.9568</v>
+        <v>-2.5896</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.88</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1572</v>
+        <v>-0.1403</v>
       </c>
       <c r="J114" t="n">
-        <v>-3.7728</v>
+        <v>-3.3672</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.75</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2856</v>
+        <v>-0.2675</v>
       </c>
       <c r="J115" t="n">
-        <v>-6.8544</v>
+        <v>-6.42</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.68</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3507</v>
+        <v>-0.3356</v>
       </c>
       <c r="J116" t="n">
-        <v>-8.4168</v>
+        <v>-8.054399999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.64</v>
       </c>
       <c r="I117" t="n">
-        <v>1.2652</v>
+        <v>1.2828</v>
       </c>
       <c r="J117" t="n">
-        <v>30.3648</v>
+        <v>30.7872</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.38</v>
       </c>
       <c r="I118" t="n">
-        <v>0.8884</v>
+        <v>0.8753</v>
       </c>
       <c r="J118" t="n">
-        <v>21.3216</v>
+        <v>21.0072</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.33</v>
       </c>
       <c r="I119" t="n">
-        <v>0.7941</v>
+        <v>0.7753</v>
       </c>
       <c r="J119" t="n">
-        <v>19.0584</v>
+        <v>18.6072</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.31</v>
       </c>
       <c r="I120" t="n">
-        <v>0.7564</v>
+        <v>0.7355</v>
       </c>
       <c r="J120" t="n">
-        <v>18.1536</v>
+        <v>17.652</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.95</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2576</v>
+        <v>-0.2235</v>
       </c>
       <c r="J121" t="n">
-        <v>-6.1824</v>
+        <v>-5.364</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.09</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2505</v>
+        <v>0.204</v>
       </c>
       <c r="J122" t="n">
-        <v>7.2645</v>
+        <v>5.916</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.02</v>
       </c>
       <c r="I123" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0624</v>
       </c>
       <c r="J123" t="n">
-        <v>2.523</v>
+        <v>1.8096</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.01</v>
       </c>
       <c r="I124" t="n">
-        <v>0.0561</v>
+        <v>0.0382</v>
       </c>
       <c r="J124" t="n">
-        <v>1.6269</v>
+        <v>1.1078</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.98</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.0369</v>
+        <v>-0.0288</v>
       </c>
       <c r="J125" t="n">
-        <v>-1.0701</v>
+        <v>-0.8352000000000001</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.48</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5334</v>
+        <v>-0.5387</v>
       </c>
       <c r="J126" t="n">
-        <v>-15.4686</v>
+        <v>-15.6223</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.94</v>
       </c>
       <c r="I127" t="n">
-        <v>1.6693</v>
+        <v>1.7224</v>
       </c>
       <c r="J127" t="n">
-        <v>48.4097</v>
+        <v>49.9496</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.36</v>
       </c>
       <c r="I128" t="n">
-        <v>0.8681</v>
+        <v>0.8491</v>
       </c>
       <c r="J128" t="n">
-        <v>25.1749</v>
+        <v>24.6239</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.05</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1661</v>
+        <v>0.1401</v>
       </c>
       <c r="J129" t="n">
-        <v>4.8169</v>
+        <v>4.0629</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.01</v>
       </c>
       <c r="I130" t="n">
-        <v>0.0228</v>
+        <v>0.0129</v>
       </c>
       <c r="J130" t="n">
-        <v>0.6612</v>
+        <v>0.3741</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.74</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.7624</v>
+        <v>-0.7392</v>
       </c>
       <c r="J131" t="n">
-        <v>-22.1096</v>
+        <v>-21.4368</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.31</v>
       </c>
       <c r="I132" t="n">
-        <v>0.7836</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="J132" t="n">
-        <v>23.508</v>
+        <v>22.698</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.28</v>
       </c>
       <c r="I133" t="n">
-        <v>0.7218</v>
+        <v>0.6912</v>
       </c>
       <c r="J133" t="n">
-        <v>21.654</v>
+        <v>20.736</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.25</v>
       </c>
       <c r="I134" t="n">
-        <v>0.6589</v>
+        <v>0.6254</v>
       </c>
       <c r="J134" t="n">
-        <v>19.767</v>
+        <v>18.762</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.99</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.0848</v>
+        <v>-0.0639</v>
       </c>
       <c r="J135" t="n">
-        <v>-2.544</v>
+        <v>-1.917</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.93</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2885</v>
+        <v>-0.2484</v>
       </c>
       <c r="J136" t="n">
-        <v>-8.654999999999999</v>
+        <v>-7.452</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.24</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5145</v>
+        <v>0.4565</v>
       </c>
       <c r="J137" t="n">
-        <v>15.435</v>
+        <v>13.695</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.02</v>
       </c>
       <c r="I138" t="n">
-        <v>0.0805</v>
+        <v>0.0572</v>
       </c>
       <c r="J138" t="n">
-        <v>2.415</v>
+        <v>1.716</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.99</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.0222</v>
+        <v>-0.0165</v>
       </c>
       <c r="J139" t="n">
-        <v>-0.666</v>
+        <v>-0.495</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.92</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1197</v>
+        <v>-0.1022</v>
       </c>
       <c r="J140" t="n">
-        <v>-3.591</v>
+        <v>-3.066</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.58</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4505</v>
+        <v>-0.4451</v>
       </c>
       <c r="J141" t="n">
-        <v>-13.515</v>
+        <v>-13.353</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.84</v>
       </c>
       <c r="I142" t="n">
-        <v>1.5421</v>
+        <v>1.581</v>
       </c>
       <c r="J142" t="n">
-        <v>33.9262</v>
+        <v>34.782</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.2</v>
       </c>
       <c r="I143" t="n">
-        <v>0.5425</v>
+        <v>0.5098</v>
       </c>
       <c r="J143" t="n">
-        <v>11.935</v>
+        <v>11.2156</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.1</v>
       </c>
       <c r="I144" t="n">
-        <v>0.3057</v>
+        <v>0.2735</v>
       </c>
       <c r="J144" t="n">
-        <v>6.7254</v>
+        <v>6.017</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.02</v>
       </c>
       <c r="I145" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.0466</v>
       </c>
       <c r="J145" t="n">
-        <v>1.3816</v>
+        <v>1.0252</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.98</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.1398</v>
+        <v>-0.1128</v>
       </c>
       <c r="J146" t="n">
-        <v>-3.0756</v>
+        <v>-2.4816</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.13</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3437</v>
+        <v>0.2926</v>
       </c>
       <c r="J147" t="n">
-        <v>7.5614</v>
+        <v>6.4372</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.97</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.0472</v>
+        <v>-0.0378</v>
       </c>
       <c r="J148" t="n">
-        <v>-1.0384</v>
+        <v>-0.8316</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.9</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1372</v>
+        <v>-0.1207</v>
       </c>
       <c r="J149" t="n">
-        <v>-3.0184</v>
+        <v>-2.6554</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3441</v>
+        <v>-0.3285</v>
       </c>
       <c r="J150" t="n">
-        <v>-7.5702</v>
+        <v>-7.227</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.65</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3805</v>
+        <v>-0.3675</v>
       </c>
       <c r="J151" t="n">
-        <v>-8.371</v>
+        <v>-8.085000000000001</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.88</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.1079</v>
+        <v>-0.0858</v>
       </c>
       <c r="J152" t="n">
-        <v>-2.3738</v>
+        <v>-1.8876</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.67</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.3322</v>
+        <v>-0.3223</v>
       </c>
       <c r="J153" t="n">
-        <v>-7.3084</v>
+        <v>-7.0906</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.54</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.4453</v>
+        <v>-0.4392</v>
       </c>
       <c r="J154" t="n">
-        <v>-9.7966</v>
+        <v>-9.6624</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.46</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.5155</v>
       </c>
       <c r="J155" t="n">
-        <v>-11.3432</v>
+        <v>-11.341</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.46</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.5155</v>
       </c>
       <c r="J156" t="n">
-        <v>-11.3432</v>
+        <v>-11.341</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.77</v>
       </c>
       <c r="I157" t="n">
-        <v>1.4029</v>
+        <v>1.4284</v>
       </c>
       <c r="J157" t="n">
-        <v>30.8638</v>
+        <v>31.4248</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.69</v>
       </c>
       <c r="I158" t="n">
-        <v>1.3049</v>
+        <v>1.3258</v>
       </c>
       <c r="J158" t="n">
-        <v>28.7078</v>
+        <v>29.1676</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.44</v>
       </c>
       <c r="I159" t="n">
-        <v>0.9792</v>
+        <v>0.9826</v>
       </c>
       <c r="J159" t="n">
-        <v>21.5424</v>
+        <v>21.6172</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.24</v>
       </c>
       <c r="I160" t="n">
-        <v>0.5955</v>
+        <v>0.5708</v>
       </c>
       <c r="J160" t="n">
-        <v>13.101</v>
+        <v>12.5576</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.16</v>
       </c>
       <c r="I161" t="n">
-        <v>0.4176</v>
+        <v>0.3861</v>
       </c>
       <c r="J161" t="n">
-        <v>9.187200000000001</v>
+        <v>8.494199999999999</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.26</v>
       </c>
       <c r="I162" t="n">
-        <v>0.3826</v>
+        <v>0.3203</v>
       </c>
       <c r="J162" t="n">
-        <v>10.7128</v>
+        <v>8.968400000000001</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.11</v>
       </c>
       <c r="I163" t="n">
-        <v>0.193</v>
+        <v>0.1509</v>
       </c>
       <c r="J163" t="n">
-        <v>5.404</v>
+        <v>4.2252</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.1</v>
       </c>
       <c r="I164" t="n">
-        <v>0.1791</v>
+        <v>0.1391</v>
       </c>
       <c r="J164" t="n">
-        <v>5.0148</v>
+        <v>3.8948</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.02</v>
       </c>
       <c r="I165" t="n">
-        <v>0.0486</v>
+        <v>0.0338</v>
       </c>
       <c r="J165" t="n">
-        <v>1.3608</v>
+        <v>0.9464</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.91</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.1422</v>
+        <v>-0.1225</v>
       </c>
       <c r="J166" t="n">
-        <v>-3.9816</v>
+        <v>-3.43</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.29</v>
       </c>
       <c r="I167" t="n">
-        <v>0.4698</v>
+        <v>0.4775</v>
       </c>
       <c r="J167" t="n">
-        <v>13.1544</v>
+        <v>13.37</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.1</v>
       </c>
       <c r="I168" t="n">
-        <v>0.2075</v>
+        <v>0.1908</v>
       </c>
       <c r="J168" t="n">
-        <v>5.81</v>
+        <v>5.3424</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.91</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1306</v>
+        <v>-0.1126</v>
       </c>
       <c r="J169" t="n">
-        <v>-3.6568</v>
+        <v>-3.1528</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.86</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1855</v>
+        <v>-0.1655</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.194</v>
+        <v>-4.634</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.54</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4842</v>
+        <v>-0.483</v>
       </c>
       <c r="J171" t="n">
-        <v>-13.5576</v>
+        <v>-13.524</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>0.98</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.0011</v>
+        <v>0.0158</v>
       </c>
       <c r="J172" t="n">
-        <v>-0.022</v>
+        <v>0.316</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.96</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.0332</v>
+        <v>-0.0198</v>
       </c>
       <c r="J173" t="n">
-        <v>-0.664</v>
+        <v>-0.396</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.66</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3536</v>
+        <v>-0.3403</v>
       </c>
       <c r="J174" t="n">
-        <v>-7.072</v>
+        <v>-6.806</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.51</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4865</v>
+        <v>-0.4833</v>
       </c>
       <c r="J175" t="n">
-        <v>-9.73</v>
+        <v>-9.666</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.44</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5476</v>
+        <v>-0.5522</v>
       </c>
       <c r="J176" t="n">
-        <v>-10.952</v>
+        <v>-11.044</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.72</v>
       </c>
       <c r="I177" t="n">
-        <v>1.3551</v>
+        <v>1.3773</v>
       </c>
       <c r="J177" t="n">
-        <v>27.102</v>
+        <v>27.546</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.42</v>
       </c>
       <c r="I178" t="n">
-        <v>0.9527</v>
+        <v>0.9488</v>
       </c>
       <c r="J178" t="n">
-        <v>19.054</v>
+        <v>18.976</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.33</v>
       </c>
       <c r="I179" t="n">
-        <v>0.7884</v>
+        <v>0.7722</v>
       </c>
       <c r="J179" t="n">
-        <v>15.768</v>
+        <v>15.444</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.26</v>
       </c>
       <c r="I180" t="n">
-        <v>0.6486</v>
+        <v>0.6251</v>
       </c>
       <c r="J180" t="n">
-        <v>12.972</v>
+        <v>12.502</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.18</v>
       </c>
       <c r="I181" t="n">
-        <v>0.4754</v>
+        <v>0.4453</v>
       </c>
       <c r="J181" t="n">
-        <v>9.507999999999999</v>
+        <v>8.906000000000001</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>0.98</v>
       </c>
       <c r="I182" t="n">
-        <v>0.0322</v>
+        <v>0.0575</v>
       </c>
       <c r="J182" t="n">
-        <v>0.6762</v>
+        <v>1.2075</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.63</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.3727</v>
+        <v>-0.3622</v>
       </c>
       <c r="J183" t="n">
-        <v>-7.8267</v>
+        <v>-7.6062</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.6</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.3986</v>
+        <v>-0.389</v>
       </c>
       <c r="J184" t="n">
-        <v>-8.3706</v>
+        <v>-8.169</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.58</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4161</v>
+        <v>-0.4073</v>
       </c>
       <c r="J185" t="n">
-        <v>-8.738099999999999</v>
+        <v>-8.5533</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.43</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.548</v>
+        <v>-0.552</v>
       </c>
       <c r="J186" t="n">
-        <v>-11.508</v>
+        <v>-11.592</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.63</v>
       </c>
       <c r="I187" t="n">
-        <v>1.235</v>
+        <v>1.2529</v>
       </c>
       <c r="J187" t="n">
-        <v>25.935</v>
+        <v>26.3109</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.52</v>
       </c>
       <c r="I188" t="n">
-        <v>1.0946</v>
+        <v>1.1095</v>
       </c>
       <c r="J188" t="n">
-        <v>22.9866</v>
+        <v>23.2995</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.41</v>
       </c>
       <c r="I189" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.928</v>
       </c>
       <c r="J189" t="n">
-        <v>19.572</v>
+        <v>19.488</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.33</v>
       </c>
       <c r="I190" t="n">
-        <v>0.7829</v>
+        <v>0.7681</v>
       </c>
       <c r="J190" t="n">
-        <v>16.4409</v>
+        <v>16.1301</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.24</v>
       </c>
       <c r="I191" t="n">
-        <v>0.6004</v>
+        <v>0.5755</v>
       </c>
       <c r="J191" t="n">
-        <v>12.6084</v>
+        <v>12.0855</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.41</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5749</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="J192" t="n">
-        <v>17.247</v>
+        <v>15.228</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.04</v>
       </c>
       <c r="I193" t="n">
-        <v>0.095</v>
+        <v>0.0678</v>
       </c>
       <c r="J193" t="n">
-        <v>2.85</v>
+        <v>2.034</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.91</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1336</v>
+        <v>-0.1148</v>
       </c>
       <c r="J194" t="n">
-        <v>-4.008</v>
+        <v>-3.444</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2404</v>
+        <v>-0.2202</v>
       </c>
       <c r="J195" t="n">
-        <v>-7.212</v>
+        <v>-6.606</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.72</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3272</v>
+        <v>-0.3108</v>
       </c>
       <c r="J196" t="n">
-        <v>-9.816000000000001</v>
+        <v>-9.324</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.28</v>
       </c>
       <c r="I197" t="n">
-        <v>0.4342</v>
+        <v>0.4349</v>
       </c>
       <c r="J197" t="n">
-        <v>13.026</v>
+        <v>13.047</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.19</v>
       </c>
       <c r="I198" t="n">
-        <v>0.319</v>
+        <v>0.3085</v>
       </c>
       <c r="J198" t="n">
-        <v>9.57</v>
+        <v>9.255000000000001</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.1</v>
       </c>
       <c r="I199" t="n">
-        <v>0.1922</v>
+        <v>0.1763</v>
       </c>
       <c r="J199" t="n">
-        <v>5.766</v>
+        <v>5.289</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.89</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.162</v>
+        <v>-0.1418</v>
       </c>
       <c r="J200" t="n">
-        <v>-4.86</v>
+        <v>-4.254</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.76</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.2953</v>
+        <v>-0.2774</v>
       </c>
       <c r="J201" t="n">
-        <v>-8.859</v>
+        <v>-8.321999999999999</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.01</v>
       </c>
       <c r="I202" t="n">
-        <v>0.0963</v>
+        <v>0.0781</v>
       </c>
       <c r="J202" t="n">
-        <v>2.1186</v>
+        <v>1.7182</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.92</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.1007</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="J203" t="n">
-        <v>-2.2154</v>
+        <v>-1.903</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.84</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1917</v>
+        <v>-0.1756</v>
       </c>
       <c r="J204" t="n">
-        <v>-4.2174</v>
+        <v>-3.8632</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.6</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4147</v>
+        <v>-0.4044</v>
       </c>
       <c r="J205" t="n">
-        <v>-9.1234</v>
+        <v>-8.896800000000001</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.49</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5112</v>
+        <v>-0.5115</v>
       </c>
       <c r="J206" t="n">
-        <v>-11.2464</v>
+        <v>-11.253</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.77</v>
       </c>
       <c r="I207" t="n">
-        <v>1.4194</v>
+        <v>1.4455</v>
       </c>
       <c r="J207" t="n">
-        <v>31.2268</v>
+        <v>31.801</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.68</v>
       </c>
       <c r="I208" t="n">
-        <v>1.3071</v>
+        <v>1.3269</v>
       </c>
       <c r="J208" t="n">
-        <v>28.7562</v>
+        <v>29.1918</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.67</v>
       </c>
       <c r="I209" t="n">
-        <v>1.2945</v>
+        <v>1.3138</v>
       </c>
       <c r="J209" t="n">
-        <v>28.479</v>
+        <v>28.9036</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.87</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.4846</v>
+        <v>-0.4496</v>
       </c>
       <c r="J210" t="n">
-        <v>-10.6612</v>
+        <v>-9.8912</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.86</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5094</v>
+        <v>-0.4751</v>
       </c>
       <c r="J211" t="n">
-        <v>-11.2068</v>
+        <v>-10.4522</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.94</v>
       </c>
       <c r="I212" t="n">
-        <v>1.593</v>
+        <v>1.6315</v>
       </c>
       <c r="J212" t="n">
-        <v>28.674</v>
+        <v>29.367</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.75</v>
       </c>
       <c r="I213" t="n">
-        <v>1.3682</v>
+        <v>1.3931</v>
       </c>
       <c r="J213" t="n">
-        <v>24.6276</v>
+        <v>25.0758</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.45</v>
       </c>
       <c r="I214" t="n">
-        <v>0.9885</v>
+        <v>0.9961</v>
       </c>
       <c r="J214" t="n">
-        <v>17.793</v>
+        <v>17.9298</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.28</v>
       </c>
       <c r="I215" t="n">
-        <v>0.6689000000000001</v>
+        <v>0.649</v>
       </c>
       <c r="J215" t="n">
-        <v>12.0402</v>
+        <v>11.682</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.23</v>
       </c>
       <c r="I216" t="n">
-        <v>0.5643</v>
+        <v>0.5383</v>
       </c>
       <c r="J216" t="n">
-        <v>10.1574</v>
+        <v>9.689399999999999</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.88</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.0984</v>
+        <v>-0.0731</v>
       </c>
       <c r="J217" t="n">
-        <v>-1.7712</v>
+        <v>-1.3158</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.66</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.3365</v>
+        <v>-0.3274</v>
       </c>
       <c r="J218" t="n">
-        <v>-6.057</v>
+        <v>-5.8932</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.62</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.3737</v>
+        <v>-0.3662</v>
       </c>
       <c r="J219" t="n">
-        <v>-6.7266</v>
+        <v>-6.5916</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.42</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.547</v>
+        <v>-0.5505</v>
       </c>
       <c r="J220" t="n">
-        <v>-9.846</v>
+        <v>-9.909000000000001</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.3</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6535</v>
+        <v>-0.6739000000000001</v>
       </c>
       <c r="J221" t="n">
-        <v>-11.763</v>
+        <v>-12.1302</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.03</v>
       </c>
       <c r="I222" t="n">
-        <v>0.0941</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="J222" t="n">
-        <v>2.7289</v>
+        <v>2.2968</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.95</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.0655</v>
       </c>
       <c r="J223" t="n">
-        <v>-2.2678</v>
+        <v>-1.8995</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.92</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1159</v>
+        <v>-0.1002</v>
       </c>
       <c r="J224" t="n">
-        <v>-3.3611</v>
+        <v>-2.9058</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.86</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1813</v>
+        <v>-0.1622</v>
       </c>
       <c r="J225" t="n">
-        <v>-5.2577</v>
+        <v>-4.7038</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3464</v>
+        <v>-0.3309</v>
       </c>
       <c r="J226" t="n">
-        <v>-10.0456</v>
+        <v>-9.5961</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.33</v>
       </c>
       <c r="I227" t="n">
-        <v>0.455</v>
+        <v>0.3886</v>
       </c>
       <c r="J227" t="n">
-        <v>13.195</v>
+        <v>11.2694</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.31</v>
       </c>
       <c r="I228" t="n">
-        <v>0.4326</v>
+        <v>0.3675</v>
       </c>
       <c r="J228" t="n">
-        <v>12.5454</v>
+        <v>10.6575</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.29</v>
       </c>
       <c r="I229" t="n">
-        <v>0.4099</v>
+        <v>0.3463</v>
       </c>
       <c r="J229" t="n">
-        <v>11.8871</v>
+        <v>10.0427</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.89</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.1694</v>
+        <v>-0.1493</v>
       </c>
       <c r="J230" t="n">
-        <v>-4.9126</v>
+        <v>-4.3297</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.84</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2232</v>
+        <v>-0.2032</v>
       </c>
       <c r="J231" t="n">
-        <v>-6.4728</v>
+        <v>-5.8928</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.32</v>
       </c>
       <c r="I232" t="n">
-        <v>0.8201000000000001</v>
+        <v>0.795</v>
       </c>
       <c r="J232" t="n">
-        <v>28.7035</v>
+        <v>27.825</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.21</v>
       </c>
       <c r="I233" t="n">
-        <v>0.585</v>
+        <v>0.5467</v>
       </c>
       <c r="J233" t="n">
-        <v>20.475</v>
+        <v>19.1345</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.11</v>
       </c>
       <c r="I234" t="n">
-        <v>0.3501</v>
+        <v>0.3117</v>
       </c>
       <c r="J234" t="n">
-        <v>12.2535</v>
+        <v>10.9095</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.2479</v>
+        <v>-0.2091</v>
       </c>
       <c r="J235" t="n">
-        <v>-8.676500000000001</v>
+        <v>-7.3185</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.88</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4124</v>
+        <v>-0.3695</v>
       </c>
       <c r="J236" t="n">
-        <v>-14.434</v>
+        <v>-12.9325</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.07</v>
       </c>
       <c r="I237" t="n">
-        <v>0.1946</v>
+        <v>0.154</v>
       </c>
       <c r="J237" t="n">
-        <v>6.811</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.06</v>
       </c>
       <c r="I238" t="n">
-        <v>0.173</v>
+        <v>0.1351</v>
       </c>
       <c r="J238" t="n">
-        <v>6.055</v>
+        <v>4.7285</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.05</v>
       </c>
       <c r="I239" t="n">
-        <v>0.1506</v>
+        <v>0.1158</v>
       </c>
       <c r="J239" t="n">
-        <v>5.271</v>
+        <v>4.053</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.91</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.1339</v>
+        <v>-0.115</v>
       </c>
       <c r="J240" t="n">
-        <v>-4.6865</v>
+        <v>-4.025</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.82</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2307</v>
+        <v>-0.2104</v>
       </c>
       <c r="J241" t="n">
-        <v>-8.0745</v>
+        <v>-7.364</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.53</v>
       </c>
       <c r="I242" t="n">
-        <v>1.1951</v>
+        <v>1.2159</v>
       </c>
       <c r="J242" t="n">
-        <v>50.1942</v>
+        <v>51.0678</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.0032</v>
+        <v>-0.0016</v>
       </c>
       <c r="J243" t="n">
-        <v>-0.1344</v>
+        <v>-0.0672</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.95</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.205</v>
+        <v>-0.1695</v>
       </c>
       <c r="J244" t="n">
-        <v>-8.609999999999999</v>
+        <v>-7.119</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2353</v>
+        <v>-0.1976</v>
       </c>
       <c r="J245" t="n">
-        <v>-9.8826</v>
+        <v>-8.299200000000001</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.71</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.7929</v>
+        <v>-0.7674</v>
       </c>
       <c r="J246" t="n">
-        <v>-33.3018</v>
+        <v>-32.2308</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.43</v>
       </c>
       <c r="I247" t="n">
-        <v>0.7739</v>
+        <v>0.7184</v>
       </c>
       <c r="J247" t="n">
-        <v>32.5038</v>
+        <v>30.1728</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.12</v>
       </c>
       <c r="I248" t="n">
-        <v>0.2793</v>
+        <v>0.232</v>
       </c>
       <c r="J248" t="n">
-        <v>11.7306</v>
+        <v>9.744</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.02</v>
       </c>
       <c r="I249" t="n">
-        <v>0.0664</v>
+        <v>0.0488</v>
       </c>
       <c r="J249" t="n">
-        <v>2.7888</v>
+        <v>2.0496</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.01</v>
       </c>
       <c r="I250" t="n">
-        <v>0.0361</v>
+        <v>0.0252</v>
       </c>
       <c r="J250" t="n">
-        <v>1.5162</v>
+        <v>1.0584</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.78</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2784</v>
+        <v>-0.2598</v>
       </c>
       <c r="J251" t="n">
-        <v>-11.6928</v>
+        <v>-10.9116</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.78</v>
       </c>
       <c r="I252" t="n">
-        <v>1.4839</v>
+        <v>1.52</v>
       </c>
       <c r="J252" t="n">
-        <v>38.5814</v>
+        <v>39.52</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.06</v>
       </c>
       <c r="I253" t="n">
-        <v>0.2048</v>
+        <v>0.1761</v>
       </c>
       <c r="J253" t="n">
-        <v>5.3248</v>
+        <v>4.5786</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.04</v>
       </c>
       <c r="I254" t="n">
-        <v>0.143</v>
+        <v>0.119</v>
       </c>
       <c r="J254" t="n">
-        <v>3.718</v>
+        <v>3.094</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.02</v>
       </c>
       <c r="I255" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0566</v>
       </c>
       <c r="J255" t="n">
-        <v>1.8954</v>
+        <v>1.4716</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.95</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.2319</v>
+        <v>-0.195</v>
       </c>
       <c r="J256" t="n">
-        <v>-6.0294</v>
+        <v>-5.07</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.27</v>
       </c>
       <c r="I257" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.4833</v>
       </c>
       <c r="J257" t="n">
-        <v>14.1128</v>
+        <v>12.5658</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.17</v>
       </c>
       <c r="I258" t="n">
-        <v>0.3764</v>
+        <v>0.3213</v>
       </c>
       <c r="J258" t="n">
-        <v>9.7864</v>
+        <v>8.3538</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.09</v>
       </c>
       <c r="I259" t="n">
-        <v>0.2285</v>
+        <v>0.1849</v>
       </c>
       <c r="J259" t="n">
-        <v>5.941</v>
+        <v>4.8074</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.96</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.0745</v>
+        <v>-0.0597</v>
       </c>
       <c r="J260" t="n">
-        <v>-1.937</v>
+        <v>-1.5522</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.64</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4041</v>
+        <v>-0.3946</v>
       </c>
       <c r="J261" t="n">
-        <v>-10.5066</v>
+        <v>-10.2596</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.62</v>
       </c>
       <c r="I262" t="n">
-        <v>1.2603</v>
+        <v>1.278</v>
       </c>
       <c r="J262" t="n">
-        <v>34.0281</v>
+        <v>34.506</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.5</v>
       </c>
       <c r="I263" t="n">
-        <v>1.0992</v>
+        <v>1.1103</v>
       </c>
       <c r="J263" t="n">
-        <v>29.6784</v>
+        <v>29.9781</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.22</v>
       </c>
       <c r="I264" t="n">
-        <v>0.5854</v>
+        <v>0.5532</v>
       </c>
       <c r="J264" t="n">
-        <v>15.8058</v>
+        <v>14.9364</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.97</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.1757</v>
+        <v>-0.1446</v>
       </c>
       <c r="J265" t="n">
-        <v>-4.7439</v>
+        <v>-3.9042</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.6063</v>
+        <v>-0.572</v>
       </c>
       <c r="J266" t="n">
-        <v>-16.3701</v>
+        <v>-15.444</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.75</v>
       </c>
       <c r="I267" t="n">
-        <v>1.1838</v>
+        <v>1.1799</v>
       </c>
       <c r="J267" t="n">
-        <v>31.9626</v>
+        <v>31.8573</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.92</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1238</v>
+        <v>-0.1052</v>
       </c>
       <c r="J268" t="n">
-        <v>-3.3426</v>
+        <v>-2.8404</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.89</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1584</v>
+        <v>-0.1384</v>
       </c>
       <c r="J269" t="n">
-        <v>-4.2768</v>
+        <v>-3.7368</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.2426</v>
+        <v>-0.2225</v>
       </c>
       <c r="J270" t="n">
-        <v>-6.5502</v>
+        <v>-6.0075</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.64</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4021</v>
+        <v>-0.3921</v>
       </c>
       <c r="J271" t="n">
-        <v>-10.8567</v>
+        <v>-10.5867</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.09</v>
       </c>
       <c r="I272" t="n">
-        <v>0.1769</v>
+        <v>0.161</v>
       </c>
       <c r="J272" t="n">
-        <v>6.1915</v>
+        <v>5.635</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.06</v>
       </c>
       <c r="I273" t="n">
-        <v>0.1288</v>
+        <v>0.1138</v>
       </c>
       <c r="J273" t="n">
-        <v>4.508</v>
+        <v>3.983</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.06</v>
       </c>
       <c r="I274" t="n">
-        <v>0.1288</v>
+        <v>0.1138</v>
       </c>
       <c r="J274" t="n">
-        <v>4.508</v>
+        <v>3.983</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.05</v>
       </c>
       <c r="I275" t="n">
-        <v>0.1118</v>
+        <v>0.0975</v>
       </c>
       <c r="J275" t="n">
-        <v>3.913</v>
+        <v>3.4125</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.96</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.0759</v>
+        <v>-0.0608</v>
       </c>
       <c r="J276" t="n">
-        <v>-2.6565</v>
+        <v>-2.128</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.24</v>
       </c>
       <c r="I277" t="n">
-        <v>0.3594</v>
+        <v>0.2988</v>
       </c>
       <c r="J277" t="n">
-        <v>12.579</v>
+        <v>10.458</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.23</v>
       </c>
       <c r="I278" t="n">
-        <v>0.3474</v>
+        <v>0.2878</v>
       </c>
       <c r="J278" t="n">
-        <v>12.159</v>
+        <v>10.073</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.07</v>
       </c>
       <c r="I279" t="n">
-        <v>0.1359</v>
+        <v>0.103</v>
       </c>
       <c r="J279" t="n">
-        <v>4.7565</v>
+        <v>3.605</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.0049</v>
+        <v>-0.0032</v>
       </c>
       <c r="J280" t="n">
-        <v>-0.1715</v>
+        <v>-0.112</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.84</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.2186</v>
+        <v>-0.1982</v>
       </c>
       <c r="J281" t="n">
-        <v>-7.651</v>
+        <v>-6.937</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.95</v>
       </c>
       <c r="I282" t="n">
-        <v>1.6377</v>
+        <v>1.6813</v>
       </c>
       <c r="J282" t="n">
-        <v>39.3048</v>
+        <v>40.3512</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.44</v>
       </c>
       <c r="I283" t="n">
-        <v>0.9871</v>
+        <v>0.9874000000000001</v>
       </c>
       <c r="J283" t="n">
-        <v>23.6904</v>
+        <v>23.6976</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.41</v>
       </c>
       <c r="I284" t="n">
-        <v>0.9365</v>
+        <v>0.9302</v>
       </c>
       <c r="J284" t="n">
-        <v>22.476</v>
+        <v>22.3248</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.04</v>
       </c>
       <c r="I285" t="n">
-        <v>0.1096</v>
+        <v>0.0847</v>
       </c>
       <c r="J285" t="n">
-        <v>2.6304</v>
+        <v>2.0328</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>1.02</v>
       </c>
       <c r="I286" t="n">
-        <v>0.0394</v>
+        <v>0.0213</v>
       </c>
       <c r="J286" t="n">
-        <v>0.9456</v>
+        <v>0.5112</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.18</v>
       </c>
       <c r="I287" t="n">
-        <v>0.4943</v>
+        <v>0.4546</v>
       </c>
       <c r="J287" t="n">
-        <v>11.8632</v>
+        <v>10.9104</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.88</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.1428</v>
+        <v>-0.1274</v>
       </c>
       <c r="J288" t="n">
-        <v>-3.4272</v>
+        <v>-3.0576</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.8</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.2285</v>
+        <v>-0.2129</v>
       </c>
       <c r="J289" t="n">
-        <v>-5.484</v>
+        <v>-5.1096</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.55</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.4551</v>
+        <v>-0.4486</v>
       </c>
       <c r="J290" t="n">
-        <v>-10.9224</v>
+        <v>-10.7664</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.29</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.6788999999999999</v>
+        <v>-0.7071</v>
       </c>
       <c r="J291" t="n">
-        <v>-16.2936</v>
+        <v>-16.9704</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.21</v>
       </c>
       <c r="I292" t="n">
-        <v>0.4759</v>
+        <v>0.4196</v>
       </c>
       <c r="J292" t="n">
-        <v>10.9457</v>
+        <v>9.6508</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>0.96</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.0665</v>
+        <v>-0.0547</v>
       </c>
       <c r="J293" t="n">
-        <v>-1.5295</v>
+        <v>-1.2581</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.88</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.1616</v>
+        <v>-0.1428</v>
       </c>
       <c r="J294" t="n">
-        <v>-3.7168</v>
+        <v>-3.2844</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.88</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1616</v>
+        <v>-0.1428</v>
       </c>
       <c r="J295" t="n">
-        <v>-3.7168</v>
+        <v>-3.2844</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.62</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.4116</v>
+        <v>-0.4017</v>
       </c>
       <c r="J296" t="n">
-        <v>-9.466799999999999</v>
+        <v>-9.239100000000001</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.57</v>
       </c>
       <c r="I297" t="n">
-        <v>1.1938</v>
+        <v>1.2085</v>
       </c>
       <c r="J297" t="n">
-        <v>27.4574</v>
+        <v>27.7955</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.47</v>
       </c>
       <c r="I298" t="n">
-        <v>1.0574</v>
+        <v>1.0641</v>
       </c>
       <c r="J298" t="n">
-        <v>24.3202</v>
+        <v>24.4743</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.17</v>
       </c>
       <c r="I299" t="n">
-        <v>0.4764</v>
+        <v>0.4428</v>
       </c>
       <c r="J299" t="n">
-        <v>10.9572</v>
+        <v>10.1844</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.98</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.1391</v>
+        <v>-0.1121</v>
       </c>
       <c r="J300" t="n">
-        <v>-3.1993</v>
+        <v>-2.5783</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.93</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3013</v>
+        <v>-0.2623</v>
       </c>
       <c r="J301" t="n">
-        <v>-6.9299</v>
+        <v>-6.0329</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.38</v>
       </c>
       <c r="I302" t="n">
-        <v>0.5174</v>
+        <v>0.4485</v>
       </c>
       <c r="J302" t="n">
-        <v>18.6264</v>
+        <v>16.146</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.11</v>
       </c>
       <c r="I303" t="n">
-        <v>0.1924</v>
+        <v>0.1506</v>
       </c>
       <c r="J303" t="n">
-        <v>6.9264</v>
+        <v>5.4216</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.09</v>
       </c>
       <c r="I304" t="n">
-        <v>0.1645</v>
+        <v>0.127</v>
       </c>
       <c r="J304" t="n">
-        <v>5.922</v>
+        <v>4.572</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.08</v>
       </c>
       <c r="I305" t="n">
-        <v>0.1501</v>
+        <v>0.115</v>
       </c>
       <c r="J305" t="n">
-        <v>5.4036</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.78</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.2797</v>
+        <v>-0.2614</v>
       </c>
       <c r="J306" t="n">
-        <v>-10.0692</v>
+        <v>-9.410399999999999</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.21</v>
       </c>
       <c r="I307" t="n">
-        <v>0.3664</v>
+        <v>0.361</v>
       </c>
       <c r="J307" t="n">
-        <v>13.1904</v>
+        <v>12.996</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.02</v>
       </c>
       <c r="I308" t="n">
-        <v>0.065</v>
+        <v>0.052</v>
       </c>
       <c r="J308" t="n">
-        <v>2.34</v>
+        <v>1.872</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.88</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.1637</v>
+        <v>-0.1443</v>
       </c>
       <c r="J309" t="n">
-        <v>-5.8932</v>
+        <v>-5.1948</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.85</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1957</v>
+        <v>-0.1755</v>
       </c>
       <c r="J310" t="n">
-        <v>-7.0452</v>
+        <v>-6.318</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.72</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.3232</v>
+        <v>-0.3064</v>
       </c>
       <c r="J311" t="n">
-        <v>-11.6352</v>
+        <v>-11.0304</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.12</v>
       </c>
       <c r="I312" t="n">
-        <v>0.3055</v>
+        <v>0.2546</v>
       </c>
       <c r="J312" t="n">
-        <v>8.554</v>
+        <v>7.1288</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.02</v>
       </c>
       <c r="I313" t="n">
-        <v>0.0834</v>
+        <v>0.0595</v>
       </c>
       <c r="J313" t="n">
-        <v>2.3352</v>
+        <v>1.666</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>0.96</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.06859999999999999</v>
+        <v>-0.0561</v>
       </c>
       <c r="J314" t="n">
-        <v>-1.9208</v>
+        <v>-1.5708</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.88</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.1636</v>
+        <v>-0.1442</v>
       </c>
       <c r="J315" t="n">
-        <v>-4.5808</v>
+        <v>-4.0376</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.3508</v>
+        <v>-0.3358</v>
       </c>
       <c r="J316" t="n">
-        <v>-9.8224</v>
+        <v>-9.4024</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.69</v>
       </c>
       <c r="I317" t="n">
-        <v>1.3599</v>
+        <v>1.3846</v>
       </c>
       <c r="J317" t="n">
-        <v>38.0772</v>
+        <v>38.7688</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.26</v>
       </c>
       <c r="I318" t="n">
-        <v>0.6721</v>
+        <v>0.6409</v>
       </c>
       <c r="J318" t="n">
-        <v>18.8188</v>
+        <v>17.9452</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.1</v>
       </c>
       <c r="I319" t="n">
-        <v>0.3112</v>
+        <v>0.2783</v>
       </c>
       <c r="J319" t="n">
-        <v>8.7136</v>
+        <v>7.7924</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>1.03</v>
       </c>
       <c r="I320" t="n">
-        <v>0.1052</v>
+        <v>0.0847</v>
       </c>
       <c r="J320" t="n">
-        <v>2.9456</v>
+        <v>2.3716</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.89</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.4054</v>
+        <v>-0.3643</v>
       </c>
       <c r="J321" t="n">
-        <v>-11.3512</v>
+        <v>-10.2004</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.27</v>
       </c>
       <c r="I322" t="n">
-        <v>0.5327</v>
+        <v>0.4731</v>
       </c>
       <c r="J322" t="n">
-        <v>21.8407</v>
+        <v>19.3971</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.11</v>
       </c>
       <c r="I323" t="n">
-        <v>0.261</v>
+        <v>0.2154</v>
       </c>
       <c r="J323" t="n">
-        <v>10.701</v>
+        <v>8.8314</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.08</v>
       </c>
       <c r="I324" t="n">
-        <v>0.2032</v>
+        <v>0.164</v>
       </c>
       <c r="J324" t="n">
-        <v>8.331200000000001</v>
+        <v>6.724</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>0.97</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.0635</v>
+        <v>-0.0497</v>
       </c>
       <c r="J325" t="n">
-        <v>-2.6035</v>
+        <v>-2.0377</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.92</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.1295</v>
+        <v>-0.1103</v>
       </c>
       <c r="J326" t="n">
-        <v>-5.3095</v>
+        <v>-4.5223</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.35</v>
       </c>
       <c r="I327" t="n">
-        <v>0.916</v>
+        <v>0.9026999999999999</v>
       </c>
       <c r="J327" t="n">
-        <v>37.556</v>
+        <v>37.0107</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.07</v>
       </c>
       <c r="I328" t="n">
-        <v>0.2604</v>
+        <v>0.2217</v>
       </c>
       <c r="J328" t="n">
-        <v>10.6764</v>
+        <v>9.089700000000001</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.93</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.2587</v>
+        <v>-0.2204</v>
       </c>
       <c r="J329" t="n">
-        <v>-10.6067</v>
+        <v>-9.0364</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.89</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.3674</v>
+        <v>-0.325</v>
       </c>
       <c r="J330" t="n">
-        <v>-15.0634</v>
+        <v>-13.325</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.74</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.7216</v>
+        <v>-0.6899</v>
       </c>
       <c r="J331" t="n">
-        <v>-29.5856</v>
+        <v>-28.2859</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.77</v>
       </c>
       <c r="I332" t="n">
-        <v>0.8643</v>
+        <v>0.7941</v>
       </c>
       <c r="J332" t="n">
-        <v>20.7432</v>
+        <v>19.0584</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.68</v>
       </c>
       <c r="I333" t="n">
-        <v>0.7804</v>
+        <v>0.7086</v>
       </c>
       <c r="J333" t="n">
-        <v>18.7296</v>
+        <v>17.0064</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.14</v>
       </c>
       <c r="I334" t="n">
-        <v>0.2133</v>
+        <v>0.1722</v>
       </c>
       <c r="J334" t="n">
-        <v>5.1192</v>
+        <v>4.1328</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>1.1</v>
       </c>
       <c r="I335" t="n">
-        <v>0.1581</v>
+        <v>0.1238</v>
       </c>
       <c r="J335" t="n">
-        <v>3.7944</v>
+        <v>2.9712</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.99</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.0499</v>
+        <v>-0.0412</v>
       </c>
       <c r="J336" t="n">
-        <v>-1.1976</v>
+        <v>-0.9888</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>0.9</v>
       </c>
       <c r="I337" t="n">
-        <v>-0.1132</v>
+        <v>-0.0974</v>
       </c>
       <c r="J337" t="n">
-        <v>-2.7168</v>
+        <v>-2.3376</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>0.86</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.1599</v>
+        <v>-0.1442</v>
       </c>
       <c r="J338" t="n">
-        <v>-3.8376</v>
+        <v>-3.4608</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>0.66</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.3536</v>
+        <v>-0.3403</v>
       </c>
       <c r="J339" t="n">
-        <v>-8.4864</v>
+        <v>-8.167199999999999</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.62</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.3893</v>
+        <v>-0.3776</v>
       </c>
       <c r="J340" t="n">
-        <v>-9.3432</v>
+        <v>-9.0624</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.51</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.4865</v>
+        <v>-0.4833</v>
       </c>
       <c r="J341" t="n">
-        <v>-11.676</v>
+        <v>-11.5992</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.54</v>
       </c>
       <c r="I342" t="n">
-        <v>0.9357</v>
+        <v>0.8917</v>
       </c>
       <c r="J342" t="n">
-        <v>32.7495</v>
+        <v>31.2095</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.09</v>
       </c>
       <c r="I343" t="n">
-        <v>0.2246</v>
+        <v>0.1823</v>
       </c>
       <c r="J343" t="n">
-        <v>7.861</v>
+        <v>6.3805</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.03</v>
       </c>
       <c r="I344" t="n">
-        <v>0.0951</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="J344" t="n">
-        <v>3.3285</v>
+        <v>2.5025</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>0.95</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.09030000000000001</v>
+        <v>-0.0738</v>
       </c>
       <c r="J345" t="n">
-        <v>-3.1605</v>
+        <v>-2.583</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.66</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.3885</v>
+        <v>-0.3778</v>
       </c>
       <c r="J346" t="n">
-        <v>-13.5975</v>
+        <v>-13.223</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>1.21</v>
       </c>
       <c r="I347" t="n">
-        <v>0.6054</v>
+        <v>0.5667</v>
       </c>
       <c r="J347" t="n">
-        <v>21.189</v>
+        <v>19.8345</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>1.11</v>
       </c>
       <c r="I348" t="n">
-        <v>0.3643</v>
+        <v>0.3223</v>
       </c>
       <c r="J348" t="n">
-        <v>12.7505</v>
+        <v>11.2805</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>1.05</v>
       </c>
       <c r="I349" t="n">
-        <v>0.1973</v>
+        <v>0.1638</v>
       </c>
       <c r="J349" t="n">
-        <v>6.9055</v>
+        <v>5.733</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.98</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.1018</v>
+        <v>-0.078</v>
       </c>
       <c r="J350" t="n">
-        <v>-3.563</v>
+        <v>-2.73</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.73</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.7476</v>
+        <v>-0.7181999999999999</v>
       </c>
       <c r="J351" t="n">
-        <v>-26.166</v>
+        <v>-25.137</v>
       </c>
     </row>
     <row r="352">
@@ -16429,10 +16429,10 @@
         <v>1.85</v>
       </c>
       <c r="I352" t="n">
-        <v>1.5046</v>
+        <v>1.5364</v>
       </c>
       <c r="J352" t="n">
-        <v>31.5966</v>
+        <v>32.2644</v>
       </c>
     </row>
     <row r="353">
@@ -16469,10 +16469,10 @@
         <v>1.72</v>
       </c>
       <c r="I353" t="n">
-        <v>1.3463</v>
+        <v>1.3686</v>
       </c>
       <c r="J353" t="n">
-        <v>28.2723</v>
+        <v>28.7406</v>
       </c>
     </row>
     <row r="354">
@@ -16509,10 +16509,10 @@
         <v>1.24</v>
       </c>
       <c r="I354" t="n">
-        <v>0.5995</v>
+        <v>0.5747</v>
       </c>
       <c r="J354" t="n">
-        <v>12.5895</v>
+        <v>12.0687</v>
       </c>
     </row>
     <row r="355">
@@ -16549,10 +16549,10 @@
         <v>1.19</v>
       </c>
       <c r="I355" t="n">
-        <v>0.4905</v>
+        <v>0.4612</v>
       </c>
       <c r="J355" t="n">
-        <v>10.3005</v>
+        <v>9.6852</v>
       </c>
     </row>
     <row r="356">
@@ -16589,10 +16589,10 @@
         <v>1.16</v>
       </c>
       <c r="I356" t="n">
-        <v>0.4217</v>
+        <v>0.3904</v>
       </c>
       <c r="J356" t="n">
-        <v>8.855700000000001</v>
+        <v>8.198399999999999</v>
       </c>
     </row>
     <row r="357">
@@ -16629,10 +16629,10 @@
         <v>1.09</v>
       </c>
       <c r="I357" t="n">
-        <v>0.315</v>
+        <v>0.2771</v>
       </c>
       <c r="J357" t="n">
-        <v>6.615</v>
+        <v>5.8191</v>
       </c>
     </row>
     <row r="358">
@@ -16669,10 +16669,10 @@
         <v>0.8</v>
       </c>
       <c r="I358" t="n">
-        <v>-0.2279</v>
+        <v>-0.2124</v>
       </c>
       <c r="J358" t="n">
-        <v>-4.7859</v>
+        <v>-4.4604</v>
       </c>
     </row>
     <row r="359">
@@ -16709,10 +16709,10 @@
         <v>0.72</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.3026</v>
+        <v>-0.2874</v>
       </c>
       <c r="J359" t="n">
-        <v>-6.3546</v>
+        <v>-6.0354</v>
       </c>
     </row>
     <row r="360">
@@ -16749,10 +16749,10 @@
         <v>0.6</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.4103</v>
+        <v>-0.3998</v>
       </c>
       <c r="J360" t="n">
-        <v>-8.616300000000001</v>
+        <v>-8.395799999999999</v>
       </c>
     </row>
     <row r="361">
@@ -16789,10 +16789,10 @@
         <v>0.47</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.5246</v>
+        <v>-0.5263</v>
       </c>
       <c r="J361" t="n">
-        <v>-11.0166</v>
+        <v>-11.0523</v>
       </c>
     </row>
     <row r="362">
@@ -16829,10 +16829,10 @@
         <v>1.33</v>
       </c>
       <c r="I362" t="n">
-        <v>0.8605</v>
+        <v>0.8397</v>
       </c>
       <c r="J362" t="n">
-        <v>34.42</v>
+        <v>33.588</v>
       </c>
     </row>
     <row r="363">
@@ -16869,10 +16869,10 @@
         <v>1.14</v>
       </c>
       <c r="I363" t="n">
-        <v>0.436</v>
+        <v>0.3937</v>
       </c>
       <c r="J363" t="n">
-        <v>17.44</v>
+        <v>15.748</v>
       </c>
     </row>
     <row r="364">
@@ -16909,10 +16909,10 @@
         <v>1.06</v>
       </c>
       <c r="I364" t="n">
-        <v>0.2246</v>
+        <v>0.1896</v>
       </c>
       <c r="J364" t="n">
-        <v>8.984</v>
+        <v>7.584</v>
       </c>
     </row>
     <row r="365">
@@ -16949,10 +16949,10 @@
         <v>0.83</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.5238</v>
+        <v>-0.4823</v>
       </c>
       <c r="J365" t="n">
-        <v>-20.952</v>
+        <v>-19.292</v>
       </c>
     </row>
     <row r="366">
@@ -16989,10 +16989,10 @@
         <v>0.8</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.5941</v>
+        <v>-0.5553</v>
       </c>
       <c r="J366" t="n">
-        <v>-23.764</v>
+        <v>-22.212</v>
       </c>
     </row>
     <row r="367">
@@ -17029,10 +17029,10 @@
         <v>1.22</v>
       </c>
       <c r="I367" t="n">
-        <v>0.4469</v>
+        <v>0.3898</v>
       </c>
       <c r="J367" t="n">
-        <v>17.876</v>
+        <v>15.592</v>
       </c>
     </row>
     <row r="368">
@@ -17069,10 +17069,10 @@
         <v>1.16</v>
       </c>
       <c r="I368" t="n">
-        <v>0.3467</v>
+        <v>0.2949</v>
       </c>
       <c r="J368" t="n">
-        <v>13.868</v>
+        <v>11.796</v>
       </c>
     </row>
     <row r="369">
@@ -17109,10 +17109,10 @@
         <v>1.12</v>
       </c>
       <c r="I369" t="n">
-        <v>0.276</v>
+        <v>0.2301</v>
       </c>
       <c r="J369" t="n">
-        <v>11.04</v>
+        <v>9.204000000000001</v>
       </c>
     </row>
     <row r="370">
@@ -17149,10 +17149,10 @@
         <v>1.11</v>
       </c>
       <c r="I370" t="n">
-        <v>0.2578</v>
+        <v>0.2136</v>
       </c>
       <c r="J370" t="n">
-        <v>10.312</v>
+        <v>8.544</v>
       </c>
     </row>
     <row r="371">
@@ -17189,10 +17189,10 @@
         <v>0.89</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.1668</v>
+        <v>-0.1465</v>
       </c>
       <c r="J371" t="n">
-        <v>-6.672</v>
+        <v>-5.86</v>
       </c>
     </row>
   </sheetData>
